--- a/mahkeme/2025-02-Dosya Listesi.xlsx
+++ b/mahkeme/2025-02-Dosya Listesi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\aaGitMe\yzhn\mahkeme\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1092DA00-AC53-470A-BA99-0540416E9D90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32C5E22B-92B6-47E1-9648-308CA2085B11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -132,7 +132,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="171" formatCode="dd/mm/yy;@"/>
+    <numFmt numFmtId="164" formatCode="dd/mm/yy;@"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -244,15 +244,15 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -597,8 +597,8 @@
         <v>28</v>
       </c>
       <c r="C2" s="6"/>
-      <c r="D2" s="5" t="s">
-        <v>5</v>
+      <c r="D2" s="6" t="s">
+        <v>33</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>3</v>

--- a/mahkeme/2025-02-Dosya Listesi.xlsx
+++ b/mahkeme/2025-02-Dosya Listesi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\aaGitMe\yzhn\mahkeme\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32C5E22B-92B6-47E1-9648-308CA2085B11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C74556E-C3A5-449D-B1EF-784B5D356FC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,26 +20,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="33">
   <si>
     <t>Dosya Listesi</t>
   </si>
   <si>
-    <t>Alacaklı</t>
-  </si>
-  <si>
-    <t>Tokat İcra Dairesi</t>
-  </si>
-  <si>
     <t>2025/1266</t>
   </si>
   <si>
-    <t>İcra Dosyası</t>
-  </si>
-  <si>
-    <t>Açık</t>
-  </si>
-  <si>
     <t>2024/22182</t>
   </si>
   <si>
@@ -67,9 +55,6 @@
     <t>2024/3369</t>
   </si>
   <si>
-    <t>2023/20377</t>
-  </si>
-  <si>
     <t>salihant</t>
   </si>
   <si>
@@ -88,9 +73,6 @@
     <t>alidemirel</t>
   </si>
   <si>
-    <t>ö14-xxx</t>
-  </si>
-  <si>
     <t>2024/217</t>
   </si>
   <si>
@@ -100,9 +82,6 @@
     <t>red</t>
   </si>
   <si>
-    <t>kabul</t>
-  </si>
-  <si>
     <t>icr-ö13</t>
   </si>
   <si>
@@ -125,29 +104,38 @@
   </si>
   <si>
     <t>KBL</t>
+  </si>
+  <si>
+    <t>TL</t>
+  </si>
+  <si>
+    <t>Dosya No</t>
+  </si>
+  <si>
+    <t>Açlş</t>
+  </si>
+  <si>
+    <t>Karar</t>
+  </si>
+  <si>
+    <t>icr-thly</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="dd/mm/yy;@"/>
+    <numFmt numFmtId="166" formatCode="[$-41F]d\ mmm\ yyyy;@"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="162"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="7" tint="0.79998168889431442"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="162"/>
@@ -183,8 +171,31 @@
       <family val="2"/>
       <charset val="162"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="162"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="7" tint="0.79998168889431442"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="162"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="162"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -221,8 +232,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -230,33 +259,55 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -571,422 +622,342 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13" customWidth="1"/>
-    <col min="6" max="7" width="8.28515625" style="9" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.5703125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="15.5703125" customWidth="1"/>
-    <col min="12" max="12" width="7.85546875" customWidth="1"/>
+    <col min="6" max="7" width="8.28515625" style="5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="21">
+        <v>45700</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="15"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" s="15"/>
+      <c r="E2" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="G2" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2" s="15"/>
+    </row>
+    <row r="3" spans="1:8" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="3">
+        <v>97</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="F3" s="6">
+        <v>45475</v>
+      </c>
+      <c r="G3" s="6"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="3"/>
+      <c r="D4" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="6">
+        <v>45588</v>
+      </c>
+      <c r="G4" s="6"/>
+    </row>
+    <row r="5" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="17">
+        <v>178</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="F5" s="19">
+        <v>45604</v>
+      </c>
+      <c r="G5" s="19"/>
+      <c r="H5" s="15"/>
+    </row>
+    <row r="6" spans="1:8" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="3">
+        <v>214</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" s="6">
+        <v>45475</v>
+      </c>
+      <c r="G6" s="6"/>
+    </row>
+    <row r="7" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="19">
+        <v>45676</v>
+      </c>
+      <c r="G7" s="19"/>
+      <c r="H7" s="15"/>
+    </row>
+    <row r="8" spans="1:8" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="3">
+        <v>113</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="6">
+        <v>45475</v>
+      </c>
+      <c r="G8" s="6"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="3"/>
+      <c r="D9" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F9" s="6">
+        <v>45588</v>
+      </c>
+      <c r="G9" s="6"/>
+    </row>
+    <row r="10" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="18">
+        <v>198</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" s="19">
+        <v>45603</v>
+      </c>
+      <c r="G10" s="19"/>
+      <c r="H10" s="15"/>
+    </row>
+    <row r="11" spans="1:8" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10">
-        <v>45676</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K2" t="s">
-        <v>4</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
+      <c r="B11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" s="5">
+        <v>45342</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F12" s="5">
+        <v>45537</v>
+      </c>
+      <c r="G12" s="5">
+        <v>45691</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="15"/>
+    </row>
+    <row r="14" spans="1:8" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14" s="30" t="s">
+        <v>27</v>
+      </c>
+      <c r="E14" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" s="5">
+        <v>45438</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="F15" s="29">
+        <v>45486</v>
+      </c>
+      <c r="G15" s="10">
+        <v>45588</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" s="1"/>
+      <c r="D16" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="6">
-        <v>178</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10">
-        <v>45604</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="E16" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" s="5">
-        <v>198</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10">
-        <v>45603</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K4" t="s">
-        <v>4</v>
-      </c>
-      <c r="L4" s="5" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10">
-        <v>45588</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K5" t="s">
-        <v>4</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" s="5"/>
-      <c r="D6" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10">
-        <v>45588</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K6" t="s">
-        <v>4</v>
-      </c>
-      <c r="L6" s="5" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" s="5">
-        <v>97</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10">
-        <v>45475</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K7" t="s">
-        <v>4</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="5">
-        <v>214</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10">
-        <v>45475</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K8" t="s">
-        <v>4</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" s="5">
-        <v>113</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10">
-        <v>45475</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K9" t="s">
-        <v>4</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E11" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11" s="9">
-        <v>45342</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K11" t="s">
-        <v>4</v>
-      </c>
-      <c r="L11" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F12" s="9">
-        <v>45691</v>
-      </c>
-      <c r="G12" s="9">
-        <v>45537</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" s="18" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C15">
-        <v>0</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E15" t="s">
-        <v>13</v>
-      </c>
-      <c r="G15" s="9">
-        <v>45438</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K15" t="s">
-        <v>4</v>
-      </c>
-      <c r="L15" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B16" s="2" t="s">
+      <c r="F16" s="28">
+        <v>45590</v>
+      </c>
+      <c r="G16" s="28">
+        <v>45688</v>
+      </c>
+      <c r="H16" s="1"/>
+    </row>
+    <row r="17" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="D16" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="E16" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="F16" s="17">
-        <v>45588</v>
-      </c>
-      <c r="G16" s="9">
-        <v>45486</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F17" s="14">
-        <v>45688</v>
-      </c>
-      <c r="G17" s="9">
-        <v>45590</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="11"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D19" t="s">
-        <v>5</v>
-      </c>
-      <c r="E19" t="s">
-        <v>15</v>
-      </c>
-      <c r="G19" s="9">
-        <v>45288</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K19" t="s">
-        <v>4</v>
-      </c>
-      <c r="L19" t="s">
-        <v>1</v>
-      </c>
-    </row>
+      <c r="C17" s="11"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="13"/>
+      <c r="H17" s="11"/>
+    </row>
+    <row r="18" spans="1:8" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/mahkeme/2025-02-Dosya Listesi.xlsx
+++ b/mahkeme/2025-02-Dosya Listesi.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\aaGitMe\yzhn\mahkeme\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C74556E-C3A5-449D-B1EF-784B5D356FC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{833724E1-168B-4D09-B1DF-BBFDD8CC1687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="375" yWindow="555" windowWidth="22920" windowHeight="13455" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="34">
   <si>
     <t>Dosya Listesi</t>
   </si>
@@ -119,6 +119,9 @@
   </si>
   <si>
     <t>icr-thly</t>
+  </si>
+  <si>
+    <t>itrz-arablc</t>
   </si>
 </sst>
 </file>
@@ -127,7 +130,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="dd/mm/yy;@"/>
-    <numFmt numFmtId="166" formatCode="[$-41F]d\ mmm\ yyyy;@"/>
+    <numFmt numFmtId="165" formatCode="[$-41F]d\ mmm\ yyyy;@"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -296,7 +299,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -627,7 +630,7 @@
   <cols>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13" customWidth="1"/>
     <col min="6" max="7" width="8.28515625" style="5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.28515625" bestFit="1" customWidth="1"/>
@@ -676,7 +679,7 @@
         <v>97</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>6</v>
@@ -695,7 +698,7 @@
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="4" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>4</v>
@@ -715,8 +718,8 @@
       <c r="C5" s="17">
         <v>178</v>
       </c>
-      <c r="D5" s="17" t="s">
-        <v>26</v>
+      <c r="D5" s="4" t="s">
+        <v>33</v>
       </c>
       <c r="E5" s="18" t="s">
         <v>2</v>
@@ -738,7 +741,7 @@
         <v>214</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>7</v>
@@ -779,7 +782,7 @@
         <v>113</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>8</v>
@@ -798,7 +801,7 @@
       </c>
       <c r="C9" s="3"/>
       <c r="D9" s="4" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>5</v>
@@ -818,8 +821,8 @@
       <c r="C10" s="18">
         <v>198</v>
       </c>
-      <c r="D10" s="17" t="s">
-        <v>26</v>
+      <c r="D10" s="4" t="s">
+        <v>33</v>
       </c>
       <c r="E10" s="18" t="s">
         <v>3</v>

--- a/mahkeme/2025-02-Dosya Listesi.xlsx
+++ b/mahkeme/2025-02-Dosya Listesi.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\aaGitMe\yzhn\mahkeme\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{833724E1-168B-4D09-B1DF-BBFDD8CC1687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5BC49E4-0C33-483B-92D4-6FE95679BFB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="375" yWindow="555" windowWidth="22920" windowHeight="13455" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="57">
   <si>
     <t>Dosya Listesi</t>
   </si>
@@ -121,7 +121,97 @@
     <t>icr-thly</t>
   </si>
   <si>
-    <t>itrz-arablc</t>
+    <t>2025/560</t>
+  </si>
+  <si>
+    <t>sh2-itrzipt</t>
+  </si>
+  <si>
+    <t>2025/263</t>
+  </si>
+  <si>
+    <t>2025/264</t>
+  </si>
+  <si>
+    <t>2025-559</t>
+  </si>
+  <si>
+    <t>tahliye</t>
+  </si>
+  <si>
+    <t>2025/25158</t>
+  </si>
+  <si>
+    <t>Arablc.No</t>
+  </si>
+  <si>
+    <t>2025/21318</t>
+  </si>
+  <si>
+    <t>2025/21077</t>
+  </si>
+  <si>
+    <t>2025/20896</t>
+  </si>
+  <si>
+    <t>2025/35</t>
+  </si>
+  <si>
+    <t>2025/34</t>
+  </si>
+  <si>
+    <t>2024/397</t>
+  </si>
+  <si>
+    <t>2024/398</t>
+  </si>
+  <si>
+    <t>2024/202930</t>
+  </si>
+  <si>
+    <t>2024/203836</t>
+  </si>
+  <si>
+    <t>2025/33</t>
+  </si>
+  <si>
+    <t>2025/43</t>
+  </si>
+  <si>
+    <t>Arablc.Trh</t>
+  </si>
+  <si>
+    <t>ada-parsel - kira sözl -  dsmgs vergisi</t>
+  </si>
+  <si>
+    <t>ön inceleme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sh-itrzipt </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">sh2-itrzipt </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="162"/>
+      </rPr>
+      <t>sadece 182.437 TL için</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="162"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
   </si>
 </sst>
 </file>
@@ -132,7 +222,7 @@
     <numFmt numFmtId="164" formatCode="dd/mm/yy;@"/>
     <numFmt numFmtId="165" formatCode="[$-41F]d\ mmm\ yyyy;@"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -197,8 +287,30 @@
       <family val="2"/>
       <charset val="162"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="7" tint="0.39997558519241921"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="162"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="5"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="162"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="7" tint="0.79998168889431442"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="162"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -225,12 +337,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="-0.499984740745262"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -243,18 +349,42 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="-0.249977111117893"/>
+        <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC00000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -271,11 +401,33 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="double">
+        <color indexed="64"/>
+      </top>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -283,19 +435,10 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -304,13 +447,78 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -625,342 +833,700 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:J38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13" customWidth="1"/>
-    <col min="6" max="7" width="8.28515625" style="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13" customWidth="1"/>
+    <col min="3" max="3" width="9.5703125" style="28" customWidth="1"/>
+    <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4" customWidth="1"/>
+    <col min="7" max="7" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10" style="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
+    <row r="1" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="21">
-        <v>45700</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="15"/>
-      <c r="B2" s="15"/>
-      <c r="C2" s="22" t="s">
+      <c r="B1" s="9"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="12">
+        <v>45706</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="9"/>
+      <c r="B2" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="34" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" s="33"/>
+      <c r="E2" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="D2" s="15"/>
-      <c r="E2" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="F2" s="24" t="s">
-        <v>30</v>
-      </c>
-      <c r="G2" s="24" t="s">
+      <c r="F2" s="13"/>
+      <c r="G2" s="33" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2" s="33" t="s">
+        <v>52</v>
+      </c>
+      <c r="I2" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="H2" s="15"/>
-    </row>
-    <row r="3" spans="1:8" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="J2" s="9"/>
+    </row>
+    <row r="3" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="27">
+        <v>45475</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="3">
+      <c r="E3" s="3">
         <v>97</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="F3" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="H3" s="6">
+        <v>45705</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="27">
+        <v>45604</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="4">
+        <v>178</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="H4" s="36">
+        <v>45705</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="1"/>
+      <c r="B5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="28">
+        <v>45704</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="14"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="26"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="9"/>
+    </row>
+    <row r="7" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="37">
+        <v>45588</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H7" s="6">
+        <v>45630</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="4"/>
+      <c r="B8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="27"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="H8" s="6">
+        <v>45630</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="4"/>
+      <c r="B9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="57">
+        <v>45704</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9"/>
+    </row>
+    <row r="10" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="14"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="14"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="10"/>
+      <c r="J10" s="9"/>
+    </row>
+    <row r="11" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="27">
+        <v>45475</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="3">
+        <v>214</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H11" s="6">
+        <v>45702</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="2"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="H12" s="6">
+        <v>45702</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="1"/>
+      <c r="B13" t="s">
         <v>33</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="6">
+      <c r="C13" s="28">
+        <v>45704</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="G13" s="1"/>
+      <c r="H13"/>
+    </row>
+    <row r="14" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="14"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="26"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="9"/>
+      <c r="I14" s="10"/>
+      <c r="J14" s="9"/>
+    </row>
+    <row r="15" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15" s="27">
+        <v>45676</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="27"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H16" s="17"/>
+    </row>
+    <row r="17" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="14"/>
+      <c r="B17" s="9"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="10"/>
+      <c r="J17" s="9"/>
+    </row>
+    <row r="18" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C18" s="58">
+        <v>45603</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="3">
+        <v>198</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H18" s="5">
+        <v>45705</v>
+      </c>
+      <c r="I18" s="6"/>
+    </row>
+    <row r="19" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="4"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="27"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="H19" s="5">
+        <v>45705</v>
+      </c>
+      <c r="I19" s="6"/>
+    </row>
+    <row r="20" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="1"/>
+      <c r="B20" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" s="57">
+        <v>45704</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+    </row>
+    <row r="21" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="1"/>
+      <c r="C21" s="28">
+        <v>45705</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G21" s="1"/>
+    </row>
+    <row r="22" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="53" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="54">
+        <v>45792</v>
+      </c>
+      <c r="D22" s="55">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="H22"/>
+    </row>
+    <row r="23" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="14"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="26"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="9"/>
+      <c r="G23" s="14"/>
+      <c r="H23" s="9"/>
+      <c r="I23" s="10"/>
+      <c r="J23" s="9"/>
+    </row>
+    <row r="24" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="B24" s="39" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="40">
+        <v>45342</v>
+      </c>
+      <c r="D24" s="38" t="s">
+        <v>14</v>
+      </c>
+      <c r="E24" s="39"/>
+      <c r="F24" s="50" t="s">
+        <v>26</v>
+      </c>
+      <c r="G24" s="39"/>
+      <c r="H24" s="41"/>
+      <c r="I24" s="41"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="38"/>
+      <c r="B25" s="38" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" s="40">
+        <v>45537</v>
+      </c>
+      <c r="D25" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="E25" s="39"/>
+      <c r="F25" s="51" t="s">
+        <v>19</v>
+      </c>
+      <c r="G25" s="39"/>
+      <c r="H25" s="41"/>
+      <c r="I25" s="41">
+        <v>45691</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="30"/>
+      <c r="B26" s="31"/>
+      <c r="C26" s="32"/>
+      <c r="D26" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+    </row>
+    <row r="27" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="14"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="26"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="10"/>
+      <c r="G27" s="10"/>
+      <c r="H27" s="10"/>
+      <c r="I27" s="10"/>
+      <c r="J27" s="9"/>
+    </row>
+    <row r="28" spans="1:10" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="38" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="C28" s="40">
+        <v>45438</v>
+      </c>
+      <c r="D28" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="39">
+        <v>0</v>
+      </c>
+      <c r="F28" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="G28" s="39"/>
+      <c r="H28" s="41"/>
+      <c r="I28" s="41"/>
+    </row>
+    <row r="29" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="38"/>
+      <c r="B29" s="42" t="s">
+        <v>17</v>
+      </c>
+      <c r="C29" s="43">
+        <v>45486</v>
+      </c>
+      <c r="D29" s="38" t="s">
+        <v>25</v>
+      </c>
+      <c r="E29" s="39"/>
+      <c r="F29" s="44" t="s">
+        <v>27</v>
+      </c>
+      <c r="G29" s="39"/>
+      <c r="H29" s="41"/>
+      <c r="I29" s="45">
+        <v>45588</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A30" s="38"/>
+      <c r="B30" s="42" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30" s="43">
+        <v>45590</v>
+      </c>
+      <c r="D30" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="E30" s="38"/>
+      <c r="F30" s="44" t="s">
+        <v>27</v>
+      </c>
+      <c r="G30" s="39"/>
+      <c r="H30" s="41"/>
+      <c r="I30" s="45">
+        <v>45688</v>
+      </c>
+      <c r="J30" s="1"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" s="19"/>
+      <c r="B31" s="20"/>
+      <c r="C31" s="46"/>
+      <c r="D31" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="E31" s="20"/>
+      <c r="F31" s="21"/>
+      <c r="G31" s="18"/>
+      <c r="H31" s="17"/>
+      <c r="I31" s="22"/>
+      <c r="J31" s="23"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="1"/>
+      <c r="B32" s="23"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="23"/>
+      <c r="F32" s="25"/>
+      <c r="I32" s="24"/>
+      <c r="J32" s="23"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" s="1"/>
+      <c r="B33" s="23"/>
+      <c r="C33" s="29"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="23"/>
+      <c r="F33" s="25"/>
+      <c r="I33" s="24"/>
+      <c r="J33" s="23"/>
+    </row>
+    <row r="34" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="9"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="26"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="9"/>
+      <c r="G34" s="9"/>
+      <c r="H34" s="10"/>
+      <c r="I34" s="10"/>
+      <c r="J34" s="9"/>
+    </row>
+    <row r="35" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="38" t="s">
+        <v>13</v>
+      </c>
+      <c r="B35" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="C35" s="40">
+        <v>45588</v>
+      </c>
+      <c r="D35" s="38" t="s">
+        <v>21</v>
+      </c>
+      <c r="E35" s="39"/>
+      <c r="F35" s="39"/>
+      <c r="G35" s="38" t="s">
+        <v>46</v>
+      </c>
+      <c r="H35" s="41">
+        <v>45625</v>
+      </c>
+      <c r="I35" s="8">
+        <v>45672</v>
+      </c>
+      <c r="J35" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" s="38" t="s">
+        <v>13</v>
+      </c>
+      <c r="B36" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="C36" s="40">
+        <v>45588</v>
+      </c>
+      <c r="D36" s="38" t="s">
+        <v>21</v>
+      </c>
+      <c r="E36" s="39"/>
+      <c r="F36" s="39"/>
+      <c r="G36" s="52" t="s">
+        <v>49</v>
+      </c>
+      <c r="H36" s="41">
+        <v>45625</v>
+      </c>
+      <c r="I36" s="8">
+        <v>45672</v>
+      </c>
+      <c r="J36" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B37" s="47" t="s">
+        <v>8</v>
+      </c>
+      <c r="C37" s="48">
         <v>45475</v>
       </c>
-      <c r="G3" s="6"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F4" s="6">
-        <v>45588</v>
-      </c>
-      <c r="G4" s="6"/>
-    </row>
-    <row r="5" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="17" t="s">
+      <c r="D37" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="17">
-        <v>178</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E5" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="F5" s="19">
-        <v>45604</v>
-      </c>
-      <c r="G5" s="19"/>
-      <c r="H5" s="15"/>
-    </row>
-    <row r="6" spans="1:8" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="4" t="s">
+      <c r="E37" s="47">
+        <v>113</v>
+      </c>
+      <c r="F37" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="G37" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="H37" s="49">
+        <v>45705</v>
+      </c>
+      <c r="I37" s="8">
+        <v>45672</v>
+      </c>
+      <c r="J37" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B38" s="47" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38" s="48"/>
+      <c r="D38" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="3">
-        <v>214</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" s="6">
-        <v>45475</v>
-      </c>
-      <c r="G6" s="6"/>
-    </row>
-    <row r="7" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17" t="s">
+      <c r="E38" s="47">
+        <v>113</v>
+      </c>
+      <c r="F38" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="E7" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="F7" s="19">
-        <v>45676</v>
-      </c>
-      <c r="G7" s="19"/>
-      <c r="H7" s="15"/>
-    </row>
-    <row r="8" spans="1:8" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="3">
-        <v>113</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" s="6">
-        <v>45475</v>
-      </c>
-      <c r="G8" s="6"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" s="3"/>
-      <c r="D9" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" s="6">
-        <v>45588</v>
-      </c>
-      <c r="G9" s="6"/>
-    </row>
-    <row r="10" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="18">
-        <v>198</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E10" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="F10" s="19">
-        <v>45603</v>
-      </c>
-      <c r="G10" s="19"/>
-      <c r="H10" s="15"/>
-    </row>
-    <row r="11" spans="1:8" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" s="5">
-        <v>45342</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F12" s="5">
-        <v>45537</v>
-      </c>
-      <c r="G12" s="5">
-        <v>45691</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="15"/>
-    </row>
-    <row r="14" spans="1:8" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14">
-        <v>0</v>
-      </c>
-      <c r="D14" s="30" t="s">
-        <v>27</v>
-      </c>
-      <c r="E14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" s="5">
-        <v>45438</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="F15" s="29">
-        <v>45486</v>
-      </c>
-      <c r="G15" s="10">
-        <v>45588</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C16" s="1"/>
-      <c r="D16" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="E16" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="F16" s="28">
-        <v>45590</v>
-      </c>
-      <c r="G16" s="28">
-        <v>45688</v>
-      </c>
-      <c r="H16" s="1"/>
-    </row>
-    <row r="17" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="25" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="C17" s="11"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="11"/>
-    </row>
-    <row r="18" spans="1:8" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+      <c r="G38" s="56" t="s">
+        <v>44</v>
+      </c>
+      <c r="H38" s="49">
+        <v>45705</v>
+      </c>
+      <c r="I38" s="8">
+        <v>45672</v>
+      </c>
+      <c r="J38" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/mahkeme/2025-02-Dosya Listesi.xlsx
+++ b/mahkeme/2025-02-Dosya Listesi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\aaGitMe\yzhn\mahkeme\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5BC49E4-0C33-483B-92D4-6FE95679BFB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAD3EE35-E64C-4AE2-9DA0-EBC49782A763}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="57">
   <si>
     <t>Dosya Listesi</t>
   </si>
@@ -427,7 +427,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -519,6 +519,7 @@
     <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -833,7 +834,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -900,7 +901,7 @@
       <c r="D3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="59">
         <v>97</v>
       </c>
       <c r="F3" s="4" t="s">
@@ -924,7 +925,7 @@
       <c r="D4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="59">
         <v>178</v>
       </c>
       <c r="F4" s="4" t="s">
@@ -971,7 +972,7 @@
       <c r="C7" s="37">
         <v>45588</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="59" t="s">
         <v>21</v>
       </c>
       <c r="E7" s="3"/>
@@ -1042,7 +1043,7 @@
       <c r="D11" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="59">
         <v>214</v>
       </c>
       <c r="F11" s="4" t="s">
@@ -1083,58 +1084,39 @@
       <c r="G13" s="1"/>
       <c r="H13"/>
     </row>
-    <row r="14" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="14"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="26"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="9"/>
-    </row>
-    <row r="15" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C15" s="27">
-        <v>45676</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C16" s="27"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="H16" s="17"/>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="C14" s="28">
+        <v>45705</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G14" s="1"/>
+    </row>
+    <row r="15" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="1"/>
+      <c r="B15" s="53" t="s">
+        <v>54</v>
+      </c>
+      <c r="C15" s="54">
+        <v>45792</v>
+      </c>
+      <c r="D15" s="55">
+        <v>0.39930555555555558</v>
+      </c>
+      <c r="H15"/>
+    </row>
+    <row r="16" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16"/>
     </row>
     <row r="17" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="14"/>
       <c r="B17" s="9"/>
+      <c r="C17" s="26"/>
       <c r="D17" s="14"/>
       <c r="E17" s="9"/>
       <c r="F17" s="9"/>
@@ -1143,387 +1125,435 @@
       <c r="I17" s="10"/>
       <c r="J17" s="9"/>
     </row>
-    <row r="18" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C18" s="58">
-        <v>45603</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="3">
-        <v>198</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="C18" s="27">
+        <v>45676</v>
+      </c>
+      <c r="D18" s="59" t="s">
+        <v>21</v>
+      </c>
+      <c r="E18" s="4"/>
       <c r="F18" s="4" t="s">
         <v>26</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H18" s="5">
-        <v>45705</v>
-      </c>
-      <c r="I18" s="6"/>
-    </row>
-    <row r="19" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="4"/>
-      <c r="B19" s="3"/>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>1</v>
+      </c>
       <c r="C19" s="27"/>
       <c r="D19" s="4"/>
-      <c r="E19" s="3"/>
+      <c r="E19" s="4"/>
       <c r="F19" s="4"/>
       <c r="G19" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H19" s="17"/>
+    </row>
+    <row r="20" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="14"/>
+      <c r="B20" s="9"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="14"/>
+      <c r="H20" s="9"/>
+      <c r="I20" s="10"/>
+      <c r="J20" s="9"/>
+    </row>
+    <row r="21" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C21" s="58">
+        <v>45603</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E21" s="59">
+        <v>198</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H21" s="5">
+        <v>45705</v>
+      </c>
+      <c r="I21" s="6"/>
+    </row>
+    <row r="22" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="4"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="27"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="H19" s="5">
+      <c r="H22" s="5">
         <v>45705</v>
       </c>
-      <c r="I19" s="6"/>
-    </row>
-    <row r="20" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="1"/>
-      <c r="B20" t="s">
+      <c r="I22" s="6"/>
+    </row>
+    <row r="23" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="1"/>
+      <c r="B23" t="s">
         <v>37</v>
       </c>
-      <c r="C20" s="57">
+      <c r="C23" s="57">
         <v>45704</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D23" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-    </row>
-    <row r="21" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="1"/>
-      <c r="C21" s="28">
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+    </row>
+    <row r="24" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="1"/>
+      <c r="C24" s="28">
         <v>45705</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D24" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="G21" s="1"/>
-    </row>
-    <row r="22" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="53" t="s">
+      <c r="G24" s="1"/>
+    </row>
+    <row r="25" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="53" t="s">
         <v>54</v>
       </c>
-      <c r="C22" s="54">
+      <c r="C25" s="54">
         <v>45792</v>
       </c>
-      <c r="D22" s="55">
+      <c r="D25" s="55">
         <v>0.39583333333333331</v>
       </c>
-      <c r="H22"/>
-    </row>
-    <row r="23" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="14"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="26"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="10"/>
-      <c r="J23" s="9"/>
-    </row>
-    <row r="24" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="38" t="s">
+      <c r="H25"/>
+    </row>
+    <row r="26" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="14"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="26"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="14"/>
+      <c r="H26" s="9"/>
+      <c r="I26" s="10"/>
+      <c r="J26" s="9"/>
+    </row>
+    <row r="27" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="B24" s="39" t="s">
+      <c r="B27" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="C24" s="40">
+      <c r="C27" s="40">
         <v>45342</v>
       </c>
-      <c r="D24" s="38" t="s">
+      <c r="D27" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="E24" s="39"/>
-      <c r="F24" s="50" t="s">
+      <c r="E27" s="39"/>
+      <c r="F27" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="G24" s="39"/>
-      <c r="H24" s="41"/>
-      <c r="I24" s="41"/>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="38"/>
-      <c r="B25" s="38" t="s">
+      <c r="G27" s="39"/>
+      <c r="H27" s="41"/>
+      <c r="I27" s="41"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="38"/>
+      <c r="B28" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="40">
+      <c r="C28" s="40">
         <v>45537</v>
       </c>
-      <c r="D25" s="38" t="s">
+      <c r="D28" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="E25" s="39"/>
-      <c r="F25" s="51" t="s">
+      <c r="E28" s="39"/>
+      <c r="F28" s="51" t="s">
         <v>19</v>
-      </c>
-      <c r="G25" s="39"/>
-      <c r="H25" s="41"/>
-      <c r="I25" s="41">
-        <v>45691</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="30"/>
-      <c r="B26" s="31"/>
-      <c r="C26" s="32"/>
-      <c r="D26" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="F26" s="5"/>
-      <c r="G26" s="5"/>
-    </row>
-    <row r="27" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="14"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="26"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="10"/>
-      <c r="G27" s="10"/>
-      <c r="H27" s="10"/>
-      <c r="I27" s="10"/>
-      <c r="J27" s="9"/>
-    </row>
-    <row r="28" spans="1:10" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="B28" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="C28" s="40">
-        <v>45438</v>
-      </c>
-      <c r="D28" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="39">
-        <v>0</v>
-      </c>
-      <c r="F28" s="15" t="s">
-        <v>27</v>
       </c>
       <c r="G28" s="39"/>
       <c r="H28" s="41"/>
-      <c r="I28" s="41"/>
-    </row>
-    <row r="29" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="38"/>
-      <c r="B29" s="42" t="s">
+      <c r="I28" s="41">
+        <v>45691</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="30"/>
+      <c r="B29" s="31"/>
+      <c r="C29" s="32"/>
+      <c r="D29" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="F29" s="5"/>
+      <c r="G29" s="5"/>
+    </row>
+    <row r="30" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="14"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="26"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="10"/>
+      <c r="G30" s="10"/>
+      <c r="H30" s="10"/>
+      <c r="I30" s="10"/>
+      <c r="J30" s="9"/>
+    </row>
+    <row r="31" spans="1:10" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="38" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="C31" s="40">
+        <v>45438</v>
+      </c>
+      <c r="D31" s="38" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="39">
+        <v>0</v>
+      </c>
+      <c r="F31" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="G31" s="39"/>
+      <c r="H31" s="41"/>
+      <c r="I31" s="41"/>
+    </row>
+    <row r="32" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="38"/>
+      <c r="B32" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="C29" s="43">
+      <c r="C32" s="43">
         <v>45486</v>
       </c>
-      <c r="D29" s="38" t="s">
+      <c r="D32" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="E29" s="39"/>
-      <c r="F29" s="44" t="s">
+      <c r="E32" s="39"/>
+      <c r="F32" s="44" t="s">
         <v>27</v>
       </c>
-      <c r="G29" s="39"/>
-      <c r="H29" s="41"/>
-      <c r="I29" s="45">
+      <c r="G32" s="39"/>
+      <c r="H32" s="41"/>
+      <c r="I32" s="45">
         <v>45588</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="38"/>
-      <c r="B30" s="42" t="s">
+    <row r="33" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A33" s="38"/>
+      <c r="B33" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="C30" s="43">
+      <c r="C33" s="43">
         <v>45590</v>
       </c>
-      <c r="D30" s="38" t="s">
+      <c r="D33" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="E30" s="38"/>
-      <c r="F30" s="44" t="s">
+      <c r="E33" s="38"/>
+      <c r="F33" s="44" t="s">
         <v>27</v>
       </c>
-      <c r="G30" s="39"/>
-      <c r="H30" s="41"/>
-      <c r="I30" s="45">
+      <c r="G33" s="39"/>
+      <c r="H33" s="41"/>
+      <c r="I33" s="45">
         <v>45688</v>
       </c>
-      <c r="J30" s="1"/>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" s="19"/>
-      <c r="B31" s="20"/>
-      <c r="C31" s="46"/>
-      <c r="D31" s="19" t="s">
+      <c r="J33" s="1"/>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" s="19"/>
+      <c r="B34" s="20"/>
+      <c r="C34" s="46"/>
+      <c r="D34" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E31" s="20"/>
-      <c r="F31" s="21"/>
-      <c r="G31" s="18"/>
-      <c r="H31" s="17"/>
-      <c r="I31" s="22"/>
-      <c r="J31" s="23"/>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" s="1"/>
-      <c r="B32" s="23"/>
-      <c r="C32" s="29"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="23"/>
-      <c r="F32" s="25"/>
-      <c r="I32" s="24"/>
-      <c r="J32" s="23"/>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="1"/>
-      <c r="B33" s="23"/>
-      <c r="C33" s="29"/>
-      <c r="D33" s="1"/>
-      <c r="E33" s="23"/>
-      <c r="F33" s="25"/>
-      <c r="I33" s="24"/>
-      <c r="J33" s="23"/>
-    </row>
-    <row r="34" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="9"/>
-      <c r="B34" s="9"/>
-      <c r="C34" s="26"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="9"/>
-      <c r="H34" s="10"/>
-      <c r="I34" s="10"/>
-      <c r="J34" s="9"/>
-    </row>
-    <row r="35" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="38" t="s">
+      <c r="E34" s="20"/>
+      <c r="F34" s="21"/>
+      <c r="G34" s="18"/>
+      <c r="H34" s="17"/>
+      <c r="I34" s="22"/>
+      <c r="J34" s="23"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" s="1"/>
+      <c r="B35" s="23"/>
+      <c r="C35" s="29"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="23"/>
+      <c r="F35" s="25"/>
+      <c r="I35" s="24"/>
+      <c r="J35" s="23"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" s="1"/>
+      <c r="B36" s="23"/>
+      <c r="C36" s="29"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="23"/>
+      <c r="F36" s="25"/>
+      <c r="I36" s="24"/>
+      <c r="J36" s="23"/>
+    </row>
+    <row r="37" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="9"/>
+      <c r="B37" s="9"/>
+      <c r="C37" s="26"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="9"/>
+      <c r="G37" s="9"/>
+      <c r="H37" s="10"/>
+      <c r="I37" s="10"/>
+      <c r="J37" s="9"/>
+    </row>
+    <row r="38" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="B35" s="39" t="s">
+      <c r="B38" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="C35" s="40">
+      <c r="C38" s="40">
         <v>45588</v>
       </c>
-      <c r="D35" s="38" t="s">
+      <c r="D38" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="E35" s="39"/>
-      <c r="F35" s="39"/>
-      <c r="G35" s="38" t="s">
+      <c r="E38" s="39"/>
+      <c r="F38" s="39"/>
+      <c r="G38" s="38" t="s">
         <v>46</v>
       </c>
-      <c r="H35" s="41">
+      <c r="H38" s="41">
         <v>45625</v>
-      </c>
-      <c r="I35" s="8">
-        <v>45672</v>
-      </c>
-      <c r="J35" s="7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="38" t="s">
-        <v>13</v>
-      </c>
-      <c r="B36" s="39" t="s">
-        <v>5</v>
-      </c>
-      <c r="C36" s="40">
-        <v>45588</v>
-      </c>
-      <c r="D36" s="38" t="s">
-        <v>21</v>
-      </c>
-      <c r="E36" s="39"/>
-      <c r="F36" s="39"/>
-      <c r="G36" s="52" t="s">
-        <v>49</v>
-      </c>
-      <c r="H36" s="41">
-        <v>45625</v>
-      </c>
-      <c r="I36" s="8">
-        <v>45672</v>
-      </c>
-      <c r="J36" s="7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B37" s="47" t="s">
-        <v>8</v>
-      </c>
-      <c r="C37" s="48">
-        <v>45475</v>
-      </c>
-      <c r="D37" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="E37" s="47">
-        <v>113</v>
-      </c>
-      <c r="F37" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="G37" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="H37" s="49">
-        <v>45705</v>
-      </c>
-      <c r="I37" s="8">
-        <v>45672</v>
-      </c>
-      <c r="J37" s="7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B38" s="47" t="s">
-        <v>8</v>
-      </c>
-      <c r="C38" s="48"/>
-      <c r="D38" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="E38" s="47">
-        <v>113</v>
-      </c>
-      <c r="F38" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="G38" s="56" t="s">
-        <v>44</v>
-      </c>
-      <c r="H38" s="49">
-        <v>45705</v>
       </c>
       <c r="I38" s="8">
         <v>45672</v>
       </c>
       <c r="J38" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" s="38" t="s">
+        <v>13</v>
+      </c>
+      <c r="B39" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="C39" s="40">
+        <v>45588</v>
+      </c>
+      <c r="D39" s="38" t="s">
+        <v>21</v>
+      </c>
+      <c r="E39" s="39"/>
+      <c r="F39" s="39"/>
+      <c r="G39" s="52" t="s">
+        <v>49</v>
+      </c>
+      <c r="H39" s="41">
+        <v>45625</v>
+      </c>
+      <c r="I39" s="8">
+        <v>45672</v>
+      </c>
+      <c r="J39" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B40" s="47" t="s">
+        <v>8</v>
+      </c>
+      <c r="C40" s="48">
+        <v>45475</v>
+      </c>
+      <c r="D40" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="E40" s="47">
+        <v>113</v>
+      </c>
+      <c r="F40" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="G40" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="H40" s="49">
+        <v>45705</v>
+      </c>
+      <c r="I40" s="8">
+        <v>45672</v>
+      </c>
+      <c r="J40" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B41" s="47" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41" s="48"/>
+      <c r="D41" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="E41" s="47">
+        <v>113</v>
+      </c>
+      <c r="F41" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="G41" s="56" t="s">
+        <v>44</v>
+      </c>
+      <c r="H41" s="49">
+        <v>45705</v>
+      </c>
+      <c r="I41" s="8">
+        <v>45672</v>
+      </c>
+      <c r="J41" s="7" t="s">
         <v>38</v>
       </c>
     </row>

--- a/mahkeme/2025-02-Dosya Listesi.xlsx
+++ b/mahkeme/2025-02-Dosya Listesi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\aaGitMe\yzhn\mahkeme\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAD3EE35-E64C-4AE2-9DA0-EBC49782A763}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{037C1B96-26E7-4278-9193-2C1CE4F0EDB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="64">
   <si>
     <t>Dosya Listesi</t>
   </si>
@@ -212,6 +212,27 @@
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">maddde 328 </t>
+  </si>
+  <si>
+    <t>ihtarname</t>
+  </si>
+  <si>
+    <t>icra emri</t>
+  </si>
+  <si>
+    <t>sulh hukuk</t>
+  </si>
+  <si>
+    <t>szl</t>
+  </si>
+  <si>
+    <t>dv</t>
+  </si>
+  <si>
+    <t>tt</t>
   </si>
 </sst>
 </file>
@@ -845,7 +866,7 @@
     <col min="7" max="7" width="12.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10" style="5" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8.7109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -861,7 +882,7 @@
       <c r="H1" s="9"/>
       <c r="I1" s="10"/>
       <c r="J1" s="12">
-        <v>45706</v>
+        <v>45708</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -913,6 +934,9 @@
       <c r="H3" s="6">
         <v>45705</v>
       </c>
+      <c r="J3" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="4"/>
@@ -936,6 +960,9 @@
       </c>
       <c r="H4" s="36">
         <v>45705</v>
+      </c>
+      <c r="J4" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -985,6 +1012,9 @@
       <c r="H7" s="6">
         <v>45630</v>
       </c>
+      <c r="J7" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="8" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
@@ -1001,6 +1031,9 @@
       <c r="H8" s="6">
         <v>45630</v>
       </c>
+      <c r="J8" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="9" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
@@ -1017,6 +1050,9 @@
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
       <c r="H9"/>
+      <c r="J9" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="10" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="14"/>
@@ -1055,6 +1091,9 @@
       <c r="H11" s="6">
         <v>45702</v>
       </c>
+      <c r="J11" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
@@ -1068,6 +1107,9 @@
       </c>
       <c r="H12" s="6">
         <v>45702</v>
+      </c>
+      <c r="J12" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
@@ -1161,6 +1203,9 @@
         <v>39</v>
       </c>
       <c r="H19" s="17"/>
+      <c r="J19" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="20" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="14"/>
@@ -1199,6 +1244,9 @@
         <v>45705</v>
       </c>
       <c r="I21" s="6"/>
+      <c r="J21" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="22" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4"/>
@@ -1214,6 +1262,9 @@
         <v>45705</v>
       </c>
       <c r="I22" s="6"/>
+      <c r="J22" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="23" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
@@ -1304,6 +1355,9 @@
       <c r="I28" s="41">
         <v>45691</v>
       </c>
+      <c r="J28" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="30"/>
@@ -1314,6 +1368,9 @@
       </c>
       <c r="F29" s="5"/>
       <c r="G29" s="5"/>
+      <c r="J29" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="30" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="14"/>
@@ -1405,7 +1462,9 @@
       <c r="G34" s="18"/>
       <c r="H34" s="17"/>
       <c r="I34" s="22"/>
-      <c r="J34" s="23"/>
+      <c r="J34" s="23" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>

--- a/mahkeme/2025-02-Dosya Listesi.xlsx
+++ b/mahkeme/2025-02-Dosya Listesi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\aaGitMe\yzhn\mahkeme\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{037C1B96-26E7-4278-9193-2C1CE4F0EDB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAF09768-4E5E-4331-8059-AB782AA62B5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="77">
   <si>
     <t>Dosya Listesi</t>
   </si>
@@ -134,9 +134,6 @@
   </si>
   <si>
     <t>2025-559</t>
-  </si>
-  <si>
-    <t>tahliye</t>
   </si>
   <si>
     <t>2025/25158</t>
@@ -214,36 +211,77 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">maddde 328 </t>
-  </si>
-  <si>
-    <t>ihtarname</t>
-  </si>
-  <si>
-    <t>icra emri</t>
-  </si>
-  <si>
-    <t>sulh hukuk</t>
-  </si>
-  <si>
-    <t>szl</t>
-  </si>
-  <si>
-    <t>dv</t>
-  </si>
-  <si>
-    <t>tt</t>
+    <t>taahhüt isteniyor ????</t>
+  </si>
+  <si>
+    <t>2 hafta</t>
+  </si>
+  <si>
+    <t>(14) dekont - (13) szl + tahh(??)</t>
+  </si>
+  <si>
+    <t>tebliğe çıkmış</t>
+  </si>
+  <si>
+    <t>ada-parsel - kira sözl -  damga vergisi</t>
+  </si>
+  <si>
+    <t>(14) dekont - (10) szl + taahhüt</t>
+  </si>
+  <si>
+    <t>(13) SZL + TAAHHÜT(???) - (9) tapu -(11) damga V</t>
+  </si>
+  <si>
+    <t>tebliğ + 2 hafta</t>
+  </si>
+  <si>
+    <t>deliller</t>
+  </si>
+  <si>
+    <t>(13) SZL + TAAHHÜT - (9) tapu -(11) damga V</t>
+  </si>
+  <si>
+    <t>tensip</t>
+  </si>
+  <si>
+    <t>2024/12482 icra</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> (10) szl </t>
+  </si>
+  <si>
+    <t>(13) SZL - (9) tapu -(11) damga V</t>
+  </si>
+  <si>
+    <t>tebliğ edlmş</t>
+  </si>
+  <si>
+    <t>davalı cevap</t>
+  </si>
+  <si>
+    <t>(3) 04.06.2024 tarihli ceza tutanağı</t>
+  </si>
+  <si>
+    <t>(4) yemin teklifi hmb</t>
+  </si>
+  <si>
+    <t>2025/559 dava dilekçesinde 2023 kirası talep ediliyor</t>
+  </si>
+  <si>
+    <t>2024/22053 te 2024-25 156000 takip başlatılmış</t>
+  </si>
+  <si>
+    <t>cevap</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yy;@"/>
-    <numFmt numFmtId="165" formatCode="[$-41F]d\ mmm\ yyyy;@"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -326,6 +364,13 @@
     <font>
       <sz val="11"/>
       <color theme="7" tint="0.79998168889431442"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="162"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="162"/>
@@ -448,7 +493,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -456,14 +501,12 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -541,6 +584,27 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="20" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -855,765 +919,1006 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J41"/>
+  <dimension ref="A1:I75"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="3" max="3" width="9.5703125" style="28" customWidth="1"/>
+    <col min="3" max="3" width="9.5703125" style="26" customWidth="1"/>
     <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="4.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="4" customWidth="1"/>
-    <col min="7" max="7" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10" style="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.7109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10" style="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
       <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="12">
-        <v>45708</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="9"/>
-      <c r="B2" s="33" t="s">
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+    </row>
+    <row r="2" spans="1:9" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="8"/>
+      <c r="B2" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="34" t="s">
+      <c r="C2" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="D2" s="33"/>
-      <c r="E2" s="13" t="s">
+      <c r="D2" s="31"/>
+      <c r="E2" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="F2" s="13"/>
+      <c r="F2" s="11"/>
       <c r="G2" s="33" t="s">
-        <v>40</v>
-      </c>
-      <c r="H2" s="33" t="s">
-        <v>52</v>
-      </c>
-      <c r="I2" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="J2" s="9"/>
-    </row>
-    <row r="3" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="H2" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="I2" s="31" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="27">
+      <c r="C3" s="25">
         <v>45475</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="59">
+      <c r="E3" s="57">
         <v>97</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="G3" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="H3" s="6">
+      <c r="H3" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="I3" s="6">
         <v>45705</v>
       </c>
-      <c r="J3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="4"/>
       <c r="B4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="27">
+      <c r="C4" s="25">
         <v>45604</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="59">
+      <c r="E4" s="57">
         <v>178</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="G4" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="H4" s="36">
+      <c r="H4" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="I4" s="34">
         <v>45705</v>
       </c>
-      <c r="J4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="28">
+      <c r="C5" s="26">
         <v>45704</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="26">
+        <v>45705</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H6" s="1"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="1"/>
+      <c r="C7" s="58"/>
+      <c r="D7" s="1"/>
+      <c r="H7" s="1"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="1"/>
+      <c r="C8" s="58" t="s">
+        <v>57</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H8" s="1"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="1"/>
+      <c r="C9" s="58">
+        <v>45712</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H9" s="1"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="1"/>
+      <c r="C10" s="58"/>
+      <c r="D10" s="1"/>
+      <c r="H10" s="1"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="1"/>
+      <c r="C11" s="61" t="s">
+        <v>63</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="H11" s="1"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="1"/>
+      <c r="C12" s="58"/>
+      <c r="D12" s="1"/>
+      <c r="H12" s="1"/>
+    </row>
+    <row r="13" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="1"/>
+      <c r="B13" s="51" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" s="52">
+        <v>45805</v>
+      </c>
+      <c r="D13" s="53">
+        <v>0.40972222222222227</v>
+      </c>
+      <c r="E13" t="s">
+        <v>56</v>
+      </c>
+      <c r="I13"/>
+    </row>
+    <row r="14" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="C14" s="58">
+        <v>45805</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="12"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="24"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="12"/>
+      <c r="I15" s="8"/>
+    </row>
+    <row r="16" spans="1:9" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C16" s="35">
+        <v>45588</v>
+      </c>
+      <c r="D16" s="57" t="s">
+        <v>21</v>
+      </c>
+      <c r="E16" s="3"/>
+      <c r="F16" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I16" s="6">
+        <v>45630</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="4"/>
+      <c r="B17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C17" s="25"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="4"/>
+      <c r="H17" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="I17" s="6">
+        <v>45630</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="4"/>
+      <c r="B18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" s="55">
+        <v>45704</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18"/>
+    </row>
+    <row r="19" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C19" s="26">
+        <v>45709</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H19" s="1"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="1"/>
+      <c r="C20" s="58" t="s">
+        <v>57</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="H20" s="1"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="1"/>
+      <c r="C21" s="58">
+        <v>45712</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H21" s="1"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="1"/>
+      <c r="C22" s="58"/>
+      <c r="D22" s="1"/>
+      <c r="H22" s="1"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="1"/>
+      <c r="C23" s="61" t="s">
+        <v>63</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="H23" s="1"/>
+    </row>
+    <row r="24" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="1"/>
+      <c r="B24" s="51" t="s">
+        <v>53</v>
+      </c>
+      <c r="C24" s="52">
+        <v>45805</v>
+      </c>
+      <c r="D24" s="59">
+        <v>0</v>
+      </c>
+      <c r="I24"/>
+    </row>
+    <row r="25" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="1"/>
+      <c r="C25" s="58">
+        <v>45805</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26"/>
+    </row>
+    <row r="27" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="12"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="24"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="12"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="12"/>
+      <c r="I27" s="8"/>
+    </row>
+    <row r="28" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="25">
+        <v>45475</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="57">
+        <v>214</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I28" s="6">
+        <v>45702</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" s="2"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="25"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="4"/>
+      <c r="H29" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="I29" s="6">
+        <v>45702</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" s="1"/>
+      <c r="B30" t="s">
+        <v>33</v>
+      </c>
+      <c r="C30" s="26">
+        <v>45704</v>
+      </c>
+      <c r="D30" s="1" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="14"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="26"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="14"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="9"/>
-    </row>
-    <row r="7" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" s="37">
+      <c r="H30" s="1"/>
+      <c r="I30"/>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" s="1"/>
+      <c r="B31" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C31" s="26">
+        <v>45705</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H31" s="1"/>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" s="1"/>
+      <c r="D32" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="H32" s="1"/>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" s="1"/>
+      <c r="C33" s="58" t="s">
+        <v>57</v>
+      </c>
+      <c r="D33" s="68" t="s">
+        <v>69</v>
+      </c>
+      <c r="H33" s="1"/>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34" s="1"/>
+      <c r="C34" s="58">
+        <v>45706</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H34" s="1"/>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" s="1"/>
+      <c r="C35" s="26">
+        <v>45711</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H35" s="1"/>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" s="1"/>
+      <c r="C36" s="61" t="s">
+        <v>71</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H36" s="1"/>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37" s="1"/>
+      <c r="C37" s="61"/>
+      <c r="D37" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H37" s="1"/>
+    </row>
+    <row r="38" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="1"/>
+      <c r="B38" s="51" t="s">
+        <v>53</v>
+      </c>
+      <c r="C38" s="52">
+        <v>45792</v>
+      </c>
+      <c r="D38" s="53">
+        <v>0.39930555555555558</v>
+      </c>
+      <c r="I38"/>
+    </row>
+    <row r="39" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="1"/>
+      <c r="C39" s="58">
+        <v>45792</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="H39" s="1"/>
+      <c r="I39"/>
+    </row>
+    <row r="41" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C41" s="56">
+        <v>45603</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E41" s="57">
+        <v>156</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G41" s="6"/>
+      <c r="H41" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I41" s="5">
+        <v>45705</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="4"/>
+      <c r="B42" s="3"/>
+      <c r="C42" s="25"/>
+      <c r="D42" s="4"/>
+      <c r="E42" s="3"/>
+      <c r="F42" s="4"/>
+      <c r="G42" s="6"/>
+      <c r="H42" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="I42" s="5">
+        <v>45705</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="1"/>
+      <c r="B43" t="s">
+        <v>37</v>
+      </c>
+      <c r="C43" s="55">
+        <v>45704</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F43" s="1"/>
+      <c r="H43" s="1"/>
+    </row>
+    <row r="44" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="1"/>
+      <c r="B44" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C44" s="26">
+        <v>45705</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H44" s="1"/>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A45" s="1"/>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A46" s="1"/>
+      <c r="C46" s="58" t="s">
+        <v>57</v>
+      </c>
+      <c r="D46" s="68" t="s">
+        <v>69</v>
+      </c>
+      <c r="G46" s="67"/>
+      <c r="H46" s="1"/>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A47" s="1"/>
+      <c r="C47" s="58">
+        <v>45706</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H47" s="1"/>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A48" s="1"/>
+      <c r="C48" s="26">
+        <v>45711</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H48" s="1"/>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A49" s="1"/>
+      <c r="B49" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C49" s="60"/>
+      <c r="D49" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H49" s="1"/>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A50" s="1"/>
+      <c r="D50" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="H50" s="1"/>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A51" s="1"/>
+      <c r="D51" s="1"/>
+      <c r="H51" s="1"/>
+    </row>
+    <row r="52" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B52" s="63" t="s">
+        <v>53</v>
+      </c>
+      <c r="C52" s="64">
+        <v>45792</v>
+      </c>
+      <c r="D52" s="65">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="I52"/>
+    </row>
+    <row r="53" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="B53" s="62"/>
+      <c r="C53" s="66">
+        <v>45792</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I53"/>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B54" s="62"/>
+      <c r="C54" s="66"/>
+      <c r="D54" s="1"/>
+      <c r="I54"/>
+    </row>
+    <row r="55" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="12"/>
+      <c r="B55" s="8"/>
+      <c r="C55" s="24"/>
+      <c r="D55" s="12"/>
+      <c r="E55" s="8"/>
+      <c r="F55" s="8"/>
+      <c r="G55" s="9"/>
+      <c r="H55" s="12"/>
+      <c r="I55" s="8"/>
+    </row>
+    <row r="56" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C56" s="25">
+        <v>45676</v>
+      </c>
+      <c r="D56" s="57" t="s">
+        <v>21</v>
+      </c>
+      <c r="E56" s="4"/>
+      <c r="F56" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A57" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C57" s="25"/>
+      <c r="D57" s="4"/>
+      <c r="E57" s="4"/>
+      <c r="F57" s="4"/>
+      <c r="H57" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I57" s="15"/>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A58" s="1"/>
+      <c r="D58" s="1"/>
+      <c r="E58" s="1"/>
+      <c r="F58" s="1"/>
+      <c r="H58" s="1"/>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B59" s="62"/>
+      <c r="C59" s="66"/>
+      <c r="D59" s="1"/>
+      <c r="I59"/>
+    </row>
+    <row r="60" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="12"/>
+      <c r="B60" s="8"/>
+      <c r="C60" s="24"/>
+      <c r="D60" s="12"/>
+      <c r="E60" s="8"/>
+      <c r="F60" s="8"/>
+      <c r="G60" s="9"/>
+      <c r="H60" s="12"/>
+      <c r="I60" s="8"/>
+    </row>
+    <row r="61" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="36" t="s">
+        <v>16</v>
+      </c>
+      <c r="B61" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="C61" s="38">
+        <v>45342</v>
+      </c>
+      <c r="D61" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="E61" s="37"/>
+      <c r="F61" s="48" t="s">
+        <v>26</v>
+      </c>
+      <c r="G61" s="39"/>
+      <c r="H61" s="37"/>
+      <c r="I61" s="39"/>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A62" s="36"/>
+      <c r="B62" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="C62" s="38">
+        <v>45537</v>
+      </c>
+      <c r="D62" s="36" t="s">
+        <v>23</v>
+      </c>
+      <c r="E62" s="37"/>
+      <c r="F62" s="49" t="s">
+        <v>19</v>
+      </c>
+      <c r="G62" s="39">
+        <v>45691</v>
+      </c>
+      <c r="H62" s="37"/>
+      <c r="I62" s="39"/>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A63" s="28"/>
+      <c r="B63" s="29"/>
+      <c r="C63" s="30"/>
+      <c r="D63" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="F63" s="5"/>
+      <c r="H63" s="5"/>
+    </row>
+    <row r="64" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="12"/>
+      <c r="B64" s="8"/>
+      <c r="C64" s="24"/>
+      <c r="D64" s="12"/>
+      <c r="E64" s="8"/>
+      <c r="F64" s="9"/>
+      <c r="G64" s="9"/>
+      <c r="H64" s="9"/>
+      <c r="I64" s="9"/>
+    </row>
+    <row r="65" spans="1:9" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="36" t="s">
+        <v>15</v>
+      </c>
+      <c r="B65" s="37" t="s">
+        <v>9</v>
+      </c>
+      <c r="C65" s="38">
+        <v>45438</v>
+      </c>
+      <c r="D65" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="E65" s="37">
+        <v>0</v>
+      </c>
+      <c r="F65" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="G65" s="39"/>
+      <c r="H65" s="37"/>
+      <c r="I65" s="39"/>
+    </row>
+    <row r="66" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A66" s="36"/>
+      <c r="B66" s="40" t="s">
+        <v>17</v>
+      </c>
+      <c r="C66" s="41">
+        <v>45486</v>
+      </c>
+      <c r="D66" s="36" t="s">
+        <v>25</v>
+      </c>
+      <c r="E66" s="37"/>
+      <c r="F66" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="G66" s="43">
         <v>45588</v>
       </c>
-      <c r="D7" s="59" t="s">
+      <c r="H66" s="37"/>
+      <c r="I66" s="39"/>
+    </row>
+    <row r="67" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A67" s="36"/>
+      <c r="B67" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="C67" s="41">
+        <v>45590</v>
+      </c>
+      <c r="D67" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="E67" s="36"/>
+      <c r="F67" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="G67" s="43">
+        <v>45688</v>
+      </c>
+      <c r="H67" s="37"/>
+      <c r="I67" s="39"/>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A68" s="17"/>
+      <c r="B68" s="18"/>
+      <c r="C68" s="44"/>
+      <c r="D68" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="E68" s="18"/>
+      <c r="F68" s="19"/>
+      <c r="G68" s="20"/>
+      <c r="H68" s="16"/>
+      <c r="I68" s="15"/>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A69" s="1"/>
+      <c r="B69" s="21"/>
+      <c r="C69" s="27"/>
+      <c r="D69" s="1"/>
+      <c r="E69" s="21"/>
+      <c r="F69" s="23"/>
+      <c r="G69" s="22"/>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A70" s="1"/>
+      <c r="B70" s="21"/>
+      <c r="C70" s="27"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="21"/>
+      <c r="F70" s="23"/>
+      <c r="G70" s="22"/>
+    </row>
+    <row r="71" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="8"/>
+      <c r="B71" s="8"/>
+      <c r="C71" s="24"/>
+      <c r="D71" s="8"/>
+      <c r="E71" s="8"/>
+      <c r="F71" s="8"/>
+      <c r="G71" s="9"/>
+      <c r="H71" s="8"/>
+      <c r="I71" s="9"/>
+    </row>
+    <row r="72" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="36" t="s">
+        <v>13</v>
+      </c>
+      <c r="B72" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="C72" s="38">
+        <v>45588</v>
+      </c>
+      <c r="D72" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="4" t="s">
+      <c r="E72" s="37"/>
+      <c r="F72" s="37"/>
+      <c r="G72" s="7">
+        <v>45672</v>
+      </c>
+      <c r="H72" s="36" t="s">
+        <v>45</v>
+      </c>
+      <c r="I72" s="39">
+        <v>45625</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A73" s="36" t="s">
+        <v>13</v>
+      </c>
+      <c r="B73" s="37" t="s">
+        <v>5</v>
+      </c>
+      <c r="C73" s="38">
+        <v>45588</v>
+      </c>
+      <c r="D73" s="36" t="s">
+        <v>21</v>
+      </c>
+      <c r="E73" s="37"/>
+      <c r="F73" s="37"/>
+      <c r="G73" s="7">
+        <v>45672</v>
+      </c>
+      <c r="H73" s="50" t="s">
+        <v>48</v>
+      </c>
+      <c r="I73" s="39">
+        <v>45625</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A74" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B74" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="C74" s="46">
+        <v>45475</v>
+      </c>
+      <c r="D74" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="E74" s="45">
+        <v>113</v>
+      </c>
+      <c r="F74" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="G7" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="H7" s="6">
-        <v>45630</v>
-      </c>
-      <c r="J7" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="4"/>
-      <c r="B8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C8" s="27"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="H8" s="6">
-        <v>45630</v>
-      </c>
-      <c r="J8" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="4"/>
-      <c r="B9" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" s="57">
-        <v>45704</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9"/>
-      <c r="J9" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="14"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="26"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="9"/>
-    </row>
-    <row r="11" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="27">
-        <v>45475</v>
-      </c>
-      <c r="D11" s="4" t="s">
+      <c r="G74" s="7">
+        <v>45672</v>
+      </c>
+      <c r="H74" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="I74" s="47">
+        <v>45705</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A75" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B75" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="C75" s="46"/>
+      <c r="D75" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="59">
-        <v>214</v>
-      </c>
-      <c r="F11" s="4" t="s">
+      <c r="E75" s="45">
+        <v>113</v>
+      </c>
+      <c r="F75" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="G11" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="H11" s="6">
-        <v>45702</v>
-      </c>
-      <c r="J11" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="2"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="H12" s="6">
-        <v>45702</v>
-      </c>
-      <c r="J12" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
-      <c r="B13" t="s">
-        <v>33</v>
-      </c>
-      <c r="C13" s="28">
-        <v>45704</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="G13" s="1"/>
-      <c r="H13"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
-      <c r="C14" s="28">
+      <c r="G75" s="7">
+        <v>45672</v>
+      </c>
+      <c r="H75" s="54" t="s">
+        <v>43</v>
+      </c>
+      <c r="I75" s="47">
         <v>45705</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="G14" s="1"/>
-    </row>
-    <row r="15" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="1"/>
-      <c r="B15" s="53" t="s">
-        <v>54</v>
-      </c>
-      <c r="C15" s="54">
-        <v>45792</v>
-      </c>
-      <c r="D15" s="55">
-        <v>0.39930555555555558</v>
-      </c>
-      <c r="H15"/>
-    </row>
-    <row r="16" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16"/>
-    </row>
-    <row r="17" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="14"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="26"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="10"/>
-      <c r="J17" s="9"/>
-    </row>
-    <row r="18" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C18" s="27">
-        <v>45676</v>
-      </c>
-      <c r="D18" s="59" t="s">
-        <v>21</v>
-      </c>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C19" s="27"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="H19" s="17"/>
-      <c r="J19" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="14"/>
-      <c r="B20" s="9"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="10"/>
-      <c r="J20" s="9"/>
-    </row>
-    <row r="21" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C21" s="58">
-        <v>45603</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E21" s="59">
-        <v>198</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="H21" s="5">
-        <v>45705</v>
-      </c>
-      <c r="I21" s="6"/>
-      <c r="J21" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="4"/>
-      <c r="B22" s="3"/>
-      <c r="C22" s="27"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="H22" s="5">
-        <v>45705</v>
-      </c>
-      <c r="I22" s="6"/>
-      <c r="J22" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="1"/>
-      <c r="B23" t="s">
-        <v>37</v>
-      </c>
-      <c r="C23" s="57">
-        <v>45704</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-    </row>
-    <row r="24" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="1"/>
-      <c r="C24" s="28">
-        <v>45705</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="G24" s="1"/>
-    </row>
-    <row r="25" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="53" t="s">
-        <v>54</v>
-      </c>
-      <c r="C25" s="54">
-        <v>45792</v>
-      </c>
-      <c r="D25" s="55">
-        <v>0.39583333333333331</v>
-      </c>
-      <c r="H25"/>
-    </row>
-    <row r="26" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="14"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="26"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="10"/>
-      <c r="J26" s="9"/>
-    </row>
-    <row r="27" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="38" t="s">
-        <v>16</v>
-      </c>
-      <c r="B27" s="39" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="40">
-        <v>45342</v>
-      </c>
-      <c r="D27" s="38" t="s">
-        <v>14</v>
-      </c>
-      <c r="E27" s="39"/>
-      <c r="F27" s="50" t="s">
-        <v>26</v>
-      </c>
-      <c r="G27" s="39"/>
-      <c r="H27" s="41"/>
-      <c r="I27" s="41"/>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="38"/>
-      <c r="B28" s="38" t="s">
-        <v>24</v>
-      </c>
-      <c r="C28" s="40">
-        <v>45537</v>
-      </c>
-      <c r="D28" s="38" t="s">
-        <v>23</v>
-      </c>
-      <c r="E28" s="39"/>
-      <c r="F28" s="51" t="s">
-        <v>19</v>
-      </c>
-      <c r="G28" s="39"/>
-      <c r="H28" s="41"/>
-      <c r="I28" s="41">
-        <v>45691</v>
-      </c>
-      <c r="J28" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="30"/>
-      <c r="B29" s="31"/>
-      <c r="C29" s="32"/>
-      <c r="D29" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="F29" s="5"/>
-      <c r="G29" s="5"/>
-      <c r="J29" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="14"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="26"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="10"/>
-      <c r="G30" s="10"/>
-      <c r="H30" s="10"/>
-      <c r="I30" s="10"/>
-      <c r="J30" s="9"/>
-    </row>
-    <row r="31" spans="1:10" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="B31" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="C31" s="40">
-        <v>45438</v>
-      </c>
-      <c r="D31" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="39">
-        <v>0</v>
-      </c>
-      <c r="F31" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="G31" s="39"/>
-      <c r="H31" s="41"/>
-      <c r="I31" s="41"/>
-    </row>
-    <row r="32" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A32" s="38"/>
-      <c r="B32" s="42" t="s">
-        <v>17</v>
-      </c>
-      <c r="C32" s="43">
-        <v>45486</v>
-      </c>
-      <c r="D32" s="38" t="s">
-        <v>25</v>
-      </c>
-      <c r="E32" s="39"/>
-      <c r="F32" s="44" t="s">
-        <v>27</v>
-      </c>
-      <c r="G32" s="39"/>
-      <c r="H32" s="41"/>
-      <c r="I32" s="45">
-        <v>45588</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A33" s="38"/>
-      <c r="B33" s="42" t="s">
-        <v>18</v>
-      </c>
-      <c r="C33" s="43">
-        <v>45590</v>
-      </c>
-      <c r="D33" s="38" t="s">
-        <v>22</v>
-      </c>
-      <c r="E33" s="38"/>
-      <c r="F33" s="44" t="s">
-        <v>27</v>
-      </c>
-      <c r="G33" s="39"/>
-      <c r="H33" s="41"/>
-      <c r="I33" s="45">
-        <v>45688</v>
-      </c>
-      <c r="J33" s="1"/>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="19"/>
-      <c r="B34" s="20"/>
-      <c r="C34" s="46"/>
-      <c r="D34" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="E34" s="20"/>
-      <c r="F34" s="21"/>
-      <c r="G34" s="18"/>
-      <c r="H34" s="17"/>
-      <c r="I34" s="22"/>
-      <c r="J34" s="23" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" s="1"/>
-      <c r="B35" s="23"/>
-      <c r="C35" s="29"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="23"/>
-      <c r="F35" s="25"/>
-      <c r="I35" s="24"/>
-      <c r="J35" s="23"/>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="1"/>
-      <c r="B36" s="23"/>
-      <c r="C36" s="29"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="23"/>
-      <c r="F36" s="25"/>
-      <c r="I36" s="24"/>
-      <c r="J36" s="23"/>
-    </row>
-    <row r="37" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="9"/>
-      <c r="B37" s="9"/>
-      <c r="C37" s="26"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="9"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="9"/>
-      <c r="H37" s="10"/>
-      <c r="I37" s="10"/>
-      <c r="J37" s="9"/>
-    </row>
-    <row r="38" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="38" t="s">
-        <v>13</v>
-      </c>
-      <c r="B38" s="39" t="s">
-        <v>5</v>
-      </c>
-      <c r="C38" s="40">
-        <v>45588</v>
-      </c>
-      <c r="D38" s="38" t="s">
-        <v>21</v>
-      </c>
-      <c r="E38" s="39"/>
-      <c r="F38" s="39"/>
-      <c r="G38" s="38" t="s">
-        <v>46</v>
-      </c>
-      <c r="H38" s="41">
-        <v>45625</v>
-      </c>
-      <c r="I38" s="8">
-        <v>45672</v>
-      </c>
-      <c r="J38" s="7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A39" s="38" t="s">
-        <v>13</v>
-      </c>
-      <c r="B39" s="39" t="s">
-        <v>5</v>
-      </c>
-      <c r="C39" s="40">
-        <v>45588</v>
-      </c>
-      <c r="D39" s="38" t="s">
-        <v>21</v>
-      </c>
-      <c r="E39" s="39"/>
-      <c r="F39" s="39"/>
-      <c r="G39" s="52" t="s">
-        <v>49</v>
-      </c>
-      <c r="H39" s="41">
-        <v>45625</v>
-      </c>
-      <c r="I39" s="8">
-        <v>45672</v>
-      </c>
-      <c r="J39" s="7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A40" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B40" s="47" t="s">
-        <v>8</v>
-      </c>
-      <c r="C40" s="48">
-        <v>45475</v>
-      </c>
-      <c r="D40" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="E40" s="47">
-        <v>113</v>
-      </c>
-      <c r="F40" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="G40" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="H40" s="49">
-        <v>45705</v>
-      </c>
-      <c r="I40" s="8">
-        <v>45672</v>
-      </c>
-      <c r="J40" s="7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A41" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B41" s="47" t="s">
-        <v>8</v>
-      </c>
-      <c r="C41" s="48"/>
-      <c r="D41" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="E41" s="47">
-        <v>113</v>
-      </c>
-      <c r="F41" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="G41" s="56" t="s">
-        <v>44</v>
-      </c>
-      <c r="H41" s="49">
-        <v>45705</v>
-      </c>
-      <c r="I41" s="8">
-        <v>45672</v>
-      </c>
-      <c r="J41" s="7" t="s">
-        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/mahkeme/2025-02-Dosya Listesi.xlsx
+++ b/mahkeme/2025-02-Dosya Listesi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\aaGitMe\yzhn\mahkeme\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAF09768-4E5E-4331-8059-AB782AA62B5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE98D4A3-186A-4780-A176-B994C7F82F09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="82">
   <si>
     <t>Dosya Listesi</t>
   </si>
@@ -272,6 +272,21 @@
   </si>
   <si>
     <t>cevap</t>
+  </si>
+  <si>
+    <t>tebliğ edildi</t>
+  </si>
+  <si>
+    <t>BAMa bşvuru son tarih</t>
+  </si>
+  <si>
+    <t>tebliğ</t>
+  </si>
+  <si>
+    <t>AliDemirel</t>
+  </si>
+  <si>
+    <t>2025/29356</t>
   </si>
 </sst>
 </file>
@@ -403,12 +418,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -449,8 +458,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -489,11 +504,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -511,14 +563,14 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -534,11 +586,6 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -548,35 +595,35 @@
     <xf numFmtId="164" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="20" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -596,7 +643,7 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="20" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -605,6 +652,39 @@
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="12" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="12" fillId="12" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="12" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="12" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="12" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="12" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="12" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="12" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -919,7 +999,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I75"/>
+  <dimension ref="A1:I86"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -947,977 +1027,1070 @@
     </row>
     <row r="2" spans="1:9" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="8"/>
-      <c r="B2" s="31" t="s">
+      <c r="B2" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="32" t="s">
+      <c r="C2" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="D2" s="31"/>
+      <c r="D2" s="28"/>
       <c r="E2" s="11" t="s">
         <v>28</v>
       </c>
       <c r="F2" s="11"/>
-      <c r="G2" s="33" t="s">
+      <c r="G2" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="H2" s="31" t="s">
+      <c r="H2" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="I2" s="31" t="s">
+      <c r="I2" s="28" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="83"/>
+      <c r="I3"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="83" t="s">
+        <v>80</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="I4" s="84">
+        <v>45712</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="83"/>
+      <c r="I5"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="83"/>
+      <c r="I6"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="83"/>
+      <c r="I7"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="83"/>
+      <c r="I8"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="83"/>
+      <c r="I9"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B11" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="25">
+      <c r="C11" s="25">
         <v>45475</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D11" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="57">
+      <c r="E11" s="54">
         <v>97</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F11" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H11" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="I3" s="6">
+      <c r="I11" s="6">
         <v>45705</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4" t="s">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="4"/>
+      <c r="B12" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="25">
+      <c r="C12" s="25">
         <v>45604</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D12" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="57">
+      <c r="E12" s="54">
         <v>178</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F12" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="H4" s="14" t="s">
+      <c r="H12" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="I4" s="34">
+      <c r="I12" s="31">
         <v>45705</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="1"/>
-      <c r="B5" t="s">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="1"/>
+      <c r="B13" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="26">
+      <c r="C13" s="26">
         <v>45704</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D13" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1" t="s">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C6" s="26">
+      <c r="C14" s="26">
         <v>45705</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D14" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="H6" s="1"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="1"/>
-      <c r="C7" s="58"/>
-      <c r="D7" s="1"/>
-      <c r="H7" s="1"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="1"/>
-      <c r="C8" s="58" t="s">
+      <c r="H14" s="1"/>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="1"/>
+      <c r="C15" s="55"/>
+      <c r="D15" s="1"/>
+      <c r="H15" s="1"/>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="1"/>
+      <c r="C16" s="55" t="s">
         <v>57</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D16" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="H8" s="1"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="1"/>
-      <c r="C9" s="58">
+      <c r="H16" s="1"/>
+    </row>
+    <row r="17" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="1"/>
+      <c r="C17" s="55">
         <v>45712</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D17" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="H9" s="1"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="1"/>
-      <c r="C10" s="58"/>
-      <c r="D10" s="1"/>
-      <c r="H10" s="1"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="1"/>
-      <c r="C11" s="61" t="s">
+      <c r="H17" s="1"/>
+    </row>
+    <row r="18" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="1"/>
+      <c r="C18" s="77">
+        <v>45717</v>
+      </c>
+      <c r="D18" s="78" t="s">
+        <v>79</v>
+      </c>
+      <c r="E18" s="79" t="s">
         <v>63</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="F18" s="78"/>
+      <c r="G18" s="80"/>
+      <c r="H18" s="78" t="s">
         <v>64</v>
       </c>
-      <c r="H11" s="1"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="1"/>
-      <c r="C12" s="58"/>
-      <c r="D12" s="1"/>
-      <c r="H12" s="1"/>
-    </row>
-    <row r="13" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="1"/>
-      <c r="B13" s="51" t="s">
-        <v>53</v>
-      </c>
-      <c r="C13" s="52">
-        <v>45805</v>
-      </c>
-      <c r="D13" s="53">
-        <v>0.40972222222222227</v>
-      </c>
-      <c r="E13" t="s">
-        <v>56</v>
-      </c>
-      <c r="I13"/>
-    </row>
-    <row r="14" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
-      <c r="C14" s="58">
-        <v>45805</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="12"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="24"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="12"/>
-      <c r="I15" s="8"/>
-    </row>
-    <row r="16" spans="1:9" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C16" s="35">
-        <v>45588</v>
-      </c>
-      <c r="D16" s="57" t="s">
-        <v>21</v>
-      </c>
-      <c r="E16" s="3"/>
-      <c r="F16" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="I16" s="6">
-        <v>45630</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="4"/>
-      <c r="B17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C17" s="25"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="4"/>
-      <c r="H17" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="I17" s="6">
-        <v>45630</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="4"/>
-      <c r="B18" t="s">
-        <v>35</v>
-      </c>
-      <c r="C18" s="55">
-        <v>45704</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18"/>
-    </row>
-    <row r="19" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="I18" s="81"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
-      <c r="B19" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C19" s="26">
-        <v>45709</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>60</v>
-      </c>
+      <c r="C19" s="58"/>
+      <c r="D19" s="1"/>
       <c r="H19" s="1"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
-      <c r="C20" s="58" t="s">
-        <v>57</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>65</v>
-      </c>
+      <c r="C20" s="55"/>
+      <c r="D20" s="1"/>
       <c r="H20" s="1"/>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
-      <c r="C21" s="58">
-        <v>45712</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="H21" s="1"/>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B21" s="48" t="s">
+        <v>53</v>
+      </c>
+      <c r="C21" s="49">
+        <v>45805</v>
+      </c>
+      <c r="D21" s="50">
+        <v>0.40972222222222227</v>
+      </c>
+      <c r="E21" t="s">
+        <v>56</v>
+      </c>
+      <c r="I21"/>
+    </row>
+    <row r="22" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
-      <c r="C22" s="58"/>
-      <c r="D22" s="1"/>
-      <c r="H22" s="1"/>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="1"/>
-      <c r="C23" s="61" t="s">
-        <v>63</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H23" s="1"/>
-    </row>
-    <row r="24" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="1"/>
-      <c r="B24" s="51" t="s">
-        <v>53</v>
-      </c>
-      <c r="C24" s="52">
+      <c r="C22" s="55">
         <v>45805</v>
       </c>
-      <c r="D24" s="59">
-        <v>0</v>
-      </c>
-      <c r="I24"/>
+      <c r="D22" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="12"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="24"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="9"/>
+      <c r="H23" s="12"/>
+      <c r="I23" s="8"/>
+    </row>
+    <row r="24" spans="1:9" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C24" s="32">
+        <v>45588</v>
+      </c>
+      <c r="D24" s="54" t="s">
+        <v>21</v>
+      </c>
+      <c r="E24" s="3"/>
+      <c r="F24" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I24" s="6">
+        <v>45630</v>
+      </c>
     </row>
     <row r="25" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="1"/>
-      <c r="C25" s="58">
-        <v>45805</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="1"/>
-      <c r="D26" s="1"/>
+      <c r="A25" s="4"/>
+      <c r="B25" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C25" s="25"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="4"/>
+      <c r="H25" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="I25" s="6">
+        <v>45630</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="4"/>
+      <c r="B26" t="s">
+        <v>35</v>
+      </c>
+      <c r="C26" s="52">
+        <v>45704</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>23</v>
+      </c>
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
       <c r="H26" s="1"/>
       <c r="I26"/>
     </row>
-    <row r="27" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="12"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="24"/>
-      <c r="D27" s="12"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="12"/>
-      <c r="I27" s="8"/>
-    </row>
-    <row r="28" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28" s="25">
-        <v>45475</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="57">
-        <v>214</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H28" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="I28" s="6">
-        <v>45702</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="2"/>
-      <c r="B29" s="3"/>
-      <c r="C29" s="25"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="3"/>
-      <c r="F29" s="4"/>
-      <c r="H29" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="I29" s="6">
-        <v>45702</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="1"/>
+      <c r="B27" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C27" s="26">
+        <v>45709</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H27" s="1"/>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" s="1"/>
+      <c r="C28" s="55" t="s">
+        <v>57</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="H28" s="1"/>
+    </row>
+    <row r="29" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="1"/>
+      <c r="C29" s="55">
+        <v>45712</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H29" s="1"/>
+    </row>
+    <row r="30" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
-      <c r="B30" t="s">
-        <v>33</v>
-      </c>
-      <c r="C30" s="26">
-        <v>45704</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="H30" s="1"/>
-      <c r="I30"/>
+      <c r="C30" s="77">
+        <v>45717</v>
+      </c>
+      <c r="D30" s="78" t="s">
+        <v>79</v>
+      </c>
+      <c r="E30" s="79" t="s">
+        <v>63</v>
+      </c>
+      <c r="F30" s="78"/>
+      <c r="G30" s="80"/>
+      <c r="H30" s="78" t="s">
+        <v>64</v>
+      </c>
+      <c r="I30" s="81"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
-      <c r="B31" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C31" s="26">
-        <v>45705</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="H31" s="1"/>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
-      <c r="D32" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="H32" s="1"/>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B32" s="48" t="s">
+        <v>53</v>
+      </c>
+      <c r="C32" s="49">
+        <v>45805</v>
+      </c>
+      <c r="D32" s="56">
+        <v>0</v>
+      </c>
+      <c r="I32"/>
+    </row>
+    <row r="33" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
-      <c r="C33" s="58" t="s">
-        <v>57</v>
-      </c>
-      <c r="D33" s="68" t="s">
-        <v>69</v>
-      </c>
-      <c r="H33" s="1"/>
+      <c r="C33" s="55">
+        <v>45805</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
-      <c r="C34" s="58">
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34"/>
+    </row>
+    <row r="35" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="12"/>
+      <c r="B35" s="8"/>
+      <c r="C35" s="24"/>
+      <c r="D35" s="12"/>
+      <c r="E35" s="12"/>
+      <c r="F35" s="12"/>
+      <c r="G35" s="9"/>
+      <c r="H35" s="12"/>
+      <c r="I35" s="8"/>
+    </row>
+    <row r="36" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="25">
+        <v>45475</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E36" s="54">
+        <v>214</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I36" s="6">
+        <v>45702</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37" s="2"/>
+      <c r="B37" s="3"/>
+      <c r="C37" s="25"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="4"/>
+      <c r="H37" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="I37" s="6">
+        <v>45702</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38" s="1"/>
+      <c r="B38" t="s">
+        <v>33</v>
+      </c>
+      <c r="C38" s="26">
+        <v>45704</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="H38" s="1"/>
+      <c r="I38"/>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39" s="1"/>
+      <c r="B39" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C39" s="26">
+        <v>45705</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H39" s="1"/>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A40" s="1"/>
+      <c r="D40" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="H40" s="1"/>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A41" s="1"/>
+      <c r="C41" s="55" t="s">
+        <v>57</v>
+      </c>
+      <c r="D41" s="65" t="s">
+        <v>69</v>
+      </c>
+      <c r="H41" s="1"/>
+    </row>
+    <row r="42" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="1"/>
+      <c r="C42" s="55">
         <v>45706</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="D42" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="H34" s="1"/>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="1"/>
-      <c r="C35" s="26">
-        <v>45711</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="H35" s="1"/>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="1"/>
-      <c r="C36" s="61" t="s">
-        <v>71</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H36" s="1"/>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" s="1"/>
-      <c r="C37" s="61"/>
-      <c r="D37" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="H37" s="1"/>
-    </row>
-    <row r="38" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="1"/>
-      <c r="B38" s="51" t="s">
-        <v>53</v>
-      </c>
-      <c r="C38" s="52">
-        <v>45792</v>
-      </c>
-      <c r="D38" s="53">
-        <v>0.39930555555555558</v>
-      </c>
-      <c r="I38"/>
-    </row>
-    <row r="39" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="1"/>
-      <c r="C39" s="58">
-        <v>45792</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="H39" s="1"/>
-      <c r="I39"/>
-    </row>
-    <row r="41" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C41" s="56">
-        <v>45603</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E41" s="57">
-        <v>156</v>
-      </c>
-      <c r="F41" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G41" s="6"/>
-      <c r="H41" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I41" s="5">
-        <v>45705</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="4"/>
-      <c r="B42" s="3"/>
-      <c r="C42" s="25"/>
-      <c r="D42" s="4"/>
-      <c r="E42" s="3"/>
-      <c r="F42" s="4"/>
-      <c r="G42" s="6"/>
-      <c r="H42" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="I42" s="5">
-        <v>45705</v>
-      </c>
+      <c r="H42" s="1"/>
     </row>
     <row r="43" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
-      <c r="B43" t="s">
-        <v>37</v>
-      </c>
-      <c r="C43" s="55">
-        <v>45704</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F43" s="1"/>
-      <c r="H43" s="1"/>
-    </row>
-    <row r="44" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="C43" s="82">
+        <v>45711</v>
+      </c>
+      <c r="D43" s="78" t="s">
+        <v>70</v>
+      </c>
+      <c r="E43" s="78"/>
+      <c r="F43" s="78"/>
+      <c r="G43" s="80"/>
+      <c r="H43" s="78"/>
+      <c r="I43" s="81"/>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
-      <c r="B44" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C44" s="26">
-        <v>45705</v>
+      <c r="C44" s="58" t="s">
+        <v>71</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="H44" s="1"/>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="C45" s="58"/>
+      <c r="D45" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H45" s="1"/>
+    </row>
+    <row r="46" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1"/>
-      <c r="C46" s="58" t="s">
+      <c r="B46" s="48" t="s">
+        <v>53</v>
+      </c>
+      <c r="C46" s="49">
+        <v>45792</v>
+      </c>
+      <c r="D46" s="50">
+        <v>0.39930555555555558</v>
+      </c>
+      <c r="I46"/>
+    </row>
+    <row r="47" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="1"/>
+      <c r="C47" s="55">
+        <v>45792</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="H47" s="1"/>
+      <c r="I47"/>
+    </row>
+    <row r="49" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C49" s="53">
+        <v>45603</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E49" s="54">
+        <v>156</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G49" s="6"/>
+      <c r="H49" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I49" s="5">
+        <v>45705</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="4"/>
+      <c r="B50" s="3"/>
+      <c r="C50" s="25"/>
+      <c r="D50" s="4"/>
+      <c r="E50" s="3"/>
+      <c r="F50" s="4"/>
+      <c r="G50" s="6"/>
+      <c r="H50" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="I50" s="5">
+        <v>45705</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="1"/>
+      <c r="B51" t="s">
+        <v>37</v>
+      </c>
+      <c r="C51" s="52">
+        <v>45704</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F51" s="1"/>
+      <c r="H51" s="1"/>
+    </row>
+    <row r="52" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="1"/>
+      <c r="B52" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C52" s="26">
+        <v>45705</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H52" s="1"/>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A53" s="1"/>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A54" s="1"/>
+      <c r="C54" s="55" t="s">
         <v>57</v>
       </c>
-      <c r="D46" s="68" t="s">
+      <c r="D54" s="65" t="s">
         <v>69</v>
       </c>
-      <c r="G46" s="67"/>
-      <c r="H46" s="1"/>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A47" s="1"/>
-      <c r="C47" s="58">
+      <c r="G54" s="64"/>
+      <c r="H54" s="1"/>
+    </row>
+    <row r="55" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="1"/>
+      <c r="C55" s="55">
         <v>45706</v>
       </c>
-      <c r="D47" s="1" t="s">
+      <c r="D55" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="H47" s="1"/>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A48" s="1"/>
-      <c r="C48" s="26">
+      <c r="H55" s="1"/>
+    </row>
+    <row r="56" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="1"/>
+      <c r="C56" s="82">
         <v>45711</v>
       </c>
-      <c r="D48" s="1" t="s">
+      <c r="D56" s="78" t="s">
         <v>70</v>
       </c>
-      <c r="H48" s="1"/>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A49" s="1"/>
-      <c r="B49" s="1" t="s">
+      <c r="E56" s="78"/>
+      <c r="F56" s="78"/>
+      <c r="G56" s="80"/>
+      <c r="H56" s="78"/>
+      <c r="I56" s="81"/>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A57" s="1"/>
+      <c r="B57" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C49" s="60"/>
-      <c r="D49" s="1" t="s">
+      <c r="C57" s="57"/>
+      <c r="D57" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H49" s="1"/>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A50" s="1"/>
-      <c r="D50" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="H50" s="1"/>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A51" s="1"/>
-      <c r="D51" s="1"/>
-      <c r="H51" s="1"/>
-    </row>
-    <row r="52" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B52" s="63" t="s">
-        <v>53</v>
-      </c>
-      <c r="C52" s="64">
-        <v>45792</v>
-      </c>
-      <c r="D52" s="65">
-        <v>0.39583333333333331</v>
-      </c>
-      <c r="I52"/>
-    </row>
-    <row r="53" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="62"/>
-      <c r="C53" s="66">
-        <v>45792</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="I53"/>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B54" s="62"/>
-      <c r="C54" s="66"/>
-      <c r="D54" s="1"/>
-      <c r="I54"/>
-    </row>
-    <row r="55" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="12"/>
-      <c r="B55" s="8"/>
-      <c r="C55" s="24"/>
-      <c r="D55" s="12"/>
-      <c r="E55" s="8"/>
-      <c r="F55" s="8"/>
-      <c r="G55" s="9"/>
-      <c r="H55" s="12"/>
-      <c r="I55" s="8"/>
-    </row>
-    <row r="56" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C56" s="25">
-        <v>45676</v>
-      </c>
-      <c r="D56" s="57" t="s">
-        <v>21</v>
-      </c>
-      <c r="E56" s="4"/>
-      <c r="F56" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H56" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A57" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C57" s="25"/>
-      <c r="D57" s="4"/>
-      <c r="E57" s="4"/>
-      <c r="F57" s="4"/>
-      <c r="H57" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="I57" s="15"/>
+      <c r="H57" s="1"/>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="1"/>
-      <c r="D58" s="1"/>
-      <c r="E58" s="1"/>
-      <c r="F58" s="1"/>
+      <c r="D58" s="1" t="s">
+        <v>74</v>
+      </c>
       <c r="H58" s="1"/>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B59" s="62"/>
-      <c r="C59" s="66"/>
+      <c r="A59" s="1"/>
       <c r="D59" s="1"/>
-      <c r="I59"/>
+      <c r="H59" s="1"/>
     </row>
     <row r="60" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="12"/>
-      <c r="B60" s="8"/>
-      <c r="C60" s="24"/>
-      <c r="D60" s="12"/>
-      <c r="E60" s="8"/>
-      <c r="F60" s="8"/>
-      <c r="G60" s="9"/>
-      <c r="H60" s="12"/>
-      <c r="I60" s="8"/>
+      <c r="B60" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="C60" s="61">
+        <v>45792</v>
+      </c>
+      <c r="D60" s="62">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="I60"/>
     </row>
     <row r="61" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="36" t="s">
+      <c r="B61" s="59"/>
+      <c r="C61" s="63">
+        <v>45792</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I61"/>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B62" s="59"/>
+      <c r="C62" s="63"/>
+      <c r="D62" s="1"/>
+      <c r="I62"/>
+    </row>
+    <row r="63" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="12"/>
+      <c r="B63" s="8"/>
+      <c r="C63" s="24"/>
+      <c r="D63" s="12"/>
+      <c r="E63" s="8"/>
+      <c r="F63" s="8"/>
+      <c r="G63" s="9"/>
+      <c r="H63" s="12"/>
+      <c r="I63" s="8"/>
+    </row>
+    <row r="64" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C64" s="25">
+        <v>45676</v>
+      </c>
+      <c r="D64" s="54" t="s">
+        <v>21</v>
+      </c>
+      <c r="E64" s="4"/>
+      <c r="F64" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A65" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C65" s="25"/>
+      <c r="D65" s="4"/>
+      <c r="E65" s="4"/>
+      <c r="F65" s="4"/>
+      <c r="H65" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I65" s="15">
+        <v>45714</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="H66" s="1"/>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B67" s="59"/>
+      <c r="C67" s="63"/>
+      <c r="D67" s="1"/>
+      <c r="I67"/>
+    </row>
+    <row r="68" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="12"/>
+      <c r="B68" s="8"/>
+      <c r="C68" s="24"/>
+      <c r="D68" s="12"/>
+      <c r="E68" s="8"/>
+      <c r="F68" s="8"/>
+      <c r="G68" s="9"/>
+      <c r="H68" s="12"/>
+      <c r="I68" s="8"/>
+    </row>
+    <row r="69" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="B61" s="37" t="s">
+      <c r="B69" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="C61" s="38">
+      <c r="C69" s="35">
         <v>45342</v>
       </c>
-      <c r="D61" s="36" t="s">
+      <c r="D69" s="33" t="s">
         <v>14</v>
       </c>
-      <c r="E61" s="37"/>
-      <c r="F61" s="48" t="s">
+      <c r="E69" s="34"/>
+      <c r="F69" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="G61" s="39"/>
-      <c r="H61" s="37"/>
-      <c r="I61" s="39"/>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A62" s="36"/>
-      <c r="B62" s="36" t="s">
+      <c r="G69" s="36"/>
+      <c r="H69" s="34"/>
+      <c r="I69" s="36"/>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A70" s="33"/>
+      <c r="B70" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="C62" s="38">
+      <c r="C70" s="35">
         <v>45537</v>
       </c>
-      <c r="D62" s="36" t="s">
+      <c r="D70" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="E62" s="37"/>
-      <c r="F62" s="49" t="s">
+      <c r="E70" s="34"/>
+      <c r="F70" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="G62" s="39">
+      <c r="G70" s="36">
         <v>45691</v>
       </c>
-      <c r="H62" s="37"/>
-      <c r="I62" s="39"/>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A63" s="28"/>
-      <c r="B63" s="29"/>
-      <c r="C63" s="30"/>
-      <c r="D63" s="17" t="s">
+      <c r="H70" s="34"/>
+      <c r="I70" s="36"/>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A71" s="66"/>
+      <c r="B71" s="67"/>
+      <c r="C71" s="68"/>
+      <c r="D71" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="F63" s="5"/>
-      <c r="H63" s="5"/>
-    </row>
-    <row r="64" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="12"/>
-      <c r="B64" s="8"/>
-      <c r="C64" s="24"/>
-      <c r="D64" s="12"/>
-      <c r="E64" s="8"/>
-      <c r="F64" s="9"/>
-      <c r="G64" s="9"/>
-      <c r="H64" s="9"/>
-      <c r="I64" s="9"/>
-    </row>
-    <row r="65" spans="1:9" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="36" t="s">
+      <c r="F71" s="5"/>
+      <c r="H71" s="5"/>
+    </row>
+    <row r="72" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="1"/>
+      <c r="C72" s="74">
+        <v>45718</v>
+      </c>
+      <c r="D72" s="75" t="s">
+        <v>77</v>
+      </c>
+      <c r="E72" s="75"/>
+      <c r="F72" s="76"/>
+      <c r="G72" s="76"/>
+      <c r="H72" s="76"/>
+      <c r="I72" s="76"/>
+    </row>
+    <row r="73" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="1"/>
+      <c r="C73" s="69">
+        <v>45733</v>
+      </c>
+      <c r="D73" s="70" t="s">
+        <v>78</v>
+      </c>
+      <c r="E73" s="70"/>
+      <c r="F73" s="71"/>
+      <c r="G73" s="71"/>
+      <c r="H73" s="72"/>
+      <c r="I73" s="73"/>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="F74" s="5"/>
+      <c r="H74" s="5"/>
+    </row>
+    <row r="75" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="12"/>
+      <c r="B75" s="8"/>
+      <c r="C75" s="24"/>
+      <c r="D75" s="12"/>
+      <c r="E75" s="8"/>
+      <c r="F75" s="9"/>
+      <c r="G75" s="9"/>
+      <c r="H75" s="9"/>
+      <c r="I75" s="9"/>
+    </row>
+    <row r="76" spans="1:9" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="B65" s="37" t="s">
+      <c r="B76" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="C65" s="38">
+      <c r="C76" s="35">
         <v>45438</v>
       </c>
-      <c r="D65" s="36" t="s">
+      <c r="D76" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="E65" s="37">
+      <c r="E76" s="34">
         <v>0</v>
       </c>
-      <c r="F65" s="13" t="s">
+      <c r="F76" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="G65" s="39"/>
-      <c r="H65" s="37"/>
-      <c r="I65" s="39"/>
-    </row>
-    <row r="66" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A66" s="36"/>
-      <c r="B66" s="40" t="s">
+      <c r="G76" s="36"/>
+      <c r="H76" s="34"/>
+      <c r="I76" s="36"/>
+    </row>
+    <row r="77" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A77" s="33"/>
+      <c r="B77" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="C66" s="41">
+      <c r="C77" s="38">
         <v>45486</v>
       </c>
-      <c r="D66" s="36" t="s">
+      <c r="D77" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="E66" s="37"/>
-      <c r="F66" s="42" t="s">
+      <c r="E77" s="34"/>
+      <c r="F77" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="G66" s="43">
+      <c r="G77" s="40">
         <v>45588</v>
       </c>
-      <c r="H66" s="37"/>
-      <c r="I66" s="39"/>
-    </row>
-    <row r="67" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A67" s="36"/>
-      <c r="B67" s="40" t="s">
+      <c r="H77" s="34"/>
+      <c r="I77" s="36"/>
+    </row>
+    <row r="78" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A78" s="33"/>
+      <c r="B78" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="C67" s="41">
+      <c r="C78" s="38">
         <v>45590</v>
       </c>
-      <c r="D67" s="36" t="s">
+      <c r="D78" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="E67" s="36"/>
-      <c r="F67" s="42" t="s">
+      <c r="E78" s="33"/>
+      <c r="F78" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="G67" s="43">
+      <c r="G78" s="40">
         <v>45688</v>
       </c>
-      <c r="H67" s="37"/>
-      <c r="I67" s="39"/>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A68" s="17"/>
-      <c r="B68" s="18"/>
-      <c r="C68" s="44"/>
-      <c r="D68" s="17" t="s">
+      <c r="H78" s="34"/>
+      <c r="I78" s="36"/>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A79" s="17"/>
+      <c r="B79" s="18"/>
+      <c r="C79" s="41"/>
+      <c r="D79" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="E68" s="18"/>
-      <c r="F68" s="19"/>
-      <c r="G68" s="20"/>
-      <c r="H68" s="16"/>
-      <c r="I68" s="15"/>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A69" s="1"/>
-      <c r="B69" s="21"/>
-      <c r="C69" s="27"/>
-      <c r="D69" s="1"/>
-      <c r="E69" s="21"/>
-      <c r="F69" s="23"/>
-      <c r="G69" s="22"/>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A70" s="1"/>
-      <c r="B70" s="21"/>
-      <c r="C70" s="27"/>
-      <c r="D70" s="1"/>
-      <c r="E70" s="21"/>
-      <c r="F70" s="23"/>
-      <c r="G70" s="22"/>
-    </row>
-    <row r="71" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="8"/>
-      <c r="B71" s="8"/>
-      <c r="C71" s="24"/>
-      <c r="D71" s="8"/>
-      <c r="E71" s="8"/>
-      <c r="F71" s="8"/>
-      <c r="G71" s="9"/>
-      <c r="H71" s="8"/>
-      <c r="I71" s="9"/>
-    </row>
-    <row r="72" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="36" t="s">
+      <c r="E79" s="18"/>
+      <c r="F79" s="19"/>
+      <c r="G79" s="20"/>
+      <c r="H79" s="16"/>
+      <c r="I79" s="15"/>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A80" s="1"/>
+      <c r="B80" s="21"/>
+      <c r="C80" s="27"/>
+      <c r="D80" s="1"/>
+      <c r="E80" s="21"/>
+      <c r="F80" s="23"/>
+      <c r="G80" s="22"/>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A81" s="1"/>
+      <c r="B81" s="21"/>
+      <c r="C81" s="27"/>
+      <c r="D81" s="1"/>
+      <c r="E81" s="21"/>
+      <c r="F81" s="23"/>
+      <c r="G81" s="22"/>
+    </row>
+    <row r="82" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="8"/>
+      <c r="B82" s="8"/>
+      <c r="C82" s="24"/>
+      <c r="D82" s="8"/>
+      <c r="E82" s="8"/>
+      <c r="F82" s="8"/>
+      <c r="G82" s="9"/>
+      <c r="H82" s="8"/>
+      <c r="I82" s="9"/>
+    </row>
+    <row r="83" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="B72" s="37" t="s">
+      <c r="B83" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="C72" s="38">
+      <c r="C83" s="35">
         <v>45588</v>
       </c>
-      <c r="D72" s="36" t="s">
+      <c r="D83" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="E72" s="37"/>
-      <c r="F72" s="37"/>
-      <c r="G72" s="7">
+      <c r="E83" s="34"/>
+      <c r="F83" s="34"/>
+      <c r="G83" s="7">
         <v>45672</v>
       </c>
-      <c r="H72" s="36" t="s">
+      <c r="H83" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="I72" s="39">
+      <c r="I83" s="36">
         <v>45625</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A73" s="36" t="s">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A84" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="B73" s="37" t="s">
+      <c r="B84" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="C73" s="38">
+      <c r="C84" s="35">
         <v>45588</v>
       </c>
-      <c r="D73" s="36" t="s">
+      <c r="D84" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="E73" s="37"/>
-      <c r="F73" s="37"/>
-      <c r="G73" s="7">
+      <c r="E84" s="34"/>
+      <c r="F84" s="34"/>
+      <c r="G84" s="7">
         <v>45672</v>
       </c>
-      <c r="H73" s="50" t="s">
+      <c r="H84" s="47" t="s">
         <v>48</v>
       </c>
-      <c r="I73" s="39">
+      <c r="I84" s="36">
         <v>45625</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A74" s="14" t="s">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A85" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="B74" s="45" t="s">
+      <c r="B85" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="C74" s="46">
+      <c r="C85" s="43">
         <v>45475</v>
       </c>
-      <c r="D74" s="14" t="s">
+      <c r="D85" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="E74" s="45">
+      <c r="E85" s="42">
         <v>113</v>
       </c>
-      <c r="F74" s="14" t="s">
+      <c r="F85" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="G74" s="7">
+      <c r="G85" s="7">
         <v>45672</v>
       </c>
-      <c r="H74" s="14" t="s">
+      <c r="H85" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="I74" s="47">
+      <c r="I85" s="44">
         <v>45705</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A75" s="14" t="s">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A86" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="B75" s="45" t="s">
+      <c r="B86" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="C75" s="46"/>
-      <c r="D75" s="14" t="s">
+      <c r="C86" s="43"/>
+      <c r="D86" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="E75" s="45">
+      <c r="E86" s="42">
         <v>113</v>
       </c>
-      <c r="F75" s="14" t="s">
+      <c r="F86" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="G75" s="7">
+      <c r="G86" s="7">
         <v>45672</v>
       </c>
-      <c r="H75" s="54" t="s">
+      <c r="H86" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="I75" s="47">
+      <c r="I86" s="44">
         <v>45705</v>
       </c>
     </row>

--- a/mahkeme/2025-02-Dosya Listesi.xlsx
+++ b/mahkeme/2025-02-Dosya Listesi.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28429"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\aaGitMe\yzhn\mahkeme\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\comprg\bvaagitme\yzhn\mahkeme\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE98D4A3-186A-4780-A176-B994C7F82F09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D01817F7-9DD2-40BC-AB9D-7F125988F57D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-45" yWindow="120" windowWidth="12225" windowHeight="10320" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="88">
   <si>
     <t>Dosya Listesi</t>
   </si>
@@ -182,9 +182,6 @@
   </si>
   <si>
     <t>ön inceleme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sh-itrzipt </t>
   </si>
   <si>
     <r>
@@ -288,6 +285,27 @@
   <si>
     <t>2025/29356</t>
   </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>davalı cexap dilekçesi vermedi</t>
+  </si>
+  <si>
+    <t>tapu ve sözleşme yollandı</t>
+  </si>
+  <si>
+    <t>(11) damga V</t>
+  </si>
+  <si>
+    <t>sh-itrzipt - tmerrüt nedeniyle tahliye</t>
+  </si>
+  <si>
+    <t>sh-itrzipt-taahhüt nedeniyle tahliye</t>
+  </si>
+  <si>
+    <t>tapu, sözleşme ve taahhüt yollandı</t>
+  </si>
 </sst>
 </file>
 
@@ -296,7 +314,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yy;@"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -390,8 +408,24 @@
       <family val="2"/>
       <charset val="162"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="162"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="162"/>
+    </font>
   </fonts>
-  <fills count="13">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -464,6 +498,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="7">
     <border>
@@ -486,17 +532,6 @@
       <left/>
       <right/>
       <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="double">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="double">
         <color indexed="64"/>
       </top>
       <bottom style="double">
@@ -541,150 +576,186 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="102">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="10" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="20" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="20" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="10" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="20" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="12" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="12" fillId="12" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="12" fillId="12" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="12" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="12" fillId="12" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="12" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="12" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="12" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="12" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="12" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="12" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="12" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="1" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="12" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="12" fillId="7" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="12" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -999,7 +1070,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I86"/>
+  <dimension ref="A1:O89"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -1007,9 +1078,9 @@
     <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="4.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="4" customWidth="1"/>
-    <col min="7" max="7" width="8.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10" style="5" customWidth="1"/>
     <col min="8" max="8" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10" style="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.140625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1049,1048 +1120,1158 @@
       </c>
     </row>
     <row r="3" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="83"/>
-      <c r="I3"/>
+      <c r="A3" s="81" t="s">
+        <v>79</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="I3" s="82">
+        <v>45712</v>
+      </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="83" t="s">
-        <v>80</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="I4" s="84">
-        <v>45712</v>
-      </c>
+      <c r="A4" s="81"/>
+      <c r="I4"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="83"/>
+      <c r="A5" s="81"/>
       <c r="I5"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="83"/>
+      <c r="A6" s="81"/>
       <c r="I6"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="83"/>
+      <c r="A7" s="81"/>
       <c r="I7"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="83"/>
+      <c r="A8" s="81"/>
       <c r="I8"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="83"/>
-      <c r="I9"/>
+      <c r="A9" s="95"/>
+      <c r="B9" s="96" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="97" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="96"/>
+      <c r="E9" s="98" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" s="98"/>
+      <c r="G9" s="99" t="s">
+        <v>31</v>
+      </c>
+      <c r="H9" s="96" t="s">
+        <v>39</v>
+      </c>
+      <c r="I9" s="96" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="83" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="25">
+        <v>45475</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="52">
+        <v>97</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="I10" s="6">
+        <v>45705</v>
+      </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>6</v>
+      <c r="A11" s="4"/>
+      <c r="B11" s="84" t="s">
+        <v>2</v>
       </c>
       <c r="C11" s="25">
-        <v>45475</v>
+        <v>45604</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="54">
-        <v>97</v>
+      <c r="E11" s="52">
+        <v>178</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="H11" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="I11" s="6">
+      <c r="H11" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="I11" s="31">
         <v>45705</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C12" s="25">
-        <v>45604</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E12" s="54">
-        <v>178</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H12" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="I12" s="31">
-        <v>45705</v>
+      <c r="A12" s="1"/>
+      <c r="B12" s="85" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12" s="26">
+        <v>45704</v>
+      </c>
+      <c r="D12" s="63" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
-      <c r="B13" t="s">
-        <v>36</v>
+      <c r="B13" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="C13" s="26">
-        <v>45704</v>
+        <v>45705</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>54</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="H13" s="1"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
-      <c r="B14" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C14" s="26">
-        <v>45705</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>60</v>
-      </c>
+      <c r="C14" s="53"/>
+      <c r="D14" s="1"/>
       <c r="H14" s="1"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
-      <c r="C15" s="55"/>
-      <c r="D15" s="1"/>
+      <c r="C15" s="53" t="s">
+        <v>56</v>
+      </c>
+      <c r="D15" s="63" t="s">
+        <v>61</v>
+      </c>
       <c r="H15" s="1"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
-      <c r="C16" s="55" t="s">
+      <c r="C16" s="53">
+        <v>45712</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H16" s="1"/>
+    </row>
+    <row r="17" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="1"/>
+      <c r="C17" s="88">
+        <v>45717</v>
+      </c>
+      <c r="D17" s="89" t="s">
+        <v>78</v>
+      </c>
+      <c r="E17" s="90" t="s">
+        <v>62</v>
+      </c>
+      <c r="F17" s="89"/>
+      <c r="G17" s="91"/>
+      <c r="H17" s="89" t="s">
+        <v>63</v>
+      </c>
+      <c r="I17" s="92"/>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A18" s="1"/>
+      <c r="C18" s="56"/>
+      <c r="D18" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="H18" s="1"/>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A19" s="1"/>
+      <c r="C19" s="53"/>
+      <c r="D19" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="H19" s="1"/>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A20" s="1"/>
+      <c r="C20" s="53"/>
+      <c r="D20" s="1"/>
+      <c r="I20" s="93" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="1"/>
+      <c r="B21" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="C21" s="47">
+        <v>45805</v>
+      </c>
+      <c r="D21" s="48">
+        <v>0.40972222222222227</v>
+      </c>
+      <c r="E21" t="s">
+        <v>55</v>
+      </c>
+      <c r="I21"/>
+    </row>
+    <row r="22" spans="1:15" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="1"/>
+      <c r="C22" s="53">
+        <v>45805</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="H16" s="1"/>
-    </row>
-    <row r="17" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="1"/>
-      <c r="C17" s="55">
-        <v>45712</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="H17" s="1"/>
-    </row>
-    <row r="18" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="1"/>
-      <c r="C18" s="77">
-        <v>45717</v>
-      </c>
-      <c r="D18" s="78" t="s">
-        <v>79</v>
-      </c>
-      <c r="E18" s="79" t="s">
-        <v>63</v>
-      </c>
-      <c r="F18" s="78"/>
-      <c r="G18" s="80"/>
-      <c r="H18" s="78" t="s">
-        <v>64</v>
-      </c>
-      <c r="I18" s="81"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="1"/>
-      <c r="C19" s="58"/>
-      <c r="D19" s="1"/>
-      <c r="H19" s="1"/>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="1"/>
-      <c r="C20" s="55"/>
-      <c r="D20" s="1"/>
-      <c r="H20" s="1"/>
-    </row>
-    <row r="21" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="1"/>
-      <c r="B21" s="48" t="s">
-        <v>53</v>
-      </c>
-      <c r="C21" s="49">
-        <v>45805</v>
-      </c>
-      <c r="D21" s="50">
-        <v>0.40972222222222227</v>
-      </c>
-      <c r="E21" t="s">
-        <v>56</v>
-      </c>
-      <c r="I21"/>
-    </row>
-    <row r="22" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="1"/>
-      <c r="C22" s="55">
-        <v>45805</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="12"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="24"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="12"/>
-      <c r="I23" s="8"/>
-    </row>
-    <row r="24" spans="1:9" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="4" t="s">
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A23" s="1"/>
+      <c r="C23" s="53"/>
+      <c r="D23" s="1"/>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A24" s="95"/>
+      <c r="B24" s="96" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" s="97" t="s">
+        <v>30</v>
+      </c>
+      <c r="D24" s="96"/>
+      <c r="E24" s="98" t="s">
+        <v>28</v>
+      </c>
+      <c r="F24" s="98"/>
+      <c r="G24" s="99" t="s">
+        <v>31</v>
+      </c>
+      <c r="H24" s="96" t="s">
+        <v>39</v>
+      </c>
+      <c r="I24" s="96" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B25" s="83" t="s">
         <v>4</v>
       </c>
-      <c r="C24" s="32">
+      <c r="C25" s="94">
         <v>45588</v>
       </c>
-      <c r="D24" s="54" t="s">
+      <c r="D25" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="E24" s="3"/>
-      <c r="F24" s="4" t="s">
+      <c r="E25" s="3"/>
+      <c r="F25" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="H24" s="4" t="s">
+      <c r="H25" s="4" t="s">
         <v>46</v>
-      </c>
-      <c r="I24" s="6">
-        <v>45630</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="4"/>
-      <c r="B25" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C25" s="25"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="4"/>
-      <c r="H25" s="14" t="s">
-        <v>47</v>
       </c>
       <c r="I25" s="6">
         <v>45630</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4"/>
-      <c r="B26" t="s">
+      <c r="B26" s="83" t="s">
+        <v>4</v>
+      </c>
+      <c r="C26" s="25"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="4"/>
+      <c r="H26" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="I26" s="6">
+        <v>45630</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="4"/>
+      <c r="B27" s="85" t="s">
         <v>35</v>
       </c>
-      <c r="C26" s="52">
+      <c r="C27" s="50">
         <v>45704</v>
       </c>
-      <c r="D26" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-      <c r="H26" s="1"/>
-      <c r="I26"/>
-    </row>
-    <row r="27" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="1"/>
-      <c r="B27" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C27" s="26">
+      <c r="D27" s="63" t="s">
+        <v>86</v>
+      </c>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27"/>
+      <c r="M27">
+        <v>200</v>
+      </c>
+      <c r="N27">
+        <v>0.3</v>
+      </c>
+      <c r="O27">
+        <f>N27*M27</f>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="1"/>
+      <c r="B28" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C28" s="26">
         <v>45709</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="D28" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H28" s="1"/>
+      <c r="M28">
+        <v>600</v>
+      </c>
+      <c r="N28">
+        <v>30</v>
+      </c>
+      <c r="O28">
+        <f>N28*M28</f>
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A29" s="1"/>
+      <c r="C29" s="53" t="s">
+        <v>56</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="H29" s="1"/>
+      <c r="M29">
+        <v>700</v>
+      </c>
+      <c r="N29">
         <v>60</v>
       </c>
-      <c r="H27" s="1"/>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="1"/>
-      <c r="C28" s="55" t="s">
-        <v>57</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="H28" s="1"/>
-    </row>
-    <row r="29" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="1"/>
-      <c r="C29" s="55">
+      <c r="O29">
+        <f>N29*M29</f>
+        <v>42000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="1"/>
+      <c r="C30" s="53">
         <v>45712</v>
       </c>
-      <c r="D29" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="H29" s="1"/>
-    </row>
-    <row r="30" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="1"/>
-      <c r="C30" s="77">
+      <c r="D30" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H30" s="1"/>
+      <c r="O30">
+        <f>SUM(O28:O29)</f>
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="1"/>
+      <c r="C31" s="75">
         <v>45717</v>
       </c>
-      <c r="D30" s="78" t="s">
-        <v>79</v>
-      </c>
-      <c r="E30" s="79" t="s">
+      <c r="D31" s="76" t="s">
+        <v>78</v>
+      </c>
+      <c r="E31" s="77" t="s">
+        <v>62</v>
+      </c>
+      <c r="F31" s="76"/>
+      <c r="G31" s="78"/>
+      <c r="H31" s="76" t="s">
         <v>63</v>
       </c>
-      <c r="F30" s="78"/>
-      <c r="G30" s="80"/>
-      <c r="H30" s="78" t="s">
-        <v>64</v>
-      </c>
-      <c r="I30" s="81"/>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="1"/>
-      <c r="H31" s="1"/>
-    </row>
-    <row r="32" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I31" s="79"/>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
-      <c r="B32" s="48" t="s">
-        <v>53</v>
-      </c>
-      <c r="C32" s="49">
-        <v>45805</v>
-      </c>
-      <c r="D32" s="56">
-        <v>0</v>
-      </c>
-      <c r="I32"/>
-    </row>
-    <row r="33" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="C32" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F32" s="5"/>
+      <c r="G32" s="101"/>
+      <c r="H32" s="100"/>
+      <c r="I32" s="101"/>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
-      <c r="C33" s="55">
-        <v>45805</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>61</v>
-      </c>
+      <c r="C33" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="F33" s="5"/>
+      <c r="G33" s="101"/>
+      <c r="H33" s="100"/>
+      <c r="I33" s="101"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
-      <c r="F34" s="1"/>
       <c r="H34" s="1"/>
-      <c r="I34"/>
     </row>
     <row r="35" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="12"/>
-      <c r="B35" s="8"/>
-      <c r="C35" s="24"/>
-      <c r="D35" s="12"/>
-      <c r="E35" s="12"/>
-      <c r="F35" s="12"/>
-      <c r="G35" s="9"/>
-      <c r="H35" s="12"/>
-      <c r="I35" s="8"/>
+      <c r="A35" s="1"/>
+      <c r="B35" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="C35" s="47">
+        <v>45805</v>
+      </c>
+      <c r="D35" s="54">
+        <v>0</v>
+      </c>
+      <c r="I35" s="93" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="36" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="2" t="s">
+      <c r="A36" s="1"/>
+      <c r="C36" s="53">
+        <v>45805</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+      <c r="H37" s="1"/>
+      <c r="I37"/>
+    </row>
+    <row r="38" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="12"/>
+      <c r="B38" s="8"/>
+      <c r="C38" s="24"/>
+      <c r="D38" s="12"/>
+      <c r="E38" s="12"/>
+      <c r="F38" s="12"/>
+      <c r="G38" s="9"/>
+      <c r="H38" s="12"/>
+      <c r="I38" s="8"/>
+    </row>
+    <row r="39" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B39" s="83" t="s">
         <v>7</v>
       </c>
-      <c r="C36" s="25">
+      <c r="C39" s="25">
         <v>45475</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="D39" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E36" s="54">
+      <c r="E39" s="52">
         <v>214</v>
       </c>
-      <c r="F36" s="4" t="s">
+      <c r="F39" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="H36" s="4" t="s">
+      <c r="H39" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I36" s="6">
+      <c r="I39" s="6">
         <v>45702</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" s="2"/>
-      <c r="B37" s="3"/>
-      <c r="C37" s="25"/>
-      <c r="D37" s="4"/>
-      <c r="E37" s="3"/>
-      <c r="F37" s="4"/>
-      <c r="H37" s="14" t="s">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A40" s="2"/>
+      <c r="B40" s="3"/>
+      <c r="C40" s="25"/>
+      <c r="D40" s="4"/>
+      <c r="E40" s="3"/>
+      <c r="F40" s="4"/>
+      <c r="H40" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="I37" s="6">
+      <c r="I40" s="6">
         <v>45702</v>
       </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38" s="1"/>
-      <c r="B38" t="s">
-        <v>33</v>
-      </c>
-      <c r="C38" s="26">
-        <v>45704</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="H38" s="1"/>
-      <c r="I38"/>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A39" s="1"/>
-      <c r="B39" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C39" s="26">
-        <v>45705</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="H39" s="1"/>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A40" s="1"/>
-      <c r="D40" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="H40" s="1"/>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
-      <c r="C41" s="55" t="s">
-        <v>57</v>
-      </c>
-      <c r="D41" s="65" t="s">
-        <v>69</v>
+      <c r="B41" s="85" t="s">
+        <v>33</v>
+      </c>
+      <c r="C41" s="26">
+        <v>45704</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>54</v>
       </c>
       <c r="H41" s="1"/>
-    </row>
-    <row r="42" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I41"/>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
-      <c r="C42" s="55">
-        <v>45706</v>
+      <c r="B42" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C42" s="26">
+        <v>45705</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="H42" s="1"/>
     </row>
-    <row r="43" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
-      <c r="C43" s="82">
-        <v>45711</v>
-      </c>
-      <c r="D43" s="78" t="s">
-        <v>70</v>
-      </c>
-      <c r="E43" s="78"/>
-      <c r="F43" s="78"/>
-      <c r="G43" s="80"/>
-      <c r="H43" s="78"/>
-      <c r="I43" s="81"/>
+      <c r="D43" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H43" s="1"/>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="1"/>
-      <c r="C44" s="58" t="s">
-        <v>71</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>72</v>
+      <c r="C44" s="53" t="s">
+        <v>56</v>
+      </c>
+      <c r="D44" s="63" t="s">
+        <v>68</v>
       </c>
       <c r="H44" s="1"/>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
-      <c r="C45" s="58"/>
+      <c r="C45" s="53">
+        <v>45706</v>
+      </c>
       <c r="D45" s="1" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="H45" s="1"/>
     </row>
     <row r="46" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1"/>
-      <c r="B46" s="48" t="s">
+      <c r="C46" s="80">
+        <v>45711</v>
+      </c>
+      <c r="D46" s="76" t="s">
+        <v>69</v>
+      </c>
+      <c r="E46" s="76"/>
+      <c r="F46" s="76"/>
+      <c r="G46" s="78"/>
+      <c r="H46" s="76"/>
+      <c r="I46" s="79"/>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A47" s="1"/>
+      <c r="C47" s="56" t="s">
+        <v>70</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H47" s="1"/>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A48" s="1"/>
+      <c r="C48" s="56"/>
+      <c r="D48" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H48" s="1"/>
+    </row>
+    <row r="49" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="1"/>
+      <c r="B49" s="46" t="s">
         <v>53</v>
       </c>
-      <c r="C46" s="49">
+      <c r="C49" s="47">
         <v>45792</v>
       </c>
-      <c r="D46" s="50">
+      <c r="D49" s="48">
         <v>0.39930555555555558</v>
       </c>
-      <c r="I46"/>
-    </row>
-    <row r="47" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="1"/>
-      <c r="C47" s="55">
+      <c r="I49"/>
+    </row>
+    <row r="50" spans="1:11" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="1"/>
+      <c r="C50" s="53">
         <v>45792</v>
       </c>
-      <c r="D47" s="1" t="s">
+      <c r="D50" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="H50" s="1"/>
+      <c r="I50"/>
+    </row>
+    <row r="52" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B52" s="83" t="s">
+        <v>3</v>
+      </c>
+      <c r="C52" s="51">
+        <v>45603</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E52" s="52">
+        <v>156</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G52" s="6"/>
+      <c r="H52" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I52" s="5">
+        <v>45705</v>
+      </c>
+      <c r="K52" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="4"/>
+      <c r="B53" s="3"/>
+      <c r="C53" s="25"/>
+      <c r="D53" s="4"/>
+      <c r="E53" s="3"/>
+      <c r="F53" s="4"/>
+      <c r="G53" s="6"/>
+      <c r="H53" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="I53" s="5">
+        <v>45705</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="1"/>
+      <c r="B54" s="85" t="s">
+        <v>37</v>
+      </c>
+      <c r="C54" s="50">
+        <v>45704</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F54" s="1"/>
+      <c r="H54" s="1"/>
+    </row>
+    <row r="55" spans="1:11" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="1"/>
+      <c r="B55" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C55" s="26">
+        <v>45705</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H55" s="1"/>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A56" s="1"/>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A57" s="1"/>
+      <c r="C57" s="53" t="s">
+        <v>56</v>
+      </c>
+      <c r="D57" s="63" t="s">
         <v>68</v>
       </c>
-      <c r="H47" s="1"/>
-      <c r="I47"/>
-    </row>
-    <row r="49" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C49" s="53">
-        <v>45603</v>
-      </c>
-      <c r="D49" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E49" s="54">
-        <v>156</v>
-      </c>
-      <c r="F49" s="4" t="s">
+      <c r="G57" s="62"/>
+      <c r="H57" s="1"/>
+    </row>
+    <row r="58" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="1"/>
+      <c r="C58" s="53">
+        <v>45706</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H58" s="1"/>
+    </row>
+    <row r="59" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="1"/>
+      <c r="C59" s="80">
+        <v>45711</v>
+      </c>
+      <c r="D59" s="76" t="s">
+        <v>69</v>
+      </c>
+      <c r="E59" s="76"/>
+      <c r="F59" s="76"/>
+      <c r="G59" s="78"/>
+      <c r="H59" s="76"/>
+      <c r="I59" s="79"/>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A60" s="1"/>
+      <c r="B60" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C60" s="55"/>
+      <c r="D60" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="H60" s="1"/>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A61" s="1"/>
+      <c r="D61" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H61" s="1"/>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="H62" s="1"/>
+    </row>
+    <row r="63" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B63" s="58" t="s">
+        <v>53</v>
+      </c>
+      <c r="C63" s="59">
+        <v>45792</v>
+      </c>
+      <c r="D63" s="60">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="I63"/>
+    </row>
+    <row r="64" spans="1:11" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="B64" s="57"/>
+      <c r="C64" s="61">
+        <v>45792</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="I64"/>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B65" s="57"/>
+      <c r="C65" s="61"/>
+      <c r="D65" s="1"/>
+      <c r="I65"/>
+    </row>
+    <row r="66" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="12"/>
+      <c r="B66" s="8"/>
+      <c r="C66" s="24"/>
+      <c r="D66" s="12"/>
+      <c r="E66" s="8"/>
+      <c r="F66" s="8"/>
+      <c r="G66" s="9"/>
+      <c r="H66" s="12"/>
+      <c r="I66" s="8"/>
+    </row>
+    <row r="67" spans="1:11" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B67" s="83" t="s">
+        <v>1</v>
+      </c>
+      <c r="C67" s="25">
+        <v>45676</v>
+      </c>
+      <c r="D67" s="52" t="s">
+        <v>21</v>
+      </c>
+      <c r="E67" s="4"/>
+      <c r="F67" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="G49" s="6"/>
-      <c r="H49" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I49" s="5">
-        <v>45705</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="4"/>
-      <c r="B50" s="3"/>
-      <c r="C50" s="25"/>
-      <c r="D50" s="4"/>
-      <c r="E50" s="3"/>
-      <c r="F50" s="4"/>
-      <c r="G50" s="6"/>
-      <c r="H50" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="I50" s="5">
-        <v>45705</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="1"/>
-      <c r="B51" t="s">
-        <v>37</v>
-      </c>
-      <c r="C51" s="52">
-        <v>45704</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F51" s="1"/>
-      <c r="H51" s="1"/>
-    </row>
-    <row r="52" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="1"/>
-      <c r="B52" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C52" s="26">
-        <v>45705</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="H52" s="1"/>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A53" s="1"/>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A54" s="1"/>
-      <c r="C54" s="55" t="s">
-        <v>57</v>
-      </c>
-      <c r="D54" s="65" t="s">
-        <v>69</v>
-      </c>
-      <c r="G54" s="64"/>
-      <c r="H54" s="1"/>
-    </row>
-    <row r="55" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="1"/>
-      <c r="C55" s="55">
-        <v>45706</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="H55" s="1"/>
-    </row>
-    <row r="56" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="1"/>
-      <c r="C56" s="82">
-        <v>45711</v>
-      </c>
-      <c r="D56" s="78" t="s">
-        <v>70</v>
-      </c>
-      <c r="E56" s="78"/>
-      <c r="F56" s="78"/>
-      <c r="G56" s="80"/>
-      <c r="H56" s="78"/>
-      <c r="I56" s="81"/>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A57" s="1"/>
-      <c r="B57" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C57" s="57"/>
-      <c r="D57" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="H57" s="1"/>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A58" s="1"/>
-      <c r="D58" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="H58" s="1"/>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A59" s="1"/>
-      <c r="D59" s="1"/>
-      <c r="H59" s="1"/>
-    </row>
-    <row r="60" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="60" t="s">
-        <v>53</v>
-      </c>
-      <c r="C60" s="61">
-        <v>45792</v>
-      </c>
-      <c r="D60" s="62">
-        <v>0.39583333333333331</v>
-      </c>
-      <c r="I60"/>
-    </row>
-    <row r="61" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="59"/>
-      <c r="C61" s="63">
-        <v>45792</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="I61"/>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B62" s="59"/>
-      <c r="C62" s="63"/>
-      <c r="D62" s="1"/>
-      <c r="I62"/>
-    </row>
-    <row r="63" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="12"/>
-      <c r="B63" s="8"/>
-      <c r="C63" s="24"/>
-      <c r="D63" s="12"/>
-      <c r="E63" s="8"/>
-      <c r="F63" s="8"/>
-      <c r="G63" s="9"/>
-      <c r="H63" s="12"/>
-      <c r="I63" s="8"/>
-    </row>
-    <row r="64" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="4" t="s">
+      <c r="H67" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="K67" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A68" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B64" s="3" t="s">
+      <c r="B68" s="83" t="s">
         <v>1</v>
       </c>
-      <c r="C64" s="25">
-        <v>45676</v>
-      </c>
-      <c r="D64" s="54" t="s">
-        <v>21</v>
-      </c>
-      <c r="E64" s="4"/>
-      <c r="F64" s="4" t="s">
+      <c r="C68" s="25"/>
+      <c r="D68" s="4"/>
+      <c r="E68" s="4"/>
+      <c r="F68" s="4"/>
+      <c r="H68" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I68" s="15">
+        <v>45714</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A69" s="1"/>
+      <c r="D69" s="1"/>
+      <c r="E69" s="1"/>
+      <c r="F69" s="1"/>
+      <c r="H69" s="1"/>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B70" s="57"/>
+      <c r="C70" s="61"/>
+      <c r="D70" s="1"/>
+      <c r="I70"/>
+    </row>
+    <row r="71" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="12"/>
+      <c r="B71" s="8"/>
+      <c r="C71" s="24"/>
+      <c r="D71" s="12"/>
+      <c r="E71" s="8"/>
+      <c r="F71" s="8"/>
+      <c r="G71" s="9"/>
+      <c r="H71" s="12"/>
+      <c r="I71" s="8"/>
+    </row>
+    <row r="72" spans="1:11" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="B72" s="83" t="s">
+        <v>10</v>
+      </c>
+      <c r="C72" s="34">
+        <v>45342</v>
+      </c>
+      <c r="D72" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="E72" s="33"/>
+      <c r="F72" s="43" t="s">
         <v>26</v>
       </c>
-      <c r="H64" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A65" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C65" s="25"/>
-      <c r="D65" s="4"/>
-      <c r="E65" s="4"/>
-      <c r="F65" s="4"/>
-      <c r="H65" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="I65" s="15">
-        <v>45714</v>
-      </c>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A66" s="1"/>
-      <c r="D66" s="1"/>
-      <c r="E66" s="1"/>
-      <c r="F66" s="1"/>
-      <c r="H66" s="1"/>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B67" s="59"/>
-      <c r="C67" s="63"/>
-      <c r="D67" s="1"/>
-      <c r="I67"/>
-    </row>
-    <row r="68" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="12"/>
-      <c r="B68" s="8"/>
-      <c r="C68" s="24"/>
-      <c r="D68" s="12"/>
-      <c r="E68" s="8"/>
-      <c r="F68" s="8"/>
-      <c r="G68" s="9"/>
-      <c r="H68" s="12"/>
-      <c r="I68" s="8"/>
-    </row>
-    <row r="69" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="33" t="s">
-        <v>16</v>
-      </c>
-      <c r="B69" s="34" t="s">
-        <v>10</v>
-      </c>
-      <c r="C69" s="35">
-        <v>45342</v>
-      </c>
-      <c r="D69" s="33" t="s">
-        <v>14</v>
-      </c>
-      <c r="E69" s="34"/>
-      <c r="F69" s="45" t="s">
-        <v>26</v>
-      </c>
-      <c r="G69" s="36"/>
-      <c r="H69" s="34"/>
-      <c r="I69" s="36"/>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A70" s="33"/>
-      <c r="B70" s="33" t="s">
+      <c r="G72" s="35"/>
+      <c r="H72" s="33"/>
+      <c r="I72" s="35"/>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A73" s="32"/>
+      <c r="B73" s="86" t="s">
         <v>24</v>
       </c>
-      <c r="C70" s="35">
+      <c r="C73" s="34">
         <v>45537</v>
       </c>
-      <c r="D70" s="33" t="s">
+      <c r="D73" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="E70" s="34"/>
-      <c r="F70" s="46" t="s">
+      <c r="E73" s="33"/>
+      <c r="F73" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="G70" s="36">
+      <c r="G73" s="35">
         <v>45691</v>
       </c>
-      <c r="H70" s="34"/>
-      <c r="I70" s="36"/>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A71" s="66"/>
-      <c r="B71" s="67"/>
-      <c r="C71" s="68"/>
-      <c r="D71" s="17" t="s">
+      <c r="H73" s="33"/>
+      <c r="I73" s="35"/>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A74" s="64"/>
+      <c r="B74" s="65"/>
+      <c r="C74" s="66"/>
+      <c r="D74" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="F71" s="5"/>
-      <c r="H71" s="5"/>
-    </row>
-    <row r="72" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="1"/>
-      <c r="C72" s="74">
-        <v>45718</v>
-      </c>
-      <c r="D72" s="75" t="s">
-        <v>77</v>
-      </c>
-      <c r="E72" s="75"/>
-      <c r="F72" s="76"/>
-      <c r="G72" s="76"/>
-      <c r="H72" s="76"/>
-      <c r="I72" s="76"/>
-    </row>
-    <row r="73" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="1"/>
-      <c r="C73" s="69">
-        <v>45733</v>
-      </c>
-      <c r="D73" s="70" t="s">
-        <v>78</v>
-      </c>
-      <c r="E73" s="70"/>
-      <c r="F73" s="71"/>
-      <c r="G73" s="71"/>
-      <c r="H73" s="72"/>
-      <c r="I73" s="73"/>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A74" s="1"/>
-      <c r="D74" s="1"/>
       <c r="F74" s="5"/>
       <c r="H74" s="5"/>
     </row>
-    <row r="75" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="12"/>
-      <c r="B75" s="8"/>
-      <c r="C75" s="24"/>
-      <c r="D75" s="12"/>
-      <c r="E75" s="8"/>
-      <c r="F75" s="9"/>
-      <c r="G75" s="9"/>
-      <c r="H75" s="9"/>
-      <c r="I75" s="9"/>
-    </row>
-    <row r="76" spans="1:9" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="33" t="s">
+    <row r="75" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="1"/>
+      <c r="C75" s="72">
+        <v>45718</v>
+      </c>
+      <c r="D75" s="73" t="s">
+        <v>76</v>
+      </c>
+      <c r="E75" s="73"/>
+      <c r="F75" s="74"/>
+      <c r="G75" s="74"/>
+      <c r="H75" s="74"/>
+      <c r="I75" s="74"/>
+    </row>
+    <row r="76" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="1"/>
+      <c r="C76" s="67">
+        <v>45733</v>
+      </c>
+      <c r="D76" s="68" t="s">
+        <v>77</v>
+      </c>
+      <c r="E76" s="68"/>
+      <c r="F76" s="69"/>
+      <c r="G76" s="69"/>
+      <c r="H76" s="70"/>
+      <c r="I76" s="71"/>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A77" s="1"/>
+      <c r="D77" s="1"/>
+      <c r="F77" s="5"/>
+      <c r="H77" s="5"/>
+    </row>
+    <row r="78" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="12"/>
+      <c r="B78" s="8"/>
+      <c r="C78" s="24"/>
+      <c r="D78" s="12"/>
+      <c r="E78" s="8"/>
+      <c r="F78" s="9"/>
+      <c r="G78" s="9"/>
+      <c r="H78" s="9"/>
+      <c r="I78" s="9"/>
+    </row>
+    <row r="79" spans="1:11" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="B76" s="34" t="s">
+      <c r="B79" s="83" t="s">
         <v>9</v>
       </c>
-      <c r="C76" s="35">
+      <c r="C79" s="34">
         <v>45438</v>
       </c>
-      <c r="D76" s="33" t="s">
+      <c r="D79" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="E76" s="34">
+      <c r="E79" s="33">
         <v>0</v>
       </c>
-      <c r="F76" s="13" t="s">
+      <c r="F79" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="G76" s="36"/>
-      <c r="H76" s="34"/>
-      <c r="I76" s="36"/>
-    </row>
-    <row r="77" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A77" s="33"/>
-      <c r="B77" s="37" t="s">
+      <c r="G79" s="35"/>
+      <c r="H79" s="33"/>
+      <c r="I79" s="35"/>
+    </row>
+    <row r="80" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A80" s="32"/>
+      <c r="B80" s="87" t="s">
         <v>17</v>
       </c>
-      <c r="C77" s="38">
+      <c r="C80" s="36">
         <v>45486</v>
       </c>
-      <c r="D77" s="33" t="s">
+      <c r="D80" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="E77" s="34"/>
-      <c r="F77" s="39" t="s">
+      <c r="E80" s="33"/>
+      <c r="F80" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="G77" s="40">
+      <c r="G80" s="38">
         <v>45588</v>
       </c>
-      <c r="H77" s="34"/>
-      <c r="I77" s="36"/>
-    </row>
-    <row r="78" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A78" s="33"/>
-      <c r="B78" s="37" t="s">
+      <c r="H80" s="33"/>
+      <c r="I80" s="35"/>
+    </row>
+    <row r="81" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A81" s="32"/>
+      <c r="B81" s="87" t="s">
         <v>18</v>
       </c>
-      <c r="C78" s="38">
+      <c r="C81" s="36">
         <v>45590</v>
       </c>
-      <c r="D78" s="33" t="s">
+      <c r="D81" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="E78" s="33"/>
-      <c r="F78" s="39" t="s">
+      <c r="E81" s="32"/>
+      <c r="F81" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="G78" s="40">
+      <c r="G81" s="38">
         <v>45688</v>
       </c>
-      <c r="H78" s="34"/>
-      <c r="I78" s="36"/>
-    </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A79" s="17"/>
-      <c r="B79" s="18"/>
-      <c r="C79" s="41"/>
-      <c r="D79" s="17" t="s">
+      <c r="H81" s="33"/>
+      <c r="I81" s="35"/>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A82" s="17"/>
+      <c r="B82" s="18"/>
+      <c r="C82" s="39"/>
+      <c r="D82" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="E79" s="18"/>
-      <c r="F79" s="19"/>
-      <c r="G79" s="20"/>
-      <c r="H79" s="16"/>
-      <c r="I79" s="15"/>
-    </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A80" s="1"/>
-      <c r="B80" s="21"/>
-      <c r="C80" s="27"/>
-      <c r="D80" s="1"/>
-      <c r="E80" s="21"/>
-      <c r="F80" s="23"/>
-      <c r="G80" s="22"/>
-    </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A81" s="1"/>
-      <c r="B81" s="21"/>
-      <c r="C81" s="27"/>
-      <c r="D81" s="1"/>
-      <c r="E81" s="21"/>
-      <c r="F81" s="23"/>
-      <c r="G81" s="22"/>
-    </row>
-    <row r="82" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="8"/>
-      <c r="B82" s="8"/>
-      <c r="C82" s="24"/>
-      <c r="D82" s="8"/>
-      <c r="E82" s="8"/>
-      <c r="F82" s="8"/>
-      <c r="G82" s="9"/>
-      <c r="H82" s="8"/>
-      <c r="I82" s="9"/>
-    </row>
-    <row r="83" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="33" t="s">
+      <c r="E82" s="18"/>
+      <c r="F82" s="19"/>
+      <c r="G82" s="20"/>
+      <c r="H82" s="16"/>
+      <c r="I82" s="15"/>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A83" s="1"/>
+      <c r="B83" s="21"/>
+      <c r="C83" s="27"/>
+      <c r="D83" s="1"/>
+      <c r="E83" s="21"/>
+      <c r="F83" s="23"/>
+      <c r="G83" s="22"/>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A84" s="1"/>
+      <c r="B84" s="21"/>
+      <c r="C84" s="27"/>
+      <c r="D84" s="1"/>
+      <c r="E84" s="21"/>
+      <c r="F84" s="23"/>
+      <c r="G84" s="22"/>
+    </row>
+    <row r="85" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="8"/>
+      <c r="B85" s="8"/>
+      <c r="C85" s="24"/>
+      <c r="D85" s="8"/>
+      <c r="E85" s="8"/>
+      <c r="F85" s="8"/>
+      <c r="G85" s="9"/>
+      <c r="H85" s="8"/>
+      <c r="I85" s="9"/>
+    </row>
+    <row r="86" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="B83" s="34" t="s">
+      <c r="B86" s="83" t="s">
         <v>5</v>
       </c>
-      <c r="C83" s="35">
+      <c r="C86" s="34">
         <v>45588</v>
       </c>
-      <c r="D83" s="33" t="s">
+      <c r="D86" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="E83" s="34"/>
-      <c r="F83" s="34"/>
-      <c r="G83" s="7">
-        <v>45672</v>
-      </c>
-      <c r="H83" s="33" t="s">
-        <v>45</v>
-      </c>
-      <c r="I83" s="36">
-        <v>45625</v>
-      </c>
-    </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A84" s="33" t="s">
-        <v>13</v>
-      </c>
-      <c r="B84" s="34" t="s">
-        <v>5</v>
-      </c>
-      <c r="C84" s="35">
-        <v>45588</v>
-      </c>
-      <c r="D84" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="E84" s="34"/>
-      <c r="F84" s="34"/>
-      <c r="G84" s="7">
-        <v>45672</v>
-      </c>
-      <c r="H84" s="47" t="s">
-        <v>48</v>
-      </c>
-      <c r="I84" s="36">
-        <v>45625</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A85" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="B85" s="42" t="s">
-        <v>8</v>
-      </c>
-      <c r="C85" s="43">
-        <v>45475</v>
-      </c>
-      <c r="D85" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="E85" s="42">
-        <v>113</v>
-      </c>
-      <c r="F85" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="G85" s="7">
-        <v>45672</v>
-      </c>
-      <c r="H85" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="I85" s="44">
-        <v>45705</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A86" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="B86" s="42" t="s">
-        <v>8</v>
-      </c>
-      <c r="C86" s="43"/>
-      <c r="D86" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="E86" s="42">
-        <v>113</v>
-      </c>
-      <c r="F86" s="14" t="s">
-        <v>26</v>
-      </c>
+      <c r="E86" s="33"/>
+      <c r="F86" s="33"/>
       <c r="G86" s="7">
         <v>45672</v>
       </c>
-      <c r="H86" s="51" t="s">
+      <c r="H86" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="I86" s="35">
+        <v>45625</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A87" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="B87" s="83" t="s">
+        <v>5</v>
+      </c>
+      <c r="C87" s="34">
+        <v>45588</v>
+      </c>
+      <c r="D87" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="E87" s="33"/>
+      <c r="F87" s="33"/>
+      <c r="G87" s="7">
+        <v>45672</v>
+      </c>
+      <c r="H87" s="45" t="s">
+        <v>48</v>
+      </c>
+      <c r="I87" s="35">
+        <v>45625</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A88" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B88" s="83" t="s">
+        <v>8</v>
+      </c>
+      <c r="C88" s="41">
+        <v>45475</v>
+      </c>
+      <c r="D88" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="E88" s="40">
+        <v>113</v>
+      </c>
+      <c r="F88" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="G88" s="7">
+        <v>45672</v>
+      </c>
+      <c r="H88" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="I88" s="42">
+        <v>45705</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A89" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B89" s="83" t="s">
+        <v>8</v>
+      </c>
+      <c r="C89" s="41"/>
+      <c r="D89" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="E89" s="40">
+        <v>113</v>
+      </c>
+      <c r="F89" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="G89" s="7">
+        <v>45672</v>
+      </c>
+      <c r="H89" s="49" t="s">
         <v>43</v>
       </c>
-      <c r="I86" s="44">
+      <c r="I89" s="42">
         <v>45705</v>
       </c>
     </row>

--- a/mahkeme/2025-02-Dosya Listesi.xlsx
+++ b/mahkeme/2025-02-Dosya Listesi.xlsx
@@ -1,26 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24326"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\comprg\bvaagitme\yzhn\mahkeme\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\aaGitMe\yzhn\mahkeme\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D01817F7-9DD2-40BC-AB9D-7F125988F57D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B849A4C-AA34-45F6-AA0D-DB02DEFC925C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-45" yWindow="120" windowWidth="12225" windowHeight="10320" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="97">
   <si>
     <t>Dosya Listesi</t>
   </si>
@@ -271,12 +282,6 @@
     <t>cevap</t>
   </si>
   <si>
-    <t>tebliğ edildi</t>
-  </si>
-  <si>
-    <t>BAMa bşvuru son tarih</t>
-  </si>
-  <si>
     <t>tebliğ</t>
   </si>
   <si>
@@ -305,16 +310,50 @@
   </si>
   <si>
     <t>tapu, sözleşme ve taahhüt yollandı</t>
+  </si>
+  <si>
+    <t>BAMa başvuru yapıldı</t>
+  </si>
+  <si>
+    <t>dava edilmedi</t>
+  </si>
+  <si>
+    <t>kendi tahliye etti 15-01-2025</t>
+  </si>
+  <si>
+    <t>kiraya veren hmb</t>
+  </si>
+  <si>
+    <t>itiraz</t>
+  </si>
+  <si>
+    <t>8-1-2024 'te AUB'a 24000 TL kira ödemesi var</t>
+  </si>
+  <si>
+    <t>kira ödemesi AUBa yapılmış</t>
+  </si>
+  <si>
+    <t>cezanın ihtirazı kayıtla yatırıldığı</t>
+  </si>
+  <si>
+    <t>dosya açılacak</t>
+  </si>
+  <si>
+    <t>sözleşmenin fesih edildiği</t>
+  </si>
+  <si>
+    <t>önceki yıl ödemeleri AUBa yyapıldı</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="dd/mm/yy;@"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -418,6 +457,20 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="162"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <u/>
       <sz val="11"/>
       <color rgb="FFC00000"/>
       <name val="Calibri"/>
@@ -588,10 +641,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="112">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -664,7 +718,6 @@
     <xf numFmtId="164" fontId="10" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="20" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -684,11 +737,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -706,11 +754,6 @@
     <xf numFmtId="164" fontId="12" fillId="12" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="12" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="12" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="12" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -756,9 +799,39 @@
     <xf numFmtId="164" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="1" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="10" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Virgül" xfId="1" builtinId="3"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
@@ -1070,12 +1143,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O89"/>
+  <dimension ref="A1:O98"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13" customWidth="1"/>
     <col min="3" max="3" width="9.5703125" style="26" customWidth="1"/>
-    <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="4.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="4" customWidth="1"/>
     <col min="7" max="7" width="10" style="5" customWidth="1"/>
@@ -1083,7 +1156,7 @@
     <col min="9" max="9" width="13.140625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
@@ -1096,7 +1169,7 @@
       <c r="H1" s="8"/>
       <c r="I1" s="8"/>
     </row>
-    <row r="2" spans="1:9" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="8"/>
       <c r="B2" s="28" t="s">
         <v>29</v>
@@ -1119,65 +1192,69 @@
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="81" t="s">
-        <v>79</v>
+    <row r="3" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="74" t="s">
+        <v>77</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="I3" s="82">
+        <v>78</v>
+      </c>
+      <c r="I3" s="75">
         <v>45712</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="81"/>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="74"/>
       <c r="I4"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="81"/>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="74"/>
       <c r="I5"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="81"/>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="74"/>
       <c r="I6"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="81"/>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="74"/>
       <c r="I7"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="81"/>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="74"/>
       <c r="I8"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="95"/>
-      <c r="B9" s="96" t="s">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="88"/>
+      <c r="B9" s="89" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="97" t="s">
+      <c r="C9" s="90" t="s">
         <v>30</v>
       </c>
-      <c r="D9" s="96"/>
-      <c r="E9" s="98" t="s">
+      <c r="D9" s="89"/>
+      <c r="E9" s="91" t="s">
         <v>28</v>
       </c>
-      <c r="F9" s="98"/>
-      <c r="G9" s="99" t="s">
+      <c r="F9" s="91"/>
+      <c r="G9" s="92" t="s">
         <v>31</v>
       </c>
-      <c r="H9" s="96" t="s">
+      <c r="H9" s="89" t="s">
         <v>39</v>
       </c>
-      <c r="I9" s="96" t="s">
+      <c r="I9" s="89" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J9" s="101"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="83" t="s">
+      <c r="B10" s="76" t="s">
         <v>6</v>
       </c>
       <c r="C10" s="25">
@@ -1186,7 +1263,7 @@
       <c r="D10" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="52">
+      <c r="E10" s="51">
         <v>97</v>
       </c>
       <c r="F10" s="4" t="s">
@@ -1198,10 +1275,11 @@
       <c r="I10" s="6">
         <v>45705</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J10" s="101"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
-      <c r="B11" s="84" t="s">
+      <c r="B11" s="77" t="s">
         <v>2</v>
       </c>
       <c r="C11" s="25">
@@ -1210,7 +1288,7 @@
       <c r="D11" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="52">
+      <c r="E11" s="51">
         <v>178</v>
       </c>
       <c r="F11" s="4" t="s">
@@ -1222,20 +1300,22 @@
       <c r="I11" s="31">
         <v>45705</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J11" s="101"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
-      <c r="B12" s="85" t="s">
+      <c r="B12" s="78" t="s">
         <v>36</v>
       </c>
       <c r="C12" s="26">
         <v>45704</v>
       </c>
-      <c r="D12" s="63" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="D12" s="59" t="s">
+        <v>83</v>
+      </c>
+      <c r="J12" s="101"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1" t="s">
         <v>65</v>
@@ -1247,94 +1327,102 @@
         <v>59</v>
       </c>
       <c r="H13" s="1"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J13" s="101"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
-      <c r="C14" s="53"/>
+      <c r="C14" s="52"/>
       <c r="D14" s="1"/>
       <c r="H14" s="1"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J14" s="101"/>
+    </row>
+    <row r="15" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
-      <c r="C15" s="53" t="s">
+      <c r="C15" s="52" t="s">
         <v>56</v>
       </c>
-      <c r="D15" s="63" t="s">
+      <c r="D15" s="59" t="s">
         <v>61</v>
       </c>
       <c r="H15" s="1"/>
-    </row>
-    <row r="16" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J15" s="101"/>
+    </row>
+    <row r="16" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
-      <c r="C16" s="53">
-        <v>45712</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="H16" s="1"/>
-    </row>
-    <row r="17" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C16" s="81">
+        <v>45717</v>
+      </c>
+      <c r="D16" s="82" t="s">
+        <v>76</v>
+      </c>
+      <c r="E16" s="83" t="s">
+        <v>62</v>
+      </c>
+      <c r="F16" s="82"/>
+      <c r="G16" s="84"/>
+      <c r="H16" s="82" t="s">
+        <v>63</v>
+      </c>
+      <c r="I16" s="85"/>
+      <c r="J16" s="101"/>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
-      <c r="C17" s="88">
-        <v>45717</v>
-      </c>
-      <c r="D17" s="89" t="s">
-        <v>78</v>
-      </c>
-      <c r="E17" s="90" t="s">
-        <v>62</v>
-      </c>
-      <c r="F17" s="89"/>
-      <c r="G17" s="91"/>
-      <c r="H17" s="89" t="s">
-        <v>63</v>
-      </c>
-      <c r="I17" s="92"/>
+      <c r="C17" s="55"/>
+      <c r="D17" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="H17" s="1"/>
+      <c r="J17" s="101"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
-      <c r="C18" s="56"/>
+      <c r="C18" s="52"/>
       <c r="D18" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H18" s="1"/>
+      <c r="J18" s="101"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
-      <c r="C19" s="53"/>
-      <c r="D19" s="1" t="s">
-        <v>83</v>
-      </c>
+      <c r="C19" s="52"/>
+      <c r="D19" s="1"/>
       <c r="H19" s="1"/>
+      <c r="J19" s="101"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
-      <c r="C20" s="53"/>
+      <c r="C20" s="52"/>
       <c r="D20" s="1"/>
-      <c r="I20" s="93" t="s">
-        <v>84</v>
-      </c>
+      <c r="I20" s="103" t="s">
+        <v>82</v>
+      </c>
+      <c r="J20" s="101"/>
     </row>
     <row r="21" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
-      <c r="B21" s="46" t="s">
+      <c r="B21" s="98" t="s">
         <v>53</v>
       </c>
-      <c r="C21" s="47">
+      <c r="C21" s="99">
         <v>45805</v>
       </c>
-      <c r="D21" s="48">
+      <c r="D21" s="100">
         <v>0.40972222222222227</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E21" s="101" t="s">
         <v>55</v>
       </c>
-      <c r="I21"/>
+      <c r="F21" s="101"/>
+      <c r="G21" s="102"/>
+      <c r="H21" s="101"/>
+      <c r="I21" s="101"/>
+      <c r="J21" s="101"/>
     </row>
     <row r="22" spans="1:15" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
-      <c r="C22" s="53">
+      <c r="C22" s="52">
         <v>45805</v>
       </c>
       <c r="D22" s="1" t="s">
@@ -1343,43 +1431,44 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
-      <c r="C23" s="53"/>
+      <c r="C23" s="52"/>
       <c r="D23" s="1"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A24" s="95"/>
-      <c r="B24" s="96" t="s">
+      <c r="A24" s="88"/>
+      <c r="B24" s="89" t="s">
         <v>29</v>
       </c>
-      <c r="C24" s="97" t="s">
+      <c r="C24" s="90" t="s">
         <v>30</v>
       </c>
-      <c r="D24" s="96"/>
-      <c r="E24" s="98" t="s">
+      <c r="D24" s="89"/>
+      <c r="E24" s="91" t="s">
         <v>28</v>
       </c>
-      <c r="F24" s="98"/>
-      <c r="G24" s="99" t="s">
+      <c r="F24" s="91"/>
+      <c r="G24" s="92" t="s">
         <v>31</v>
       </c>
-      <c r="H24" s="96" t="s">
+      <c r="H24" s="89" t="s">
         <v>39</v>
       </c>
-      <c r="I24" s="96" t="s">
+      <c r="I24" s="89" t="s">
         <v>51</v>
       </c>
+      <c r="J24" s="101"/>
     </row>
     <row r="25" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B25" s="83" t="s">
+      <c r="B25" s="76" t="s">
         <v>4</v>
       </c>
-      <c r="C25" s="94">
+      <c r="C25" s="87">
         <v>45588</v>
       </c>
-      <c r="D25" s="52" t="s">
+      <c r="D25" s="51" t="s">
         <v>21</v>
       </c>
       <c r="E25" s="3"/>
@@ -1392,10 +1481,11 @@
       <c r="I25" s="6">
         <v>45630</v>
       </c>
+      <c r="J25" s="101"/>
     </row>
     <row r="26" spans="1:15" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4"/>
-      <c r="B26" s="83" t="s">
+      <c r="B26" s="76" t="s">
         <v>4</v>
       </c>
       <c r="C26" s="25"/>
@@ -1408,22 +1498,24 @@
       <c r="I26" s="6">
         <v>45630</v>
       </c>
+      <c r="J26" s="101"/>
     </row>
     <row r="27" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4"/>
-      <c r="B27" s="85" t="s">
+      <c r="B27" s="78" t="s">
         <v>35</v>
       </c>
-      <c r="C27" s="50">
+      <c r="C27" s="49">
         <v>45704</v>
       </c>
-      <c r="D27" s="63" t="s">
-        <v>86</v>
+      <c r="D27" s="59" t="s">
+        <v>84</v>
       </c>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
       <c r="H27" s="1"/>
       <c r="I27"/>
+      <c r="J27" s="101"/>
       <c r="M27">
         <v>200</v>
       </c>
@@ -1447,6 +1539,7 @@
         <v>59</v>
       </c>
       <c r="H28" s="1"/>
+      <c r="J28" s="101"/>
       <c r="M28">
         <v>600</v>
       </c>
@@ -1460,13 +1553,14 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
-      <c r="C29" s="53" t="s">
+      <c r="C29" s="52" t="s">
         <v>56</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>64</v>
       </c>
       <c r="H29" s="1"/>
+      <c r="J29" s="101"/>
       <c r="M29">
         <v>700</v>
       </c>
@@ -1480,13 +1574,14 @@
     </row>
     <row r="30" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
-      <c r="C30" s="53">
+      <c r="C30" s="52">
         <v>45712</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>58</v>
       </c>
       <c r="H30" s="1"/>
+      <c r="J30" s="101"/>
       <c r="O30">
         <f>SUM(O28:O29)</f>
         <v>60000</v>
@@ -1494,47 +1589,54 @@
     </row>
     <row r="31" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
-      <c r="C31" s="75">
+      <c r="C31" s="68">
         <v>45717</v>
       </c>
-      <c r="D31" s="76" t="s">
-        <v>78</v>
-      </c>
-      <c r="E31" s="77" t="s">
+      <c r="D31" s="69" t="s">
+        <v>76</v>
+      </c>
+      <c r="E31" s="70" t="s">
         <v>62</v>
       </c>
-      <c r="F31" s="76"/>
-      <c r="G31" s="78"/>
-      <c r="H31" s="76" t="s">
+      <c r="F31" s="69"/>
+      <c r="G31" s="71"/>
+      <c r="H31" s="69" t="s">
         <v>63</v>
       </c>
-      <c r="I31" s="79"/>
+      <c r="I31" s="72"/>
+      <c r="J31" s="101"/>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="C32" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F32" s="5"/>
-      <c r="G32" s="101"/>
-      <c r="H32" s="100"/>
-      <c r="I32" s="101"/>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G32" s="94"/>
+      <c r="H32" s="93"/>
+      <c r="I32" s="94"/>
+      <c r="J32" s="101"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="C33" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F33" s="5"/>
-      <c r="G33" s="101"/>
-      <c r="H33" s="100"/>
-      <c r="I33" s="101"/>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G33" s="94"/>
+      <c r="H33" s="93"/>
+      <c r="I33" s="94"/>
+      <c r="J33" s="101"/>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="H34" s="1"/>
-    </row>
-    <row r="35" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I34" s="86" t="s">
+        <v>82</v>
+      </c>
+      <c r="J34" s="101"/>
+    </row>
+    <row r="35" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
       <c r="B35" s="46" t="s">
         <v>53</v>
@@ -1542,23 +1644,28 @@
       <c r="C35" s="47">
         <v>45805</v>
       </c>
-      <c r="D35" s="54">
+      <c r="D35" s="53">
         <v>0</v>
       </c>
-      <c r="I35" s="93" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="J35" s="101"/>
+    </row>
+    <row r="36" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
-      <c r="C36" s="53">
+      <c r="B36" s="101"/>
+      <c r="C36" s="105">
         <v>45805</v>
       </c>
-      <c r="D36" s="1" t="s">
+      <c r="D36" s="2" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E36" s="101"/>
+      <c r="F36" s="101"/>
+      <c r="G36" s="102"/>
+      <c r="H36" s="101"/>
+      <c r="I36" s="102"/>
+      <c r="J36" s="101"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
@@ -1566,7 +1673,7 @@
       <c r="H37" s="1"/>
       <c r="I37"/>
     </row>
-    <row r="38" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="12"/>
       <c r="B38" s="8"/>
       <c r="C38" s="24"/>
@@ -1577,11 +1684,11 @@
       <c r="H38" s="12"/>
       <c r="I38" s="8"/>
     </row>
-    <row r="39" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B39" s="83" t="s">
+      <c r="B39" s="76" t="s">
         <v>7</v>
       </c>
       <c r="C39" s="25">
@@ -1590,7 +1697,7 @@
       <c r="D39" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E39" s="52">
+      <c r="E39" s="51">
         <v>214</v>
       </c>
       <c r="F39" s="4" t="s">
@@ -1602,12 +1709,15 @@
       <c r="I39" s="6">
         <v>45702</v>
       </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J39" s="101"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="2"/>
       <c r="B40" s="3"/>
       <c r="C40" s="25"/>
-      <c r="D40" s="4"/>
+      <c r="D40" s="95">
+        <v>158437</v>
+      </c>
       <c r="E40" s="3"/>
       <c r="F40" s="4"/>
       <c r="H40" s="14" t="s">
@@ -1616,10 +1726,11 @@
       <c r="I40" s="6">
         <v>45702</v>
       </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J40" s="101"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
-      <c r="B41" s="85" t="s">
+      <c r="B41" s="78" t="s">
         <v>33</v>
       </c>
       <c r="C41" s="26">
@@ -1630,8 +1741,9 @@
       </c>
       <c r="H41" s="1"/>
       <c r="I41"/>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J41" s="101"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="1"/>
       <c r="B42" s="1" t="s">
         <v>65</v>
@@ -1643,314 +1755,333 @@
         <v>52</v>
       </c>
       <c r="H42" s="1"/>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J42" s="101"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="1"/>
       <c r="D43" s="1" t="s">
         <v>66</v>
       </c>
       <c r="H43" s="1"/>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J43" s="101"/>
+    </row>
+    <row r="44" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
-      <c r="C44" s="53" t="s">
+      <c r="C44" s="52" t="s">
         <v>56</v>
       </c>
-      <c r="D44" s="63" t="s">
+      <c r="D44" s="59" t="s">
         <v>68</v>
       </c>
       <c r="H44" s="1"/>
-    </row>
-    <row r="45" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J44" s="101"/>
+    </row>
+    <row r="45" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
-      <c r="C45" s="53">
-        <v>45706</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="H45" s="1"/>
-    </row>
-    <row r="46" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="1"/>
-      <c r="C46" s="80">
+      <c r="C45" s="73">
         <v>45711</v>
       </c>
-      <c r="D46" s="76" t="s">
+      <c r="D45" s="69" t="s">
         <v>69</v>
       </c>
-      <c r="E46" s="76"/>
-      <c r="F46" s="76"/>
-      <c r="G46" s="78"/>
-      <c r="H46" s="76"/>
-      <c r="I46" s="79"/>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A47" s="1"/>
-      <c r="C47" s="56" t="s">
+      <c r="E45" s="69"/>
+      <c r="F45" s="69"/>
+      <c r="G45" s="71"/>
+      <c r="H45" s="69"/>
+      <c r="I45" s="72"/>
+      <c r="J45" s="101"/>
+    </row>
+    <row r="46" spans="1:10" s="97" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C46" s="55" t="s">
         <v>70</v>
       </c>
-      <c r="D47" s="1" t="s">
+      <c r="D46" s="93"/>
+      <c r="E46" s="93"/>
+      <c r="F46" s="93"/>
+      <c r="G46" s="94"/>
+      <c r="H46" s="93"/>
+      <c r="I46" s="94"/>
+      <c r="J46" s="101"/>
+    </row>
+    <row r="47" spans="1:10" s="97" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="96">
+        <v>1</v>
+      </c>
+      <c r="C47" s="55" t="s">
+        <v>89</v>
+      </c>
+      <c r="D47" s="59" t="s">
+        <v>91</v>
+      </c>
+      <c r="E47" s="93"/>
+      <c r="F47" s="93"/>
+      <c r="G47" s="94"/>
+      <c r="H47" s="93"/>
+      <c r="I47" s="94"/>
+      <c r="J47" s="101"/>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48" s="1"/>
+      <c r="D48" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="H47" s="1"/>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A48" s="1"/>
-      <c r="C48" s="56"/>
-      <c r="D48" s="1" t="s">
+      <c r="H48" s="1"/>
+      <c r="J48" s="101"/>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A49" s="1"/>
+      <c r="C49" s="55"/>
+      <c r="D49" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H48" s="1"/>
-    </row>
-    <row r="49" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="1"/>
-      <c r="B49" s="46" t="s">
+      <c r="H49" s="1"/>
+      <c r="J49" s="101"/>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A50" s="1"/>
+      <c r="C50" s="55"/>
+      <c r="D50" s="1"/>
+      <c r="H50" s="1"/>
+      <c r="J50" s="101"/>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A51" s="1"/>
+      <c r="C51" s="55"/>
+      <c r="D51" s="1"/>
+      <c r="H51" s="1"/>
+      <c r="I51" s="104" t="s">
+        <v>93</v>
+      </c>
+      <c r="J51" s="101"/>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A52" s="1"/>
+      <c r="C52" s="55"/>
+      <c r="D52" s="1"/>
+      <c r="H52" s="1"/>
+      <c r="I52" s="104" t="s">
+        <v>92</v>
+      </c>
+      <c r="J52" s="101"/>
+    </row>
+    <row r="53" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="1"/>
+      <c r="B53" s="98" t="s">
         <v>53</v>
       </c>
-      <c r="C49" s="47">
+      <c r="C53" s="99">
         <v>45792</v>
       </c>
-      <c r="D49" s="48">
+      <c r="D53" s="100">
         <v>0.39930555555555558</v>
       </c>
-      <c r="I49"/>
-    </row>
-    <row r="50" spans="1:11" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="1"/>
-      <c r="C50" s="53">
+      <c r="E53" s="101"/>
+      <c r="F53" s="101"/>
+      <c r="G53" s="102"/>
+      <c r="H53" s="101"/>
+      <c r="I53" s="101"/>
+      <c r="J53" s="101"/>
+    </row>
+    <row r="54" spans="1:11" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="1"/>
+      <c r="C54" s="52">
         <v>45792</v>
       </c>
-      <c r="D50" s="1" t="s">
+      <c r="D54" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="H50" s="1"/>
-      <c r="I50"/>
-    </row>
-    <row r="52" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="4" t="s">
+      <c r="H54" s="1"/>
+      <c r="I54"/>
+    </row>
+    <row r="56" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B52" s="83" t="s">
+      <c r="B56" s="76" t="s">
         <v>3</v>
       </c>
-      <c r="C52" s="51">
+      <c r="C56" s="50">
         <v>45603</v>
       </c>
-      <c r="D52" s="4" t="s">
+      <c r="D56" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E52" s="52">
+      <c r="E56" s="51">
         <v>156</v>
       </c>
-      <c r="F52" s="4" t="s">
+      <c r="F56" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="G52" s="6"/>
-      <c r="H52" s="1" t="s">
+      <c r="G56" s="6"/>
+      <c r="H56" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="I52" s="5">
+      <c r="I56" s="5">
         <v>45705</v>
       </c>
-      <c r="K52" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="4"/>
-      <c r="B53" s="3"/>
-      <c r="C53" s="25"/>
-      <c r="D53" s="4"/>
-      <c r="E53" s="3"/>
-      <c r="F53" s="4"/>
-      <c r="G53" s="6"/>
-      <c r="H53" s="14" t="s">
+      <c r="J56" s="101"/>
+      <c r="K56" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="4"/>
+      <c r="B57" s="3"/>
+      <c r="C57" s="25"/>
+      <c r="D57" s="4"/>
+      <c r="E57" s="3"/>
+      <c r="F57" s="4"/>
+      <c r="G57" s="6"/>
+      <c r="H57" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="I53" s="5">
+      <c r="I57" s="5">
         <v>45705</v>
       </c>
-    </row>
-    <row r="54" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="1"/>
-      <c r="B54" s="85" t="s">
-        <v>37</v>
-      </c>
-      <c r="C54" s="50">
-        <v>45704</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F54" s="1"/>
-      <c r="H54" s="1"/>
-    </row>
-    <row r="55" spans="1:11" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="1"/>
-      <c r="B55" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C55" s="26">
-        <v>45705</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="H55" s="1"/>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A56" s="1"/>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A57" s="1"/>
-      <c r="C57" s="53" t="s">
-        <v>56</v>
-      </c>
-      <c r="D57" s="63" t="s">
-        <v>68</v>
-      </c>
-      <c r="G57" s="62"/>
-      <c r="H57" s="1"/>
+      <c r="J57" s="101"/>
     </row>
     <row r="58" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1"/>
-      <c r="C58" s="53">
-        <v>45706</v>
+      <c r="B58" s="78" t="s">
+        <v>37</v>
+      </c>
+      <c r="C58" s="49">
+        <v>45704</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>58</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="F58" s="1"/>
       <c r="H58" s="1"/>
-    </row>
-    <row r="59" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J58" s="101"/>
+    </row>
+    <row r="59" spans="1:11" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1"/>
-      <c r="C59" s="80">
-        <v>45711</v>
-      </c>
-      <c r="D59" s="76" t="s">
-        <v>69</v>
-      </c>
-      <c r="E59" s="76"/>
-      <c r="F59" s="76"/>
-      <c r="G59" s="78"/>
-      <c r="H59" s="76"/>
-      <c r="I59" s="79"/>
+      <c r="B59" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C59" s="26">
+        <v>45705</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H59" s="1"/>
+      <c r="J59" s="101"/>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="1"/>
-      <c r="B60" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C60" s="55"/>
-      <c r="D60" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="H60" s="1"/>
+      <c r="J60" s="101"/>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="1"/>
-      <c r="D61" s="1" t="s">
+      <c r="C61" s="52" t="s">
+        <v>56</v>
+      </c>
+      <c r="D61" s="59" t="s">
+        <v>68</v>
+      </c>
+      <c r="G61" s="58"/>
+      <c r="H61" s="1"/>
+      <c r="J61" s="101"/>
+    </row>
+    <row r="62" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="1"/>
+      <c r="C62" s="52">
+        <v>45706</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H62" s="1"/>
+      <c r="J62" s="101"/>
+    </row>
+    <row r="63" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="1"/>
+      <c r="C63" s="73">
+        <v>45711</v>
+      </c>
+      <c r="D63" s="69" t="s">
+        <v>69</v>
+      </c>
+      <c r="E63" s="69"/>
+      <c r="F63" s="69"/>
+      <c r="G63" s="71"/>
+      <c r="H63" s="69"/>
+      <c r="I63" s="72"/>
+      <c r="J63" s="101"/>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A64" s="1"/>
+      <c r="B64" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C64" s="54"/>
+      <c r="D64" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="H64" s="1"/>
+      <c r="J64" s="101"/>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A65" s="1"/>
+      <c r="D65" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="H61" s="1"/>
-    </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A62" s="1"/>
-      <c r="D62" s="1"/>
-      <c r="H62" s="1"/>
-    </row>
-    <row r="63" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B63" s="58" t="s">
+      <c r="H65" s="1"/>
+      <c r="J65" s="101"/>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="104" t="s">
+        <v>96</v>
+      </c>
+      <c r="J66" s="101"/>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A67" s="1"/>
+      <c r="D67" s="1"/>
+      <c r="H67" s="1"/>
+      <c r="I67" s="104" t="s">
+        <v>93</v>
+      </c>
+      <c r="J67" s="101"/>
+    </row>
+    <row r="68" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B68" s="106" t="s">
         <v>53</v>
       </c>
-      <c r="C63" s="59">
+      <c r="C68" s="107">
         <v>45792</v>
       </c>
-      <c r="D63" s="60">
+      <c r="D68" s="108">
         <v>0.39583333333333331</v>
       </c>
-      <c r="I63"/>
-    </row>
-    <row r="64" spans="1:11" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B64" s="57"/>
-      <c r="C64" s="61">
+      <c r="E68" s="101"/>
+      <c r="F68" s="101"/>
+      <c r="G68" s="102"/>
+      <c r="H68" s="101"/>
+      <c r="I68" s="101"/>
+      <c r="J68" s="101"/>
+    </row>
+    <row r="69" spans="1:11" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="B69" s="56"/>
+      <c r="C69" s="57">
         <v>45792</v>
       </c>
-      <c r="D64" s="1" t="s">
+      <c r="D69" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="I64"/>
-    </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B65" s="57"/>
-      <c r="C65" s="61"/>
-      <c r="D65" s="1"/>
-      <c r="I65"/>
-    </row>
-    <row r="66" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="12"/>
-      <c r="B66" s="8"/>
-      <c r="C66" s="24"/>
-      <c r="D66" s="12"/>
-      <c r="E66" s="8"/>
-      <c r="F66" s="8"/>
-      <c r="G66" s="9"/>
-      <c r="H66" s="12"/>
-      <c r="I66" s="8"/>
-    </row>
-    <row r="67" spans="1:11" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B67" s="83" t="s">
-        <v>1</v>
-      </c>
-      <c r="C67" s="25">
-        <v>45676</v>
-      </c>
-      <c r="D67" s="52" t="s">
-        <v>21</v>
-      </c>
-      <c r="E67" s="4"/>
-      <c r="F67" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H67" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="K67" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A68" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B68" s="83" t="s">
-        <v>1</v>
-      </c>
-      <c r="C68" s="25"/>
-      <c r="D68" s="4"/>
-      <c r="E68" s="4"/>
-      <c r="F68" s="4"/>
-      <c r="H68" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="I68" s="15">
-        <v>45714</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A69" s="1"/>
-      <c r="D69" s="1"/>
-      <c r="E69" s="1"/>
-      <c r="F69" s="1"/>
-      <c r="H69" s="1"/>
+      <c r="I69"/>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B70" s="57"/>
-      <c r="C70" s="61"/>
+      <c r="B70" s="56"/>
+      <c r="C70" s="57"/>
       <c r="D70" s="1"/>
       <c r="I70"/>
     </row>
@@ -1966,312 +2097,430 @@
       <c r="I71" s="8"/>
     </row>
     <row r="72" spans="1:11" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="B72" s="83" t="s">
-        <v>10</v>
-      </c>
-      <c r="C72" s="34">
-        <v>45342</v>
-      </c>
-      <c r="D72" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="E72" s="33"/>
-      <c r="F72" s="43" t="s">
+      <c r="A72" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B72" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="C72" s="25">
+        <v>45676</v>
+      </c>
+      <c r="D72" s="51" t="s">
+        <v>21</v>
+      </c>
+      <c r="E72" s="4"/>
+      <c r="F72" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="G72" s="35"/>
-      <c r="H72" s="33"/>
-      <c r="I72" s="35"/>
+      <c r="H72" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="J72" s="101"/>
+      <c r="K72" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A73" s="32"/>
-      <c r="B73" s="86" t="s">
-        <v>24</v>
-      </c>
-      <c r="C73" s="34">
-        <v>45537</v>
-      </c>
-      <c r="D73" s="32" t="s">
-        <v>23</v>
-      </c>
-      <c r="E73" s="33"/>
-      <c r="F73" s="44" t="s">
-        <v>19</v>
-      </c>
-      <c r="G73" s="35">
-        <v>45691</v>
-      </c>
-      <c r="H73" s="33"/>
-      <c r="I73" s="35"/>
+      <c r="A73" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B73" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="C73" s="25"/>
+      <c r="D73" s="4"/>
+      <c r="E73" s="4"/>
+      <c r="F73" s="4"/>
+      <c r="H73" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="I73" s="15">
+        <v>45714</v>
+      </c>
+      <c r="J73" s="101"/>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A74" s="64"/>
-      <c r="B74" s="65"/>
-      <c r="C74" s="66"/>
-      <c r="D74" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="F74" s="5"/>
-      <c r="H74" s="5"/>
-    </row>
-    <row r="75" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="1"/>
-      <c r="C75" s="72">
-        <v>45718</v>
-      </c>
-      <c r="D75" s="73" t="s">
-        <v>76</v>
-      </c>
-      <c r="E75" s="73"/>
-      <c r="F75" s="74"/>
-      <c r="G75" s="74"/>
-      <c r="H75" s="74"/>
-      <c r="I75" s="74"/>
-    </row>
-    <row r="76" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="1"/>
-      <c r="C76" s="67">
-        <v>45733</v>
-      </c>
-      <c r="D76" s="68" t="s">
-        <v>77</v>
-      </c>
-      <c r="E76" s="68"/>
-      <c r="F76" s="69"/>
-      <c r="G76" s="69"/>
-      <c r="H76" s="70"/>
-      <c r="I76" s="71"/>
+      <c r="A74" s="96"/>
+      <c r="B74" s="97"/>
+      <c r="C74" s="110"/>
+      <c r="D74" s="96"/>
+      <c r="E74" s="96"/>
+      <c r="F74" s="96"/>
+      <c r="G74" s="111"/>
+      <c r="H74" s="96"/>
+      <c r="I74" s="104" t="s">
+        <v>94</v>
+      </c>
+      <c r="J74" s="101"/>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A75" s="96"/>
+      <c r="B75" s="97"/>
+      <c r="C75" s="110"/>
+      <c r="D75" s="96"/>
+      <c r="E75" s="96"/>
+      <c r="F75" s="96"/>
+      <c r="G75" s="111"/>
+      <c r="H75" s="96"/>
+      <c r="I75" s="111"/>
+      <c r="J75" s="101"/>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A76" s="2"/>
+      <c r="B76" s="101"/>
+      <c r="C76" s="109"/>
+      <c r="D76" s="2"/>
+      <c r="E76" s="2"/>
+      <c r="F76" s="2"/>
+      <c r="G76" s="102"/>
+      <c r="H76" s="2"/>
+      <c r="I76" s="102"/>
+      <c r="J76" s="101"/>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="1"/>
       <c r="D77" s="1"/>
-      <c r="F77" s="5"/>
-      <c r="H77" s="5"/>
-    </row>
-    <row r="78" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="12"/>
-      <c r="B78" s="8"/>
-      <c r="C78" s="24"/>
-      <c r="D78" s="12"/>
-      <c r="E78" s="8"/>
-      <c r="F78" s="9"/>
-      <c r="G78" s="9"/>
-      <c r="H78" s="9"/>
-      <c r="I78" s="9"/>
-    </row>
-    <row r="79" spans="1:11" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="B79" s="83" t="s">
-        <v>9</v>
-      </c>
-      <c r="C79" s="34">
-        <v>45438</v>
-      </c>
-      <c r="D79" s="32" t="s">
-        <v>20</v>
-      </c>
-      <c r="E79" s="33">
-        <v>0</v>
-      </c>
-      <c r="F79" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="G79" s="35"/>
-      <c r="H79" s="33"/>
-      <c r="I79" s="35"/>
-    </row>
-    <row r="80" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A80" s="32"/>
-      <c r="B80" s="87" t="s">
-        <v>17</v>
-      </c>
-      <c r="C80" s="36">
-        <v>45486</v>
+      <c r="E77" s="1"/>
+      <c r="F77" s="1"/>
+      <c r="H77" s="1"/>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B78" s="56"/>
+      <c r="C78" s="57"/>
+      <c r="D78" s="1"/>
+      <c r="I78"/>
+    </row>
+    <row r="79" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="12"/>
+      <c r="B79" s="8"/>
+      <c r="C79" s="24"/>
+      <c r="D79" s="12"/>
+      <c r="E79" s="8"/>
+      <c r="F79" s="8"/>
+      <c r="G79" s="9"/>
+      <c r="H79" s="12"/>
+      <c r="I79" s="8"/>
+    </row>
+    <row r="80" spans="1:11" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="B80" s="76" t="s">
+        <v>10</v>
+      </c>
+      <c r="C80" s="34">
+        <v>45342</v>
       </c>
       <c r="D80" s="32" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="E80" s="33"/>
-      <c r="F80" s="37" t="s">
-        <v>27</v>
-      </c>
-      <c r="G80" s="38">
-        <v>45588</v>
-      </c>
+      <c r="F80" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="G80" s="35"/>
       <c r="H80" s="33"/>
       <c r="I80" s="35"/>
     </row>
-    <row r="81" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="32"/>
-      <c r="B81" s="87" t="s">
-        <v>18</v>
-      </c>
-      <c r="C81" s="36">
-        <v>45590</v>
+      <c r="B81" s="79" t="s">
+        <v>24</v>
+      </c>
+      <c r="C81" s="34">
+        <v>45537</v>
       </c>
       <c r="D81" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="E81" s="32"/>
-      <c r="F81" s="37" t="s">
-        <v>27</v>
-      </c>
-      <c r="G81" s="38">
-        <v>45688</v>
+        <v>23</v>
+      </c>
+      <c r="E81" s="33"/>
+      <c r="F81" s="44" t="s">
+        <v>19</v>
+      </c>
+      <c r="G81" s="35">
+        <v>45691</v>
       </c>
       <c r="H81" s="33"/>
       <c r="I81" s="35"/>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A82" s="17"/>
-      <c r="B82" s="18"/>
-      <c r="C82" s="39"/>
+    <row r="82" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="60"/>
+      <c r="B82" s="61"/>
+      <c r="C82" s="62"/>
       <c r="D82" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="E82" s="18"/>
-      <c r="F82" s="19"/>
-      <c r="G82" s="20"/>
-      <c r="H82" s="16"/>
-      <c r="I82" s="15"/>
-    </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="F82" s="5"/>
+      <c r="H82" s="5"/>
+    </row>
+    <row r="83" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="1"/>
-      <c r="B83" s="21"/>
-      <c r="C83" s="27"/>
-      <c r="D83" s="1"/>
-      <c r="E83" s="21"/>
-      <c r="F83" s="23"/>
-      <c r="G83" s="22"/>
+      <c r="C83" s="63">
+        <v>45726</v>
+      </c>
+      <c r="D83" s="64" t="s">
+        <v>86</v>
+      </c>
+      <c r="E83" s="64"/>
+      <c r="F83" s="65"/>
+      <c r="G83" s="65"/>
+      <c r="H83" s="66"/>
+      <c r="I83" s="67"/>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="1"/>
-      <c r="B84" s="21"/>
-      <c r="C84" s="27"/>
       <c r="D84" s="1"/>
-      <c r="E84" s="21"/>
-      <c r="F84" s="23"/>
-      <c r="G84" s="22"/>
+      <c r="F84" s="5"/>
+      <c r="H84" s="5"/>
     </row>
     <row r="85" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="8"/>
+      <c r="A85" s="12"/>
       <c r="B85" s="8"/>
       <c r="C85" s="24"/>
-      <c r="D85" s="8"/>
+      <c r="D85" s="12"/>
       <c r="E85" s="8"/>
-      <c r="F85" s="8"/>
+      <c r="F85" s="9"/>
       <c r="G85" s="9"/>
-      <c r="H85" s="8"/>
+      <c r="H85" s="9"/>
       <c r="I85" s="9"/>
     </row>
-    <row r="86" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A86" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="B86" s="76" t="s">
+        <v>9</v>
+      </c>
+      <c r="C86" s="34">
+        <v>45438</v>
+      </c>
+      <c r="D86" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="E86" s="33">
+        <v>0</v>
+      </c>
+      <c r="F86" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="G86" s="35"/>
+      <c r="H86" s="33"/>
+      <c r="I86" s="35"/>
+    </row>
+    <row r="87" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A87" s="32"/>
+      <c r="B87" s="80" t="s">
+        <v>17</v>
+      </c>
+      <c r="C87" s="36">
+        <v>45486</v>
+      </c>
+      <c r="D87" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="E87" s="33"/>
+      <c r="F87" s="37" t="s">
+        <v>27</v>
+      </c>
+      <c r="G87" s="38">
+        <v>45588</v>
+      </c>
+      <c r="H87" s="33"/>
+      <c r="I87" s="35"/>
+    </row>
+    <row r="88" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A88" s="32"/>
+      <c r="B88" s="80" t="s">
+        <v>18</v>
+      </c>
+      <c r="C88" s="36">
+        <v>45590</v>
+      </c>
+      <c r="D88" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="E88" s="32"/>
+      <c r="F88" s="37" t="s">
+        <v>27</v>
+      </c>
+      <c r="G88" s="38">
+        <v>45688</v>
+      </c>
+      <c r="H88" s="33"/>
+      <c r="I88" s="35"/>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A89" s="17"/>
+      <c r="B89" s="18"/>
+      <c r="C89" s="39"/>
+      <c r="D89" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="E89" s="18"/>
+      <c r="F89" s="19"/>
+      <c r="G89" s="20"/>
+      <c r="H89" s="16"/>
+      <c r="I89" s="15"/>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A90" s="1"/>
+      <c r="B90" s="21"/>
+      <c r="C90" s="27"/>
+      <c r="D90" s="1"/>
+      <c r="E90" s="21"/>
+      <c r="F90" s="23"/>
+      <c r="G90" s="22"/>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A91" s="1"/>
+      <c r="B91" s="21"/>
+      <c r="C91" s="27"/>
+      <c r="D91" s="1"/>
+      <c r="E91" s="21"/>
+      <c r="F91" s="23"/>
+      <c r="G91" s="22"/>
+    </row>
+    <row r="92" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="8"/>
+      <c r="B92" s="8"/>
+      <c r="C92" s="24"/>
+      <c r="D92" s="8"/>
+      <c r="E92" s="8"/>
+      <c r="F92" s="8"/>
+      <c r="G92" s="9"/>
+      <c r="H92" s="8"/>
+      <c r="I92" s="9"/>
+    </row>
+    <row r="93" spans="1:9" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="B86" s="83" t="s">
+      <c r="B93" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="C86" s="34">
+      <c r="C93" s="34">
         <v>45588</v>
       </c>
-      <c r="D86" s="32" t="s">
+      <c r="D93" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="E86" s="33"/>
-      <c r="F86" s="33"/>
-      <c r="G86" s="7">
+      <c r="E93" s="33"/>
+      <c r="F93" s="33"/>
+      <c r="G93" s="7">
         <v>45672</v>
       </c>
-      <c r="H86" s="32" t="s">
+      <c r="H93" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="I86" s="35">
+      <c r="I93" s="35">
         <v>45625</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A87" s="32" t="s">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A94" s="32"/>
+      <c r="B94" s="76" t="s">
+        <v>88</v>
+      </c>
+      <c r="C94" s="34"/>
+      <c r="D94" s="32"/>
+      <c r="E94" s="33"/>
+      <c r="F94" s="33"/>
+      <c r="G94" s="7"/>
+      <c r="H94" s="32"/>
+      <c r="I94" s="35"/>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A95" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="B87" s="83" t="s">
+      <c r="B95" s="76" t="s">
         <v>5</v>
       </c>
-      <c r="C87" s="34">
+      <c r="C95" s="34">
         <v>45588</v>
       </c>
-      <c r="D87" s="32" t="s">
+      <c r="D95" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="E87" s="33"/>
-      <c r="F87" s="33"/>
-      <c r="G87" s="7">
+      <c r="E95" s="33"/>
+      <c r="F95" s="33"/>
+      <c r="G95" s="7">
         <v>45672</v>
       </c>
-      <c r="H87" s="45" t="s">
+      <c r="H95" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="I87" s="35">
+      <c r="I95" s="35">
         <v>45625</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A88" s="14" t="s">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A96" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="B88" s="83" t="s">
+      <c r="B96" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="C88" s="41">
+      <c r="C96" s="41">
         <v>45475</v>
       </c>
-      <c r="D88" s="14" t="s">
+      <c r="D96" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="E88" s="40">
+      <c r="E96" s="40">
         <v>113</v>
       </c>
-      <c r="F88" s="14" t="s">
+      <c r="F96" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="G88" s="7">
+      <c r="G96" s="7">
         <v>45672</v>
       </c>
-      <c r="H88" s="14" t="s">
+      <c r="H96" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="I88" s="42">
+      <c r="I96" s="42">
         <v>45705</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A89" s="14" t="s">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A97" s="14"/>
+      <c r="B97" s="76" t="s">
+        <v>87</v>
+      </c>
+      <c r="C97" s="41"/>
+      <c r="D97" s="14"/>
+      <c r="E97" s="40"/>
+      <c r="F97" s="14"/>
+      <c r="G97" s="7"/>
+      <c r="H97" s="14"/>
+      <c r="I97" s="42"/>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A98" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="B89" s="83" t="s">
+      <c r="B98" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="C89" s="41"/>
-      <c r="D89" s="14" t="s">
+      <c r="C98" s="41"/>
+      <c r="D98" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="E89" s="40">
+      <c r="E98" s="40">
         <v>113</v>
       </c>
-      <c r="F89" s="14" t="s">
+      <c r="F98" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="G89" s="7">
+      <c r="G98" s="7">
         <v>45672</v>
       </c>
-      <c r="H89" s="49" t="s">
+      <c r="H98" s="48" t="s">
         <v>43</v>
       </c>
-      <c r="I89" s="42">
+      <c r="I98" s="42">
         <v>45705</v>
       </c>
     </row>

--- a/mahkeme/2025-02-Dosya Listesi.xlsx
+++ b/mahkeme/2025-02-Dosya Listesi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\aaGitMe\yzhn\mahkeme\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B76158E-4D8A-40D3-A42C-F2D92AD24E91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C3A02FF-95A4-4836-AEE4-2BD222F42EF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="107">
   <si>
     <t>Dosya Listesi</t>
   </si>
@@ -340,6 +340,39 @@
   </si>
   <si>
     <t>önceki yıl ödemeleri AUBa yyapıldı</t>
+  </si>
+  <si>
+    <t>2025/61</t>
+  </si>
+  <si>
+    <t>hmb ceza</t>
+  </si>
+  <si>
+    <t>5. asliye ceza</t>
+  </si>
+  <si>
+    <t>Tarih</t>
+  </si>
+  <si>
+    <t>1.sulh hukuk</t>
+  </si>
+  <si>
+    <t>smt trgt</t>
+  </si>
+  <si>
+    <t>2025-560</t>
+  </si>
+  <si>
+    <t>2.sulh hukuk</t>
+  </si>
+  <si>
+    <t>slh ant</t>
+  </si>
+  <si>
+    <t>mtn çlk</t>
+  </si>
+  <si>
+    <t>2025/559</t>
   </si>
 </sst>
 </file>
@@ -687,7 +720,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="124">
+  <cellXfs count="129">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -892,6 +925,17 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="13" fillId="12" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1207,1430 +1251,1607 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J105"/>
+  <dimension ref="A1:J116"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13" customWidth="1"/>
     <col min="3" max="3" width="9.5703125" style="25" customWidth="1"/>
     <col min="4" max="4" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="4" customWidth="1"/>
     <col min="7" max="7" width="10" style="5" customWidth="1"/>
     <col min="8" max="8" width="12.28515625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13.140625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="124" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
-    </row>
-    <row r="2" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="94"/>
-      <c r="B2" s="95" t="s">
+      <c r="B1" s="125"/>
+      <c r="C1" s="126"/>
+      <c r="D1" s="125"/>
+      <c r="E1" s="125"/>
+      <c r="F1" s="125"/>
+      <c r="G1" s="92"/>
+      <c r="H1" s="125"/>
+      <c r="I1" s="125"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="124"/>
+      <c r="B2" s="125"/>
+      <c r="C2" s="126" t="s">
+        <v>99</v>
+      </c>
+      <c r="D2" s="125"/>
+      <c r="E2" s="125"/>
+      <c r="F2" s="125"/>
+      <c r="G2" s="92"/>
+      <c r="H2" s="125"/>
+      <c r="I2" s="125"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="127"/>
+      <c r="B3" s="125" t="s">
+        <v>96</v>
+      </c>
+      <c r="C3" s="25">
+        <v>45827</v>
+      </c>
+      <c r="D3" s="126" t="s">
+        <v>97</v>
+      </c>
+      <c r="E3">
+        <v>9</v>
+      </c>
+      <c r="F3">
+        <v>40</v>
+      </c>
+      <c r="H3" s="125" t="s">
+        <v>98</v>
+      </c>
+      <c r="I3" s="92"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="124"/>
+      <c r="B4" s="125" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="126">
+        <v>45805</v>
+      </c>
+      <c r="D4" s="125" t="s">
+        <v>101</v>
+      </c>
+      <c r="E4">
+        <v>9</v>
+      </c>
+      <c r="F4">
+        <v>50</v>
+      </c>
+      <c r="G4" s="125"/>
+      <c r="H4" s="125" t="s">
+        <v>100</v>
+      </c>
+      <c r="I4" s="92"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="124"/>
+      <c r="B5" s="128" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" s="126">
+        <v>45805</v>
+      </c>
+      <c r="D5" s="125" t="s">
+        <v>101</v>
+      </c>
+      <c r="E5" s="125"/>
+      <c r="F5" s="125"/>
+      <c r="G5" s="92"/>
+      <c r="H5" s="125" t="s">
+        <v>100</v>
+      </c>
+      <c r="I5" s="92"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="124"/>
+      <c r="B6" s="125" t="s">
+        <v>102</v>
+      </c>
+      <c r="C6" s="126">
+        <v>45792</v>
+      </c>
+      <c r="D6" s="125" t="s">
+        <v>104</v>
+      </c>
+      <c r="E6" s="125">
+        <v>9</v>
+      </c>
+      <c r="F6" s="125">
+        <v>35</v>
+      </c>
+      <c r="G6" s="92"/>
+      <c r="H6" s="125" t="s">
+        <v>103</v>
+      </c>
+      <c r="I6" s="125"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="124"/>
+      <c r="B7" s="128" t="s">
+        <v>106</v>
+      </c>
+      <c r="C7" s="25">
+        <v>45792</v>
+      </c>
+      <c r="D7" s="128" t="s">
+        <v>105</v>
+      </c>
+      <c r="E7" s="128">
+        <v>9</v>
+      </c>
+      <c r="F7" s="128">
+        <v>30</v>
+      </c>
+      <c r="H7" s="125" t="s">
+        <v>103</v>
+      </c>
+      <c r="I7" s="125"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="124"/>
+      <c r="B8" s="125"/>
+      <c r="C8" s="126"/>
+      <c r="D8" s="125"/>
+      <c r="E8" s="125"/>
+      <c r="F8" s="125"/>
+      <c r="G8" s="92"/>
+      <c r="H8" s="125"/>
+      <c r="I8" s="125"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="124"/>
+      <c r="B9" s="125"/>
+      <c r="C9" s="126"/>
+      <c r="D9" s="125"/>
+      <c r="E9" s="125"/>
+      <c r="F9" s="125"/>
+      <c r="G9" s="92"/>
+      <c r="H9" s="125"/>
+      <c r="I9" s="125"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="124"/>
+      <c r="B10" s="125"/>
+      <c r="C10" s="126"/>
+      <c r="D10" s="125"/>
+      <c r="E10" s="125"/>
+      <c r="F10" s="125"/>
+      <c r="G10" s="92"/>
+      <c r="H10" s="125"/>
+      <c r="I10" s="125"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="124"/>
+      <c r="B11" s="125"/>
+      <c r="C11" s="126"/>
+      <c r="D11" s="125"/>
+      <c r="E11" s="125"/>
+      <c r="F11" s="125"/>
+      <c r="G11" s="92"/>
+      <c r="H11" s="125"/>
+      <c r="I11" s="125"/>
+    </row>
+    <row r="12" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="10"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="23"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+    </row>
+    <row r="13" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="94"/>
+      <c r="B13" s="95" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="96" t="s">
+      <c r="C13" s="96" t="s">
         <v>30</v>
       </c>
-      <c r="D2" s="95"/>
-      <c r="E2" s="97" t="s">
+      <c r="D13" s="95"/>
+      <c r="E13" s="97" t="s">
         <v>28</v>
       </c>
-      <c r="F2" s="97"/>
-      <c r="G2" s="98" t="s">
+      <c r="F13" s="97"/>
+      <c r="G13" s="98" t="s">
         <v>31</v>
       </c>
-      <c r="H2" s="95" t="s">
+      <c r="H13" s="95" t="s">
         <v>39</v>
       </c>
-      <c r="I2" s="95" t="s">
+      <c r="I13" s="95" t="s">
         <v>51</v>
       </c>
-      <c r="J2" s="78"/>
-    </row>
-    <row r="3" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="61" t="s">
+      <c r="J13" s="78"/>
+    </row>
+    <row r="14" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="61" t="s">
         <v>77</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D14" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H14" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="I3" s="62">
+      <c r="I14" s="62">
         <v>45712</v>
       </c>
-      <c r="J3" s="78"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="61"/>
-      <c r="I4"/>
-      <c r="J4" s="78"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="61"/>
-      <c r="I5"/>
-      <c r="J5" s="78"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="63" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="30">
-        <v>45342</v>
-      </c>
-      <c r="D6" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="29"/>
-      <c r="F6" s="39" t="s">
-        <v>26</v>
-      </c>
-      <c r="G6" s="31"/>
-      <c r="H6" s="29"/>
-      <c r="I6" s="31"/>
-      <c r="J6" s="78"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="28"/>
-      <c r="B7" s="66" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="30">
-        <v>45537</v>
-      </c>
-      <c r="D7" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" s="29"/>
-      <c r="F7" s="40" t="s">
-        <v>19</v>
-      </c>
-      <c r="G7" s="31">
-        <v>45691</v>
-      </c>
-      <c r="H7" s="29"/>
-      <c r="I7" s="31"/>
-      <c r="J7" s="78"/>
-    </row>
-    <row r="8" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="56"/>
-      <c r="B8" s="57"/>
-      <c r="C8" s="58"/>
-      <c r="D8" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="F8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="J8" s="78"/>
-    </row>
-    <row r="9" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="1"/>
-      <c r="C9" s="121">
-        <v>45726</v>
-      </c>
-      <c r="D9" s="122" t="s">
-        <v>85</v>
-      </c>
-      <c r="E9" s="122"/>
-      <c r="F9" s="123"/>
-      <c r="G9" s="123"/>
-      <c r="H9" s="59"/>
-      <c r="I9" s="60"/>
-      <c r="J9" s="78"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="1"/>
-      <c r="C10" s="89"/>
-      <c r="D10" s="90"/>
-      <c r="E10" s="90"/>
-      <c r="F10" s="91"/>
-      <c r="G10" s="91"/>
-      <c r="H10" s="92"/>
-      <c r="I10" s="92"/>
-      <c r="J10" s="78"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="61"/>
-      <c r="I11"/>
-      <c r="J11" s="78"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="93"/>
-      <c r="B12" s="78"/>
-      <c r="C12" s="86"/>
-      <c r="D12" s="78"/>
-      <c r="E12" s="78"/>
-      <c r="F12" s="78"/>
-      <c r="G12" s="79"/>
-      <c r="H12" s="78"/>
-      <c r="I12" s="78"/>
-      <c r="J12" s="78"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="61"/>
-      <c r="I13"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="61"/>
-      <c r="I14"/>
+      <c r="J14" s="78"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="61"/>
       <c r="I15"/>
+      <c r="J15" s="78"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="99"/>
-      <c r="B16" s="100" t="s">
-        <v>29</v>
-      </c>
-      <c r="C16" s="101" t="s">
-        <v>30</v>
-      </c>
-      <c r="D16" s="100"/>
-      <c r="E16" s="102" t="s">
-        <v>28</v>
-      </c>
-      <c r="F16" s="102"/>
-      <c r="G16" s="103" t="s">
-        <v>31</v>
-      </c>
-      <c r="H16" s="100" t="s">
-        <v>39</v>
-      </c>
-      <c r="I16" s="100" t="s">
-        <v>51</v>
-      </c>
+      <c r="A16" s="61"/>
+      <c r="I16"/>
       <c r="J16" s="78"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>12</v>
+      <c r="A17" s="28" t="s">
+        <v>16</v>
       </c>
       <c r="B17" s="63" t="s">
-        <v>6</v>
-      </c>
-      <c r="C17" s="24">
-        <v>45475</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="47">
-        <v>97</v>
-      </c>
-      <c r="F17" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="30">
+        <v>45342</v>
+      </c>
+      <c r="D17" s="28" t="s">
+        <v>14</v>
+      </c>
+      <c r="E17" s="29"/>
+      <c r="F17" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="H17" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="I17" s="6">
-        <v>45705</v>
-      </c>
+      <c r="G17" s="31"/>
+      <c r="H17" s="29"/>
+      <c r="I17" s="31"/>
       <c r="J17" s="78"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="4"/>
-      <c r="B18" s="64" t="s">
-        <v>2</v>
-      </c>
-      <c r="C18" s="24">
-        <v>45604</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="47">
-        <v>178</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H18" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="I18" s="27">
-        <v>45705</v>
-      </c>
+      <c r="A18" s="28"/>
+      <c r="B18" s="66" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" s="30">
+        <v>45537</v>
+      </c>
+      <c r="D18" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" s="29"/>
+      <c r="F18" s="40" t="s">
+        <v>19</v>
+      </c>
+      <c r="G18" s="31">
+        <v>45691</v>
+      </c>
+      <c r="H18" s="29"/>
+      <c r="I18" s="31"/>
       <c r="J18" s="78"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="1"/>
-      <c r="B19" s="65" t="s">
-        <v>36</v>
-      </c>
-      <c r="C19" s="25">
-        <v>45704</v>
-      </c>
-      <c r="D19" s="55" t="s">
-        <v>82</v>
-      </c>
+    <row r="19" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="56"/>
+      <c r="B19" s="57"/>
+      <c r="C19" s="58"/>
+      <c r="D19" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="F19" s="5"/>
+      <c r="H19" s="5"/>
       <c r="J19" s="78"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
-      <c r="B20" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C20" s="25">
-        <v>45705</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="H20" s="1"/>
+      <c r="C20" s="121">
+        <v>45726</v>
+      </c>
+      <c r="D20" s="122" t="s">
+        <v>85</v>
+      </c>
+      <c r="E20" s="122"/>
+      <c r="F20" s="123"/>
+      <c r="G20" s="123"/>
+      <c r="H20" s="59"/>
+      <c r="I20" s="60"/>
       <c r="J20" s="78"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
-      <c r="C21" s="48"/>
-      <c r="D21" s="1"/>
-      <c r="H21" s="1"/>
+      <c r="C21" s="89"/>
+      <c r="D21" s="90"/>
+      <c r="E21" s="90"/>
+      <c r="F21" s="91"/>
+      <c r="G21" s="91"/>
+      <c r="H21" s="92"/>
+      <c r="I21" s="92"/>
       <c r="J21" s="78"/>
     </row>
-    <row r="22" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="1"/>
-      <c r="C22" s="48" t="s">
-        <v>56</v>
-      </c>
-      <c r="D22" s="55" t="s">
-        <v>61</v>
-      </c>
-      <c r="H22" s="1"/>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="61"/>
+      <c r="I22"/>
       <c r="J22" s="78"/>
     </row>
-    <row r="23" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="1"/>
-      <c r="C23" s="116">
-        <v>45717</v>
-      </c>
-      <c r="D23" s="117" t="s">
-        <v>76</v>
-      </c>
-      <c r="E23" s="118" t="s">
-        <v>62</v>
-      </c>
-      <c r="F23" s="117"/>
-      <c r="G23" s="119"/>
-      <c r="H23" s="117" t="s">
-        <v>63</v>
-      </c>
-      <c r="I23" s="120"/>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="93"/>
+      <c r="B23" s="78"/>
+      <c r="C23" s="86"/>
+      <c r="D23" s="78"/>
+      <c r="E23" s="78"/>
+      <c r="F23" s="78"/>
+      <c r="G23" s="79"/>
+      <c r="H23" s="78"/>
+      <c r="I23" s="78"/>
       <c r="J23" s="78"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="1"/>
-      <c r="C24" s="51"/>
-      <c r="D24" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="H24" s="1"/>
-      <c r="J24" s="78"/>
+      <c r="A24" s="61"/>
+      <c r="I24"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="1"/>
-      <c r="C25" s="48"/>
-      <c r="D25" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="H25" s="1"/>
-      <c r="J25" s="78"/>
+      <c r="A25" s="61"/>
+      <c r="I25"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="1"/>
-      <c r="C26" s="48"/>
-      <c r="D26" s="1"/>
-      <c r="H26" s="1"/>
-      <c r="J26" s="78"/>
+      <c r="A26" s="61"/>
+      <c r="I26"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" s="1"/>
-      <c r="C27" s="48"/>
-      <c r="D27" s="1"/>
-      <c r="I27" s="80" t="s">
-        <v>81</v>
+      <c r="A27" s="99"/>
+      <c r="B27" s="100" t="s">
+        <v>29</v>
+      </c>
+      <c r="C27" s="101" t="s">
+        <v>30</v>
+      </c>
+      <c r="D27" s="100"/>
+      <c r="E27" s="102" t="s">
+        <v>28</v>
+      </c>
+      <c r="F27" s="102"/>
+      <c r="G27" s="103" t="s">
+        <v>31</v>
+      </c>
+      <c r="H27" s="100" t="s">
+        <v>39</v>
+      </c>
+      <c r="I27" s="100" t="s">
+        <v>51</v>
       </c>
       <c r="J27" s="78"/>
     </row>
-    <row r="28" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="1"/>
-      <c r="B28" s="75" t="s">
-        <v>53</v>
-      </c>
-      <c r="C28" s="76">
-        <v>45805</v>
-      </c>
-      <c r="D28" s="77">
-        <v>0.40972222222222227</v>
-      </c>
-      <c r="E28" s="78" t="s">
-        <v>55</v>
-      </c>
-      <c r="F28" s="78"/>
-      <c r="G28" s="79"/>
-      <c r="H28" s="78"/>
-      <c r="I28" s="78"/>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B28" s="63" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="24">
+        <v>45475</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="47">
+        <v>97</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="I28" s="6">
+        <v>45705</v>
+      </c>
       <c r="J28" s="78"/>
     </row>
-    <row r="29" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="1"/>
-      <c r="C29" s="48">
-        <v>45805</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>57</v>
-      </c>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="4"/>
+      <c r="B29" s="64" t="s">
+        <v>2</v>
+      </c>
+      <c r="C29" s="24">
+        <v>45604</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="47">
+        <v>178</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="I29" s="27">
+        <v>45705</v>
+      </c>
+      <c r="J29" s="78"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
-      <c r="C30" s="48"/>
-      <c r="D30" s="1"/>
+      <c r="B30" s="65" t="s">
+        <v>36</v>
+      </c>
+      <c r="C30" s="25">
+        <v>45704</v>
+      </c>
+      <c r="D30" s="55" t="s">
+        <v>82</v>
+      </c>
+      <c r="J30" s="78"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" s="99"/>
-      <c r="B31" s="100" t="s">
-        <v>29</v>
-      </c>
-      <c r="C31" s="101" t="s">
-        <v>30</v>
-      </c>
-      <c r="D31" s="100"/>
-      <c r="E31" s="102" t="s">
-        <v>28</v>
-      </c>
-      <c r="F31" s="102"/>
-      <c r="G31" s="103" t="s">
-        <v>31</v>
-      </c>
-      <c r="H31" s="100" t="s">
-        <v>39</v>
-      </c>
-      <c r="I31" s="100" t="s">
-        <v>51</v>
-      </c>
+      <c r="A31" s="1"/>
+      <c r="B31" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C31" s="25">
+        <v>45705</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H31" s="1"/>
       <c r="J31" s="78"/>
     </row>
-    <row r="32" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B32" s="63" t="s">
-        <v>4</v>
-      </c>
-      <c r="C32" s="69">
-        <v>45588</v>
-      </c>
-      <c r="D32" s="47" t="s">
-        <v>21</v>
-      </c>
-      <c r="E32" s="3"/>
-      <c r="F32" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H32" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="I32" s="6">
-        <v>45630</v>
-      </c>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="1"/>
+      <c r="C32" s="48"/>
+      <c r="D32" s="1"/>
+      <c r="H32" s="1"/>
       <c r="J32" s="78"/>
     </row>
-    <row r="33" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="4"/>
-      <c r="B33" s="63" t="s">
-        <v>4</v>
-      </c>
-      <c r="C33" s="24"/>
-      <c r="D33" s="4"/>
-      <c r="E33" s="3"/>
-      <c r="F33" s="4"/>
-      <c r="H33" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="I33" s="6">
-        <v>45630</v>
-      </c>
+    <row r="33" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="1"/>
+      <c r="C33" s="48" t="s">
+        <v>56</v>
+      </c>
+      <c r="D33" s="55" t="s">
+        <v>61</v>
+      </c>
+      <c r="H33" s="1"/>
       <c r="J33" s="78"/>
     </row>
     <row r="34" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="4"/>
-      <c r="B34" s="65" t="s">
-        <v>35</v>
-      </c>
-      <c r="C34" s="45">
-        <v>45704</v>
-      </c>
-      <c r="D34" s="55" t="s">
-        <v>83</v>
-      </c>
-      <c r="E34" s="1"/>
-      <c r="F34" s="1"/>
-      <c r="H34" s="1"/>
-      <c r="I34"/>
+      <c r="A34" s="1"/>
+      <c r="C34" s="116">
+        <v>45717</v>
+      </c>
+      <c r="D34" s="117" t="s">
+        <v>76</v>
+      </c>
+      <c r="E34" s="118" t="s">
+        <v>62</v>
+      </c>
+      <c r="F34" s="117"/>
+      <c r="G34" s="119"/>
+      <c r="H34" s="117" t="s">
+        <v>63</v>
+      </c>
+      <c r="I34" s="120"/>
       <c r="J34" s="78"/>
     </row>
-    <row r="35" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
-      <c r="B35" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C35" s="25">
-        <v>45709</v>
-      </c>
+      <c r="C35" s="51"/>
       <c r="D35" s="1" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="H35" s="1"/>
       <c r="J35" s="78"/>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
-      <c r="C36" s="48" t="s">
-        <v>56</v>
-      </c>
+      <c r="C36" s="48"/>
       <c r="D36" s="1" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="H36" s="1"/>
       <c r="J36" s="78"/>
     </row>
-    <row r="37" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
-      <c r="C37" s="48">
-        <v>45712</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>58</v>
-      </c>
+      <c r="C37" s="48"/>
+      <c r="D37" s="1"/>
       <c r="H37" s="1"/>
       <c r="J37" s="78"/>
     </row>
-    <row r="38" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
-      <c r="C38" s="110">
-        <v>45717</v>
-      </c>
-      <c r="D38" s="111" t="s">
-        <v>76</v>
-      </c>
-      <c r="E38" s="112" t="s">
-        <v>62</v>
-      </c>
-      <c r="F38" s="111"/>
-      <c r="G38" s="113"/>
-      <c r="H38" s="111" t="s">
-        <v>63</v>
-      </c>
-      <c r="I38" s="114"/>
+      <c r="C38" s="48"/>
+      <c r="D38" s="1"/>
+      <c r="I38" s="80" t="s">
+        <v>81</v>
+      </c>
       <c r="J38" s="78"/>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
-      <c r="C39" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="F39" s="5"/>
-      <c r="G39" s="71"/>
-      <c r="H39" s="70"/>
-      <c r="I39" s="71"/>
+      <c r="B39" s="75" t="s">
+        <v>53</v>
+      </c>
+      <c r="C39" s="76">
+        <v>45805</v>
+      </c>
+      <c r="D39" s="77">
+        <v>0.40972222222222227</v>
+      </c>
+      <c r="E39" s="78" t="s">
+        <v>55</v>
+      </c>
+      <c r="F39" s="78"/>
+      <c r="G39" s="79"/>
+      <c r="H39" s="78"/>
+      <c r="I39" s="78"/>
       <c r="J39" s="78"/>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1"/>
-      <c r="C40" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="F40" s="5"/>
-      <c r="G40" s="71"/>
-      <c r="H40" s="70"/>
-      <c r="I40" s="71"/>
-      <c r="J40" s="78"/>
+      <c r="C40" s="48">
+        <v>45805</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
-      <c r="H41" s="1"/>
-      <c r="I41" s="68" t="s">
-        <v>81</v>
-      </c>
-      <c r="J41" s="78"/>
-    </row>
-    <row r="42" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="1"/>
-      <c r="B42" s="42" t="s">
-        <v>53</v>
-      </c>
-      <c r="C42" s="43">
-        <v>45805</v>
-      </c>
-      <c r="D42" s="49">
-        <v>0</v>
+      <c r="C41" s="48"/>
+      <c r="D41" s="1"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="99"/>
+      <c r="B42" s="100" t="s">
+        <v>29</v>
+      </c>
+      <c r="C42" s="101" t="s">
+        <v>30</v>
+      </c>
+      <c r="D42" s="100"/>
+      <c r="E42" s="102" t="s">
+        <v>28</v>
+      </c>
+      <c r="F42" s="102"/>
+      <c r="G42" s="103" t="s">
+        <v>31</v>
+      </c>
+      <c r="H42" s="100" t="s">
+        <v>39</v>
+      </c>
+      <c r="I42" s="100" t="s">
+        <v>51</v>
       </c>
       <c r="J42" s="78"/>
     </row>
-    <row r="43" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="1"/>
-      <c r="B43" s="78"/>
-      <c r="C43" s="82">
-        <v>45805</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E43" s="78"/>
-      <c r="F43" s="78"/>
-      <c r="G43" s="79"/>
-      <c r="H43" s="78"/>
-      <c r="I43" s="79"/>
+    <row r="43" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B43" s="63" t="s">
+        <v>4</v>
+      </c>
+      <c r="C43" s="69">
+        <v>45588</v>
+      </c>
+      <c r="D43" s="47" t="s">
+        <v>21</v>
+      </c>
+      <c r="E43" s="3"/>
+      <c r="F43" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I43" s="6">
+        <v>45630</v>
+      </c>
       <c r="J43" s="78"/>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A44" s="73"/>
-      <c r="B44" s="74"/>
-      <c r="C44" s="108"/>
-      <c r="D44" s="73"/>
-      <c r="E44" s="74"/>
-      <c r="F44" s="74"/>
-      <c r="G44" s="88"/>
-      <c r="H44" s="74"/>
-      <c r="I44" s="88"/>
-      <c r="J44" s="74"/>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A45" s="73"/>
-      <c r="B45" s="74"/>
-      <c r="C45" s="108"/>
-      <c r="D45" s="73"/>
-      <c r="E45" s="74"/>
-      <c r="F45" s="74"/>
-      <c r="G45" s="88"/>
-      <c r="H45" s="74"/>
-      <c r="I45" s="88"/>
-      <c r="J45" s="74"/>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="4"/>
+      <c r="B44" s="63" t="s">
+        <v>4</v>
+      </c>
+      <c r="C44" s="24"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="3"/>
+      <c r="F44" s="4"/>
+      <c r="H44" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="I44" s="6">
+        <v>45630</v>
+      </c>
+      <c r="J44" s="78"/>
+    </row>
+    <row r="45" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="4"/>
+      <c r="B45" s="65" t="s">
+        <v>35</v>
+      </c>
+      <c r="C45" s="45">
+        <v>45704</v>
+      </c>
+      <c r="D45" s="55" t="s">
+        <v>83</v>
+      </c>
+      <c r="E45" s="1"/>
+      <c r="F45" s="1"/>
+      <c r="H45" s="1"/>
+      <c r="I45"/>
+      <c r="J45" s="78"/>
+    </row>
+    <row r="46" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1"/>
-      <c r="D46" s="1"/>
-      <c r="E46" s="1"/>
-      <c r="F46" s="1"/>
+      <c r="B46" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C46" s="25">
+        <v>45709</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>59</v>
+      </c>
       <c r="H46" s="1"/>
-      <c r="I46"/>
+      <c r="J46" s="78"/>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A47" s="99"/>
-      <c r="B47" s="100" t="s">
-        <v>29</v>
-      </c>
-      <c r="C47" s="101" t="s">
-        <v>30</v>
-      </c>
-      <c r="D47" s="100"/>
-      <c r="E47" s="102" t="s">
-        <v>28</v>
-      </c>
-      <c r="F47" s="102"/>
-      <c r="G47" s="103" t="s">
-        <v>31</v>
-      </c>
-      <c r="H47" s="100" t="s">
-        <v>39</v>
-      </c>
-      <c r="I47" s="100" t="s">
-        <v>51</v>
-      </c>
+      <c r="A47" s="1"/>
+      <c r="C47" s="48" t="s">
+        <v>56</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="H47" s="1"/>
       <c r="J47" s="78"/>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A48" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B48" s="63" t="s">
-        <v>7</v>
-      </c>
-      <c r="C48" s="24">
-        <v>45475</v>
-      </c>
-      <c r="D48" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E48" s="47">
-        <v>214</v>
-      </c>
-      <c r="F48" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H48" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="I48" s="6">
-        <v>45702</v>
-      </c>
+    <row r="48" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="1"/>
+      <c r="C48" s="48">
+        <v>45712</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H48" s="1"/>
       <c r="J48" s="78"/>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A49" s="2"/>
-      <c r="B49" s="3"/>
-      <c r="C49" s="24"/>
-      <c r="D49" s="72">
-        <v>158437</v>
-      </c>
-      <c r="E49" s="3"/>
-      <c r="F49" s="4"/>
-      <c r="H49" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="I49" s="6">
-        <v>45702</v>
-      </c>
+    <row r="49" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="1"/>
+      <c r="C49" s="110">
+        <v>45717</v>
+      </c>
+      <c r="D49" s="111" t="s">
+        <v>76</v>
+      </c>
+      <c r="E49" s="112" t="s">
+        <v>62</v>
+      </c>
+      <c r="F49" s="111"/>
+      <c r="G49" s="113"/>
+      <c r="H49" s="111" t="s">
+        <v>63</v>
+      </c>
+      <c r="I49" s="114"/>
       <c r="J49" s="78"/>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="1"/>
-      <c r="B50" s="65" t="s">
-        <v>33</v>
-      </c>
-      <c r="C50" s="25">
-        <v>45704</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="H50" s="1"/>
-      <c r="I50"/>
+      <c r="C50" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F50" s="5"/>
+      <c r="G50" s="71"/>
+      <c r="H50" s="70"/>
+      <c r="I50" s="71"/>
       <c r="J50" s="78"/>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="1"/>
-      <c r="B51" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C51" s="25">
-        <v>45705</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="H51" s="1"/>
+      <c r="C51" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F51" s="5"/>
+      <c r="G51" s="71"/>
+      <c r="H51" s="70"/>
+      <c r="I51" s="71"/>
       <c r="J51" s="78"/>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="1"/>
-      <c r="D52" s="1" t="s">
-        <v>66</v>
-      </c>
       <c r="H52" s="1"/>
+      <c r="I52" s="68" t="s">
+        <v>81</v>
+      </c>
       <c r="J52" s="78"/>
     </row>
     <row r="53" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1"/>
-      <c r="C53" s="48" t="s">
-        <v>56</v>
-      </c>
-      <c r="D53" s="55" t="s">
-        <v>68</v>
-      </c>
-      <c r="H53" s="1"/>
+      <c r="B53" s="42" t="s">
+        <v>53</v>
+      </c>
+      <c r="C53" s="43">
+        <v>45805</v>
+      </c>
+      <c r="D53" s="49">
+        <v>0</v>
+      </c>
       <c r="J53" s="78"/>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1"/>
-      <c r="C54" s="104">
-        <v>45711</v>
-      </c>
-      <c r="D54" s="105" t="s">
-        <v>69</v>
-      </c>
-      <c r="E54" s="105"/>
-      <c r="F54" s="105"/>
-      <c r="G54" s="106"/>
-      <c r="H54" s="105"/>
-      <c r="I54" s="107"/>
+      <c r="B54" s="78"/>
+      <c r="C54" s="82">
+        <v>45805</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E54" s="78"/>
+      <c r="F54" s="78"/>
+      <c r="G54" s="79"/>
+      <c r="H54" s="78"/>
+      <c r="I54" s="79"/>
       <c r="J54" s="78"/>
     </row>
-    <row r="55" spans="1:10" s="74" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C55" s="51" t="s">
-        <v>70</v>
-      </c>
-      <c r="D55" s="70"/>
-      <c r="E55" s="70"/>
-      <c r="F55" s="70"/>
-      <c r="G55" s="71"/>
-      <c r="H55" s="70"/>
-      <c r="I55" s="71"/>
-      <c r="J55" s="78"/>
-    </row>
-    <row r="56" spans="1:10" s="74" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="73">
-        <v>1</v>
-      </c>
-      <c r="C56" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="D56" s="55" t="s">
-        <v>90</v>
-      </c>
-      <c r="E56" s="70"/>
-      <c r="F56" s="70"/>
-      <c r="G56" s="71"/>
-      <c r="H56" s="70"/>
-      <c r="I56" s="71"/>
-      <c r="J56" s="78"/>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A55" s="73"/>
+      <c r="B55" s="74"/>
+      <c r="C55" s="108"/>
+      <c r="D55" s="73"/>
+      <c r="E55" s="74"/>
+      <c r="F55" s="74"/>
+      <c r="G55" s="88"/>
+      <c r="H55" s="74"/>
+      <c r="I55" s="88"/>
+      <c r="J55" s="74"/>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A56" s="73"/>
+      <c r="B56" s="74"/>
+      <c r="C56" s="108"/>
+      <c r="D56" s="73"/>
+      <c r="E56" s="74"/>
+      <c r="F56" s="74"/>
+      <c r="G56" s="88"/>
+      <c r="H56" s="74"/>
+      <c r="I56" s="88"/>
+      <c r="J56" s="74"/>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="1"/>
-      <c r="D57" s="1" t="s">
-        <v>71</v>
-      </c>
+      <c r="D57" s="1"/>
+      <c r="E57" s="1"/>
+      <c r="F57" s="1"/>
       <c r="H57" s="1"/>
-      <c r="J57" s="78"/>
+      <c r="I57"/>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A58" s="1"/>
-      <c r="C58" s="51"/>
-      <c r="D58" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H58" s="1"/>
+      <c r="A58" s="99"/>
+      <c r="B58" s="100" t="s">
+        <v>29</v>
+      </c>
+      <c r="C58" s="101" t="s">
+        <v>30</v>
+      </c>
+      <c r="D58" s="100"/>
+      <c r="E58" s="102" t="s">
+        <v>28</v>
+      </c>
+      <c r="F58" s="102"/>
+      <c r="G58" s="103" t="s">
+        <v>31</v>
+      </c>
+      <c r="H58" s="100" t="s">
+        <v>39</v>
+      </c>
+      <c r="I58" s="100" t="s">
+        <v>51</v>
+      </c>
       <c r="J58" s="78"/>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A59" s="1"/>
-      <c r="C59" s="51"/>
-      <c r="D59" s="1"/>
-      <c r="H59" s="1"/>
+      <c r="A59" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B59" s="63" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59" s="24">
+        <v>45475</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E59" s="47">
+        <v>214</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H59" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I59" s="6">
+        <v>45702</v>
+      </c>
       <c r="J59" s="78"/>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A60" s="1"/>
-      <c r="C60" s="51"/>
-      <c r="D60" s="1"/>
-      <c r="H60" s="1"/>
-      <c r="I60" s="81" t="s">
-        <v>92</v>
+      <c r="A60" s="2"/>
+      <c r="B60" s="3"/>
+      <c r="C60" s="24"/>
+      <c r="D60" s="72">
+        <v>158437</v>
+      </c>
+      <c r="E60" s="3"/>
+      <c r="F60" s="4"/>
+      <c r="H60" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="I60" s="6">
+        <v>45702</v>
       </c>
       <c r="J60" s="78"/>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="1"/>
-      <c r="C61" s="51"/>
-      <c r="D61" s="1"/>
+      <c r="B61" s="65" t="s">
+        <v>33</v>
+      </c>
+      <c r="C61" s="25">
+        <v>45704</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>54</v>
+      </c>
       <c r="H61" s="1"/>
-      <c r="I61" s="81" t="s">
-        <v>91</v>
-      </c>
+      <c r="I61"/>
       <c r="J61" s="78"/>
     </row>
-    <row r="62" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="1"/>
-      <c r="B62" s="75" t="s">
-        <v>53</v>
-      </c>
-      <c r="C62" s="109">
-        <v>45792</v>
-      </c>
-      <c r="D62" s="77">
-        <v>0.39930555555555558</v>
-      </c>
-      <c r="E62" s="78"/>
-      <c r="F62" s="78"/>
-      <c r="G62" s="79"/>
-      <c r="H62" s="78"/>
-      <c r="I62" s="78"/>
+      <c r="B62" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C62" s="25">
+        <v>45705</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H62" s="1"/>
       <c r="J62" s="78"/>
     </row>
-    <row r="63" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="1"/>
-      <c r="C63" s="48">
-        <v>45792</v>
-      </c>
       <c r="D63" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H63" s="1"/>
-      <c r="I63"/>
-    </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J63" s="78"/>
+    </row>
+    <row r="64" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="1"/>
-      <c r="C64" s="48"/>
-      <c r="D64" s="1"/>
+      <c r="C64" s="48" t="s">
+        <v>56</v>
+      </c>
+      <c r="D64" s="55" t="s">
+        <v>68</v>
+      </c>
       <c r="H64" s="1"/>
-      <c r="I64"/>
+      <c r="J64" s="78"/>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A65" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B65" s="63" t="s">
+      <c r="A65" s="1"/>
+      <c r="C65" s="104">
+        <v>45711</v>
+      </c>
+      <c r="D65" s="105" t="s">
+        <v>69</v>
+      </c>
+      <c r="E65" s="105"/>
+      <c r="F65" s="105"/>
+      <c r="G65" s="106"/>
+      <c r="H65" s="105"/>
+      <c r="I65" s="107"/>
+      <c r="J65" s="78"/>
+    </row>
+    <row r="66" spans="1:10" s="74" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C66" s="51" t="s">
+        <v>70</v>
+      </c>
+      <c r="D66" s="70"/>
+      <c r="E66" s="70"/>
+      <c r="F66" s="70"/>
+      <c r="G66" s="71"/>
+      <c r="H66" s="70"/>
+      <c r="I66" s="71"/>
+      <c r="J66" s="78"/>
+    </row>
+    <row r="67" spans="1:10" s="74" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="73">
         <v>1</v>
       </c>
-      <c r="C65" s="24">
-        <v>45676</v>
-      </c>
-      <c r="D65" s="47" t="s">
-        <v>21</v>
-      </c>
-      <c r="E65" s="4"/>
-      <c r="F65" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H65" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="J65" s="78"/>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A66" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B66" s="63" t="s">
-        <v>1</v>
-      </c>
-      <c r="C66" s="24"/>
-      <c r="D66" s="4"/>
-      <c r="E66" s="4"/>
-      <c r="F66" s="4"/>
-      <c r="H66" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="I66" s="14">
-        <v>45714</v>
-      </c>
-      <c r="J66" s="78"/>
-    </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A67" s="73"/>
-      <c r="B67" s="74"/>
-      <c r="C67" s="87"/>
-      <c r="D67" s="73"/>
-      <c r="E67" s="73"/>
-      <c r="F67" s="73"/>
-      <c r="G67" s="88"/>
-      <c r="H67" s="73"/>
+      <c r="C67" s="51" t="s">
+        <v>88</v>
+      </c>
+      <c r="D67" s="55" t="s">
+        <v>90</v>
+      </c>
+      <c r="E67" s="70"/>
+      <c r="F67" s="70"/>
+      <c r="G67" s="71"/>
+      <c r="H67" s="70"/>
+      <c r="I67" s="71"/>
       <c r="J67" s="78"/>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A68" s="73"/>
-      <c r="B68" s="74"/>
-      <c r="C68" s="87"/>
-      <c r="D68" s="73"/>
-      <c r="E68" s="73"/>
-      <c r="F68" s="73"/>
-      <c r="G68" s="88"/>
-      <c r="H68" s="73"/>
-      <c r="I68" s="81" t="s">
-        <v>93</v>
-      </c>
+      <c r="A68" s="1"/>
+      <c r="D68" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H68" s="1"/>
       <c r="J68" s="78"/>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A69" s="2"/>
-      <c r="B69" s="78"/>
-      <c r="C69" s="86"/>
-      <c r="D69" s="2"/>
-      <c r="E69" s="2"/>
-      <c r="F69" s="2"/>
-      <c r="G69" s="79"/>
-      <c r="H69" s="2"/>
-      <c r="I69" s="79"/>
+      <c r="A69" s="1"/>
+      <c r="C69" s="51"/>
+      <c r="D69" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H69" s="1"/>
       <c r="J69" s="78"/>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" s="1"/>
-      <c r="C70" s="48"/>
+      <c r="C70" s="51"/>
       <c r="D70" s="1"/>
       <c r="H70" s="1"/>
-      <c r="I70"/>
+      <c r="J70" s="78"/>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" s="1"/>
-      <c r="C71" s="48"/>
+      <c r="C71" s="51"/>
       <c r="D71" s="1"/>
       <c r="H71" s="1"/>
-      <c r="I71"/>
+      <c r="I71" s="81" t="s">
+        <v>92</v>
+      </c>
+      <c r="J71" s="78"/>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" s="1"/>
-      <c r="C72" s="48"/>
+      <c r="C72" s="51"/>
       <c r="D72" s="1"/>
       <c r="H72" s="1"/>
-      <c r="I72"/>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I72" s="81" t="s">
+        <v>91</v>
+      </c>
+      <c r="J72" s="78"/>
+    </row>
+    <row r="73" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="1"/>
-      <c r="C73" s="48"/>
-      <c r="D73" s="1"/>
-      <c r="H73" s="1"/>
-      <c r="I73"/>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A74" s="99"/>
-      <c r="B74" s="100" t="s">
-        <v>29</v>
-      </c>
-      <c r="C74" s="101" t="s">
-        <v>30</v>
-      </c>
-      <c r="D74" s="100"/>
-      <c r="E74" s="102" t="s">
-        <v>28</v>
-      </c>
-      <c r="F74" s="102"/>
-      <c r="G74" s="103" t="s">
-        <v>31</v>
-      </c>
-      <c r="H74" s="100" t="s">
-        <v>39</v>
-      </c>
-      <c r="I74" s="100" t="s">
-        <v>51</v>
-      </c>
-      <c r="J74" s="78"/>
-    </row>
-    <row r="75" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B75" s="63" t="s">
-        <v>3</v>
-      </c>
-      <c r="C75" s="46">
-        <v>45603</v>
-      </c>
-      <c r="D75" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E75" s="47">
-        <v>156</v>
-      </c>
-      <c r="F75" s="4" t="s">
+      <c r="B73" s="75" t="s">
+        <v>53</v>
+      </c>
+      <c r="C73" s="109">
+        <v>45792</v>
+      </c>
+      <c r="D73" s="77">
+        <v>0.39930555555555558</v>
+      </c>
+      <c r="E73" s="78"/>
+      <c r="F73" s="78"/>
+      <c r="G73" s="79"/>
+      <c r="H73" s="78"/>
+      <c r="I73" s="78"/>
+      <c r="J73" s="78"/>
+    </row>
+    <row r="74" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="1"/>
+      <c r="C74" s="48">
+        <v>45792</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="H74" s="1"/>
+      <c r="I74"/>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A75" s="1"/>
+      <c r="C75" s="48"/>
+      <c r="D75" s="1"/>
+      <c r="H75" s="1"/>
+      <c r="I75"/>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A76" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B76" s="63" t="s">
+        <v>1</v>
+      </c>
+      <c r="C76" s="24">
+        <v>45676</v>
+      </c>
+      <c r="D76" s="47" t="s">
+        <v>21</v>
+      </c>
+      <c r="E76" s="4"/>
+      <c r="F76" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="G75" s="6"/>
-      <c r="H75" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="I75" s="5">
-        <v>45705</v>
-      </c>
-      <c r="J75" s="78"/>
-    </row>
-    <row r="76" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="4"/>
-      <c r="B76" s="3"/>
-      <c r="C76" s="24"/>
-      <c r="D76" s="4"/>
-      <c r="E76" s="3"/>
-      <c r="F76" s="4"/>
-      <c r="G76" s="6"/>
-      <c r="H76" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="I76" s="5">
-        <v>45705</v>
+      <c r="H76" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="J76" s="78"/>
     </row>
-    <row r="77" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="1"/>
-      <c r="B77" s="65" t="s">
-        <v>37</v>
-      </c>
-      <c r="C77" s="45">
-        <v>45704</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F77" s="1"/>
-      <c r="H77" s="1"/>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A77" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B77" s="63" t="s">
+        <v>1</v>
+      </c>
+      <c r="C77" s="24"/>
+      <c r="D77" s="4"/>
+      <c r="E77" s="4"/>
+      <c r="F77" s="4"/>
+      <c r="H77" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="I77" s="14">
+        <v>45714</v>
+      </c>
       <c r="J77" s="78"/>
     </row>
-    <row r="78" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="1"/>
-      <c r="B78" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C78" s="25">
-        <v>45705</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="H78" s="1"/>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A78" s="73"/>
+      <c r="B78" s="74"/>
+      <c r="C78" s="87"/>
+      <c r="D78" s="73"/>
+      <c r="E78" s="73"/>
+      <c r="F78" s="73"/>
+      <c r="G78" s="88"/>
+      <c r="H78" s="73"/>
       <c r="J78" s="78"/>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A79" s="1"/>
+      <c r="A79" s="73"/>
+      <c r="B79" s="74"/>
+      <c r="C79" s="87"/>
+      <c r="D79" s="73"/>
+      <c r="E79" s="73"/>
+      <c r="F79" s="73"/>
+      <c r="G79" s="88"/>
+      <c r="H79" s="73"/>
+      <c r="I79" s="81" t="s">
+        <v>93</v>
+      </c>
       <c r="J79" s="78"/>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A80" s="1"/>
-      <c r="C80" s="48" t="s">
-        <v>56</v>
-      </c>
-      <c r="D80" s="55" t="s">
-        <v>68</v>
-      </c>
-      <c r="G80" s="54"/>
-      <c r="H80" s="1"/>
+      <c r="A80" s="2"/>
+      <c r="B80" s="78"/>
+      <c r="C80" s="86"/>
+      <c r="D80" s="2"/>
+      <c r="E80" s="2"/>
+      <c r="F80" s="2"/>
+      <c r="G80" s="79"/>
+      <c r="H80" s="2"/>
+      <c r="I80" s="79"/>
       <c r="J80" s="78"/>
     </row>
-    <row r="81" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" s="1"/>
-      <c r="C81" s="48">
-        <v>45706</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>58</v>
-      </c>
+      <c r="C81" s="48"/>
+      <c r="D81" s="1"/>
       <c r="H81" s="1"/>
-      <c r="J81" s="78"/>
-    </row>
-    <row r="82" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I81"/>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" s="1"/>
-      <c r="C82" s="115">
-        <v>45711</v>
-      </c>
-      <c r="D82" s="111" t="s">
-        <v>69</v>
-      </c>
-      <c r="E82" s="111"/>
-      <c r="F82" s="111"/>
-      <c r="G82" s="113"/>
-      <c r="H82" s="111"/>
-      <c r="I82" s="114"/>
-      <c r="J82" s="78"/>
+      <c r="C82" s="48"/>
+      <c r="D82" s="1"/>
+      <c r="H82" s="1"/>
+      <c r="I82"/>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" s="1"/>
-      <c r="B83" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C83" s="50"/>
-      <c r="D83" s="1" t="s">
-        <v>74</v>
-      </c>
+      <c r="C83" s="48"/>
+      <c r="D83" s="1"/>
       <c r="H83" s="1"/>
-      <c r="J83" s="78"/>
+      <c r="I83"/>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" s="1"/>
-      <c r="D84" s="1" t="s">
+      <c r="C84" s="48"/>
+      <c r="D84" s="1"/>
+      <c r="H84" s="1"/>
+      <c r="I84"/>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A85" s="99"/>
+      <c r="B85" s="100" t="s">
+        <v>29</v>
+      </c>
+      <c r="C85" s="101" t="s">
+        <v>30</v>
+      </c>
+      <c r="D85" s="100"/>
+      <c r="E85" s="102" t="s">
+        <v>28</v>
+      </c>
+      <c r="F85" s="102"/>
+      <c r="G85" s="103" t="s">
+        <v>31</v>
+      </c>
+      <c r="H85" s="100" t="s">
+        <v>39</v>
+      </c>
+      <c r="I85" s="100" t="s">
+        <v>51</v>
+      </c>
+      <c r="J85" s="78"/>
+    </row>
+    <row r="86" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B86" s="63" t="s">
+        <v>3</v>
+      </c>
+      <c r="C86" s="46">
+        <v>45603</v>
+      </c>
+      <c r="D86" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E86" s="47">
+        <v>156</v>
+      </c>
+      <c r="F86" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G86" s="6"/>
+      <c r="H86" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I86" s="5">
+        <v>45705</v>
+      </c>
+      <c r="J86" s="78"/>
+    </row>
+    <row r="87" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="4"/>
+      <c r="B87" s="3"/>
+      <c r="C87" s="24"/>
+      <c r="D87" s="4"/>
+      <c r="E87" s="3"/>
+      <c r="F87" s="4"/>
+      <c r="G87" s="6"/>
+      <c r="H87" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="I87" s="5">
+        <v>45705</v>
+      </c>
+      <c r="J87" s="78"/>
+    </row>
+    <row r="88" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="1"/>
+      <c r="B88" s="65" t="s">
+        <v>37</v>
+      </c>
+      <c r="C88" s="45">
+        <v>45704</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F88" s="1"/>
+      <c r="H88" s="1"/>
+      <c r="J88" s="78"/>
+    </row>
+    <row r="89" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="1"/>
+      <c r="B89" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C89" s="25">
+        <v>45705</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H89" s="1"/>
+      <c r="J89" s="78"/>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A90" s="1"/>
+      <c r="J90" s="78"/>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A91" s="1"/>
+      <c r="C91" s="48" t="s">
+        <v>56</v>
+      </c>
+      <c r="D91" s="55" t="s">
+        <v>68</v>
+      </c>
+      <c r="G91" s="54"/>
+      <c r="H91" s="1"/>
+      <c r="J91" s="78"/>
+    </row>
+    <row r="92" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="1"/>
+      <c r="C92" s="48">
+        <v>45706</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H92" s="1"/>
+      <c r="J92" s="78"/>
+    </row>
+    <row r="93" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="1"/>
+      <c r="C93" s="115">
+        <v>45711</v>
+      </c>
+      <c r="D93" s="111" t="s">
+        <v>69</v>
+      </c>
+      <c r="E93" s="111"/>
+      <c r="F93" s="111"/>
+      <c r="G93" s="113"/>
+      <c r="H93" s="111"/>
+      <c r="I93" s="114"/>
+      <c r="J93" s="78"/>
+    </row>
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A94" s="1"/>
+      <c r="B94" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C94" s="50"/>
+      <c r="D94" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="H94" s="1"/>
+      <c r="J94" s="78"/>
+    </row>
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A95" s="1"/>
+      <c r="D95" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="H84" s="1"/>
-      <c r="J84" s="78"/>
-    </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A85" s="1"/>
-      <c r="D85" s="1"/>
-      <c r="H85" s="1"/>
-      <c r="I85" s="81" t="s">
+      <c r="H95" s="1"/>
+      <c r="J95" s="78"/>
+    </row>
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A96" s="1"/>
+      <c r="D96" s="1"/>
+      <c r="H96" s="1"/>
+      <c r="I96" s="81" t="s">
         <v>95</v>
       </c>
-      <c r="J85" s="78"/>
-    </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A86" s="1"/>
-      <c r="D86" s="1"/>
-      <c r="H86" s="1"/>
-      <c r="I86" s="81" t="s">
+      <c r="J96" s="78"/>
+    </row>
+    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A97" s="1"/>
+      <c r="D97" s="1"/>
+      <c r="H97" s="1"/>
+      <c r="I97" s="81" t="s">
         <v>92</v>
       </c>
-      <c r="J86" s="78"/>
-    </row>
-    <row r="87" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B87" s="83" t="s">
+      <c r="J97" s="78"/>
+    </row>
+    <row r="98" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B98" s="83" t="s">
         <v>53</v>
       </c>
-      <c r="C87" s="84">
+      <c r="C98" s="84">
         <v>45792</v>
       </c>
-      <c r="D87" s="85">
+      <c r="D98" s="85">
         <v>0.39583333333333331</v>
       </c>
-      <c r="E87" s="78"/>
-      <c r="F87" s="78"/>
-      <c r="G87" s="79"/>
-      <c r="H87" s="78"/>
-      <c r="I87" s="78"/>
-      <c r="J87" s="78"/>
-    </row>
-    <row r="88" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B88" s="52"/>
-      <c r="C88" s="53">
+      <c r="E98" s="78"/>
+      <c r="F98" s="78"/>
+      <c r="G98" s="79"/>
+      <c r="H98" s="78"/>
+      <c r="I98" s="78"/>
+      <c r="J98" s="78"/>
+    </row>
+    <row r="99" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="B99" s="52"/>
+      <c r="C99" s="53">
         <v>45792</v>
       </c>
-      <c r="D88" s="1" t="s">
+      <c r="D99" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="I88"/>
-    </row>
-    <row r="89" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="8"/>
-      <c r="B89" s="8"/>
-      <c r="C89" s="23"/>
-      <c r="D89" s="8"/>
-      <c r="E89" s="8"/>
-      <c r="F89" s="8"/>
-      <c r="G89" s="9"/>
-      <c r="H89" s="8"/>
-      <c r="I89" s="9"/>
-    </row>
-    <row r="90" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="28" t="s">
+      <c r="I99"/>
+    </row>
+    <row r="100" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="8"/>
+      <c r="B100" s="8"/>
+      <c r="C100" s="23"/>
+      <c r="D100" s="8"/>
+      <c r="E100" s="8"/>
+      <c r="F100" s="8"/>
+      <c r="G100" s="9"/>
+      <c r="H100" s="8"/>
+      <c r="I100" s="9"/>
+    </row>
+    <row r="101" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="B90" s="63" t="s">
+      <c r="B101" s="63" t="s">
         <v>5</v>
       </c>
-      <c r="C90" s="30">
+      <c r="C101" s="30">
         <v>45588</v>
       </c>
-      <c r="D90" s="28" t="s">
+      <c r="D101" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="E90" s="29"/>
-      <c r="F90" s="29"/>
-      <c r="G90" s="7">
+      <c r="E101" s="29"/>
+      <c r="F101" s="29"/>
+      <c r="G101" s="7">
         <v>45672</v>
       </c>
-      <c r="H90" s="28" t="s">
+      <c r="H101" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="I90" s="31">
+      <c r="I101" s="31">
         <v>45625</v>
       </c>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A91" s="28"/>
-      <c r="B91" s="63" t="s">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A102" s="28"/>
+      <c r="B102" s="63" t="s">
         <v>87</v>
       </c>
-      <c r="C91" s="30"/>
-      <c r="D91" s="28"/>
-      <c r="E91" s="29"/>
-      <c r="F91" s="29"/>
-      <c r="G91" s="7"/>
-      <c r="H91" s="28"/>
-      <c r="I91" s="31"/>
-    </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A92" s="28" t="s">
+      <c r="C102" s="30"/>
+      <c r="D102" s="28"/>
+      <c r="E102" s="29"/>
+      <c r="F102" s="29"/>
+      <c r="G102" s="7"/>
+      <c r="H102" s="28"/>
+      <c r="I102" s="31"/>
+    </row>
+    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A103" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="B92" s="63" t="s">
+      <c r="B103" s="63" t="s">
         <v>5</v>
       </c>
-      <c r="C92" s="30">
+      <c r="C103" s="30">
         <v>45588</v>
       </c>
-      <c r="D92" s="28" t="s">
+      <c r="D103" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="E92" s="29"/>
-      <c r="F92" s="29"/>
-      <c r="G92" s="7">
+      <c r="E103" s="29"/>
+      <c r="F103" s="29"/>
+      <c r="G103" s="7">
         <v>45672</v>
       </c>
-      <c r="H92" s="41" t="s">
+      <c r="H103" s="41" t="s">
         <v>48</v>
       </c>
-      <c r="I92" s="31">
+      <c r="I103" s="31">
         <v>45625</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A93" s="13" t="s">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A104" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="B93" s="63" t="s">
+      <c r="B104" s="63" t="s">
         <v>8</v>
       </c>
-      <c r="C93" s="37">
+      <c r="C104" s="37">
         <v>45475</v>
       </c>
-      <c r="D93" s="13" t="s">
+      <c r="D104" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E93" s="36">
+      <c r="E104" s="36">
         <v>113</v>
       </c>
-      <c r="F93" s="13" t="s">
+      <c r="F104" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="G93" s="7">
+      <c r="G104" s="7">
         <v>45672</v>
       </c>
-      <c r="H93" s="13" t="s">
+      <c r="H104" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="I93" s="38">
+      <c r="I104" s="38">
         <v>45705</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A94" s="13"/>
-      <c r="B94" s="63" t="s">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A105" s="13"/>
+      <c r="B105" s="63" t="s">
         <v>86</v>
       </c>
-      <c r="C94" s="37"/>
-      <c r="D94" s="13"/>
-      <c r="E94" s="36"/>
-      <c r="F94" s="13"/>
-      <c r="G94" s="7"/>
-      <c r="H94" s="13"/>
-      <c r="I94" s="38"/>
-    </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A95" s="13" t="s">
+      <c r="C105" s="37"/>
+      <c r="D105" s="13"/>
+      <c r="E105" s="36"/>
+      <c r="F105" s="13"/>
+      <c r="G105" s="7"/>
+      <c r="H105" s="13"/>
+      <c r="I105" s="38"/>
+    </row>
+    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A106" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="B95" s="63" t="s">
+      <c r="B106" s="63" t="s">
         <v>8</v>
       </c>
-      <c r="C95" s="37"/>
-      <c r="D95" s="13" t="s">
+      <c r="C106" s="37"/>
+      <c r="D106" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E95" s="36">
+      <c r="E106" s="36">
         <v>113</v>
       </c>
-      <c r="F95" s="13" t="s">
+      <c r="F106" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="G95" s="7">
+      <c r="G106" s="7">
         <v>45672</v>
       </c>
-      <c r="H95" s="44" t="s">
+      <c r="H106" s="44" t="s">
         <v>43</v>
       </c>
-      <c r="I95" s="38">
+      <c r="I106" s="38">
         <v>45705</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="11"/>
-      <c r="B99" s="8"/>
-      <c r="C99" s="23"/>
-      <c r="D99" s="11"/>
-      <c r="E99" s="8"/>
-      <c r="F99" s="9"/>
-      <c r="G99" s="9"/>
-      <c r="H99" s="9"/>
-      <c r="I99" s="9"/>
-    </row>
-    <row r="100" spans="1:9" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="28" t="s">
+    <row r="110" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A110" s="11"/>
+      <c r="B110" s="8"/>
+      <c r="C110" s="23"/>
+      <c r="D110" s="11"/>
+      <c r="E110" s="8"/>
+      <c r="F110" s="9"/>
+      <c r="G110" s="9"/>
+      <c r="H110" s="9"/>
+      <c r="I110" s="9"/>
+    </row>
+    <row r="111" spans="1:10" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="B100" s="63" t="s">
+      <c r="B111" s="63" t="s">
         <v>9</v>
       </c>
-      <c r="C100" s="30">
+      <c r="C111" s="30">
         <v>45438</v>
       </c>
-      <c r="D100" s="28" t="s">
+      <c r="D111" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="E100" s="29">
+      <c r="E111" s="29">
         <v>0</v>
       </c>
-      <c r="F100" s="12" t="s">
+      <c r="F111" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="G100" s="31"/>
-      <c r="H100" s="29"/>
-      <c r="I100" s="31"/>
-    </row>
-    <row r="101" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A101" s="28"/>
-      <c r="B101" s="67" t="s">
+      <c r="G111" s="31"/>
+      <c r="H111" s="29"/>
+      <c r="I111" s="31"/>
+    </row>
+    <row r="112" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A112" s="28"/>
+      <c r="B112" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="C101" s="32">
+      <c r="C112" s="32">
         <v>45486</v>
       </c>
-      <c r="D101" s="28" t="s">
+      <c r="D112" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="E101" s="29"/>
-      <c r="F101" s="33" t="s">
+      <c r="E112" s="29"/>
+      <c r="F112" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="G101" s="34">
+      <c r="G112" s="34">
         <v>45588</v>
       </c>
-      <c r="H101" s="29"/>
-      <c r="I101" s="31"/>
-    </row>
-    <row r="102" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A102" s="28"/>
-      <c r="B102" s="67" t="s">
+      <c r="H112" s="29"/>
+      <c r="I112" s="31"/>
+    </row>
+    <row r="113" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A113" s="28"/>
+      <c r="B113" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="C102" s="32">
+      <c r="C113" s="32">
         <v>45590</v>
       </c>
-      <c r="D102" s="28" t="s">
+      <c r="D113" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="E102" s="28"/>
-      <c r="F102" s="33" t="s">
+      <c r="E113" s="28"/>
+      <c r="F113" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="G102" s="34">
+      <c r="G113" s="34">
         <v>45688</v>
       </c>
-      <c r="H102" s="29"/>
-      <c r="I102" s="31"/>
-    </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A103" s="16"/>
-      <c r="B103" s="17"/>
-      <c r="C103" s="35"/>
-      <c r="D103" s="16" t="s">
+      <c r="H113" s="29"/>
+      <c r="I113" s="31"/>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A114" s="16"/>
+      <c r="B114" s="17"/>
+      <c r="C114" s="35"/>
+      <c r="D114" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="E103" s="17"/>
-      <c r="F103" s="18"/>
-      <c r="G103" s="19"/>
-      <c r="H103" s="15"/>
-      <c r="I103" s="14"/>
-    </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A104" s="1"/>
-      <c r="B104" s="20"/>
-      <c r="C104" s="26"/>
-      <c r="D104" s="1"/>
-      <c r="E104" s="20"/>
-      <c r="F104" s="22"/>
-      <c r="G104" s="21"/>
-    </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A105" s="1"/>
-      <c r="B105" s="20"/>
-      <c r="C105" s="26"/>
-      <c r="D105" s="1"/>
-      <c r="E105" s="20"/>
-      <c r="F105" s="22"/>
-      <c r="G105" s="21"/>
+      <c r="E114" s="17"/>
+      <c r="F114" s="18"/>
+      <c r="G114" s="19"/>
+      <c r="H114" s="15"/>
+      <c r="I114" s="14"/>
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A115" s="1"/>
+      <c r="B115" s="20"/>
+      <c r="C115" s="26"/>
+      <c r="D115" s="1"/>
+      <c r="E115" s="20"/>
+      <c r="F115" s="22"/>
+      <c r="G115" s="21"/>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A116" s="1"/>
+      <c r="B116" s="20"/>
+      <c r="C116" s="26"/>
+      <c r="D116" s="1"/>
+      <c r="E116" s="20"/>
+      <c r="F116" s="22"/>
+      <c r="G116" s="21"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/mahkeme/2025-02-Dosya Listesi.xlsx
+++ b/mahkeme/2025-02-Dosya Listesi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\aaGitMe\yzhn\mahkeme\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C3A02FF-95A4-4836-AEE4-2BD222F42EF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{376551AE-B91C-4240-8626-444BAAE66197}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="120">
   <si>
     <t>Dosya Listesi</t>
   </si>
@@ -374,6 +374,45 @@
   <si>
     <t>2025/559</t>
   </si>
+  <si>
+    <t>sözl aslı verilecek</t>
+  </si>
+  <si>
+    <t>imza</t>
+  </si>
+  <si>
+    <t>hsp hrkt ve no</t>
+  </si>
+  <si>
+    <t>duruşma</t>
+  </si>
+  <si>
+    <t>sulh hukuk</t>
+  </si>
+  <si>
+    <t>327.mdd</t>
+  </si>
+  <si>
+    <t>itrz.ipt</t>
+  </si>
+  <si>
+    <t>dosya</t>
+  </si>
+  <si>
+    <t>açılacak</t>
+  </si>
+  <si>
+    <t>kesinleşti</t>
+  </si>
+  <si>
+    <t>çıktı</t>
+  </si>
+  <si>
+    <t>bam</t>
+  </si>
+  <si>
+    <t>dava</t>
+  </si>
 </sst>
 </file>
 
@@ -383,7 +422,7 @@
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="dd/mm/yy;@"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -398,14 +437,6 @@
       <b/>
       <sz val="11"/>
       <color theme="7" tint="0.79998168889431442"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="162"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FFFFFF00"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="162"/>
@@ -436,14 +467,6 @@
       <u/>
       <sz val="11"/>
       <color theme="7" tint="0.79998168889431442"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="162"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="162"/>
@@ -508,15 +531,84 @@
       <charset val="162"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="162"/>
+    </font>
+    <font>
       <b/>
+      <u/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="162"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color theme="5" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="162"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="5" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="162"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="5" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="162"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="5" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="162"/>
+    </font>
+    <font>
       <sz val="12"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="162"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFFF00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="162"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFFFF00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="162"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="162"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -601,8 +693,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -715,12 +813,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="129">
+  <cellXfs count="167">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -728,24 +835,16 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -755,7 +854,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -765,14 +864,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="4" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -780,35 +871,31 @@
     <xf numFmtId="164" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="20" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="20" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -816,7 +903,7 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="16" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
@@ -824,91 +911,71 @@
     <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="1" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="10" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="12" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="12" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -919,23 +986,119 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="13" fillId="12" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="13" fillId="12" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="12" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="11" fillId="12" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="16" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="20" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="8" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="8" fillId="15" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="15" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="15" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="18" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="20" fontId="18" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="22" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="24" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="15" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1251,11 +1414,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J116"/>
+  <dimension ref="A1:J118"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="3" max="3" width="9.5703125" style="25" customWidth="1"/>
+    <col min="3" max="3" width="10.28515625" style="19" customWidth="1"/>
     <col min="4" max="4" width="11.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="4" customWidth="1"/>
@@ -1265,1179 +1428,1248 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="124" t="s">
+      <c r="A1" s="101" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="125"/>
-      <c r="C1" s="126"/>
-      <c r="D1" s="125"/>
-      <c r="E1" s="125"/>
-      <c r="F1" s="125"/>
-      <c r="G1" s="92"/>
-      <c r="H1" s="125"/>
-      <c r="I1" s="125"/>
+      <c r="B1" s="102"/>
+      <c r="C1" s="103"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="72"/>
+      <c r="H1" s="102"/>
+      <c r="I1" s="102"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="124"/>
-      <c r="B2" s="125"/>
-      <c r="C2" s="126" t="s">
+      <c r="A2" s="101"/>
+      <c r="B2" s="139" t="s">
+        <v>114</v>
+      </c>
+      <c r="C2" s="103" t="s">
         <v>99</v>
       </c>
-      <c r="D2" s="125"/>
-      <c r="E2" s="125"/>
-      <c r="F2" s="125"/>
-      <c r="G2" s="92"/>
-      <c r="H2" s="125"/>
-      <c r="I2" s="125"/>
+      <c r="D2" s="102"/>
+      <c r="E2" s="102"/>
+      <c r="F2" s="102"/>
+      <c r="G2" s="72"/>
+      <c r="H2" s="102"/>
+      <c r="I2" s="102"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="127"/>
-      <c r="B3" s="125" t="s">
+      <c r="A3" s="101"/>
+      <c r="B3" s="102"/>
+      <c r="C3" s="103"/>
+      <c r="D3" s="102"/>
+      <c r="E3" s="102"/>
+      <c r="F3" s="102"/>
+      <c r="G3" s="72"/>
+      <c r="H3" s="102"/>
+      <c r="I3" s="102"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="101"/>
+      <c r="B4" s="143" t="s">
+        <v>115</v>
+      </c>
+      <c r="C4" s="103"/>
+      <c r="D4" s="139" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="102"/>
+      <c r="F4" s="102"/>
+      <c r="G4" s="139" t="s">
+        <v>112</v>
+      </c>
+      <c r="H4" s="139" t="s">
+        <v>111</v>
+      </c>
+      <c r="I4" s="102"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="101"/>
+      <c r="B5" s="143" t="s">
+        <v>115</v>
+      </c>
+      <c r="C5" s="61" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="102" t="s">
+        <v>104</v>
+      </c>
+      <c r="E5" s="102"/>
+      <c r="F5" s="102"/>
+      <c r="G5" s="140" t="s">
+        <v>113</v>
+      </c>
+      <c r="H5" s="139" t="s">
+        <v>111</v>
+      </c>
+      <c r="I5" s="102"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="101"/>
+      <c r="B6" s="102"/>
+      <c r="C6" s="103"/>
+      <c r="D6" s="102"/>
+      <c r="E6" s="102"/>
+      <c r="F6" s="102"/>
+      <c r="G6" s="72"/>
+      <c r="H6" s="102"/>
+      <c r="I6" s="102"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="101"/>
+      <c r="B7" s="141" t="s">
+        <v>106</v>
+      </c>
+      <c r="C7" s="19">
+        <v>45939</v>
+      </c>
+      <c r="D7" s="105" t="s">
+        <v>105</v>
+      </c>
+      <c r="E7" s="105">
+        <v>9</v>
+      </c>
+      <c r="F7" s="105">
+        <v>30</v>
+      </c>
+      <c r="H7" s="102" t="s">
+        <v>103</v>
+      </c>
+      <c r="I7" s="102"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="101"/>
+      <c r="B8" s="141" t="s">
+        <v>102</v>
+      </c>
+      <c r="C8" s="103">
+        <v>45939</v>
+      </c>
+      <c r="D8" s="102" t="s">
+        <v>104</v>
+      </c>
+      <c r="E8" s="102">
+        <v>9</v>
+      </c>
+      <c r="F8" s="102">
+        <v>40</v>
+      </c>
+      <c r="G8" s="72"/>
+      <c r="H8" s="102" t="s">
+        <v>103</v>
+      </c>
+      <c r="I8" s="102"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="101"/>
+      <c r="B9" s="102"/>
+      <c r="C9" s="103"/>
+      <c r="D9" s="102"/>
+      <c r="E9" s="102"/>
+      <c r="F9" s="102"/>
+      <c r="G9" s="72"/>
+      <c r="H9" s="102"/>
+      <c r="I9" s="102"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="104"/>
+      <c r="I10" s="72"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="101"/>
+      <c r="B11" s="142" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="103">
+        <v>45805</v>
+      </c>
+      <c r="D11" s="102" t="s">
+        <v>101</v>
+      </c>
+      <c r="E11">
+        <v>9</v>
+      </c>
+      <c r="F11">
+        <v>50</v>
+      </c>
+      <c r="G11" s="102"/>
+      <c r="H11" s="102" t="s">
+        <v>100</v>
+      </c>
+      <c r="I11" s="72"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="101"/>
+      <c r="B12" s="142" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="103">
+        <v>45805</v>
+      </c>
+      <c r="D12" s="102" t="s">
+        <v>101</v>
+      </c>
+      <c r="E12" s="102"/>
+      <c r="F12" s="102"/>
+      <c r="G12" s="72"/>
+      <c r="H12" s="102" t="s">
+        <v>100</v>
+      </c>
+      <c r="I12" s="72"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="101"/>
+      <c r="B13" s="142" t="s">
         <v>96</v>
       </c>
-      <c r="C3" s="25">
+      <c r="C13" s="19">
         <v>45827</v>
       </c>
-      <c r="D3" s="126" t="s">
+      <c r="D13" s="103" t="s">
         <v>97</v>
       </c>
-      <c r="E3">
+      <c r="E13">
         <v>9</v>
       </c>
-      <c r="F3">
+      <c r="F13">
         <v>40</v>
       </c>
-      <c r="H3" s="125" t="s">
+      <c r="H13" s="102" t="s">
         <v>98</v>
       </c>
-      <c r="I3" s="92"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="124"/>
-      <c r="B4" s="125" t="s">
-        <v>36</v>
-      </c>
-      <c r="C4" s="126">
-        <v>45805</v>
-      </c>
-      <c r="D4" s="125" t="s">
-        <v>101</v>
-      </c>
-      <c r="E4">
-        <v>9</v>
-      </c>
-      <c r="F4">
-        <v>50</v>
-      </c>
-      <c r="G4" s="125"/>
-      <c r="H4" s="125" t="s">
-        <v>100</v>
-      </c>
-      <c r="I4" s="92"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="124"/>
-      <c r="B5" s="128" t="s">
-        <v>35</v>
-      </c>
-      <c r="C5" s="126">
-        <v>45805</v>
-      </c>
-      <c r="D5" s="125" t="s">
-        <v>101</v>
-      </c>
-      <c r="E5" s="125"/>
-      <c r="F5" s="125"/>
-      <c r="G5" s="92"/>
-      <c r="H5" s="125" t="s">
-        <v>100</v>
-      </c>
-      <c r="I5" s="92"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="124"/>
-      <c r="B6" s="125" t="s">
-        <v>102</v>
-      </c>
-      <c r="C6" s="126">
-        <v>45792</v>
-      </c>
-      <c r="D6" s="125" t="s">
-        <v>104</v>
-      </c>
-      <c r="E6" s="125">
-        <v>9</v>
-      </c>
-      <c r="F6" s="125">
-        <v>35</v>
-      </c>
-      <c r="G6" s="92"/>
-      <c r="H6" s="125" t="s">
-        <v>103</v>
-      </c>
-      <c r="I6" s="125"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="124"/>
-      <c r="B7" s="128" t="s">
-        <v>106</v>
-      </c>
-      <c r="C7" s="25">
-        <v>45792</v>
-      </c>
-      <c r="D7" s="128" t="s">
-        <v>105</v>
-      </c>
-      <c r="E7" s="128">
-        <v>9</v>
-      </c>
-      <c r="F7" s="128">
+      <c r="I13" s="102"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="101"/>
+      <c r="I14" s="102"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="49"/>
+      <c r="I15"/>
+      <c r="J15" s="61"/>
+    </row>
+    <row r="16" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="127"/>
+      <c r="B16" s="128" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" s="129" t="s">
         <v>30</v>
       </c>
-      <c r="H7" s="125" t="s">
-        <v>103</v>
-      </c>
-      <c r="I7" s="125"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="124"/>
-      <c r="B8" s="125"/>
-      <c r="C8" s="126"/>
-      <c r="D8" s="125"/>
-      <c r="E8" s="125"/>
-      <c r="F8" s="125"/>
-      <c r="G8" s="92"/>
-      <c r="H8" s="125"/>
-      <c r="I8" s="125"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="124"/>
-      <c r="B9" s="125"/>
-      <c r="C9" s="126"/>
-      <c r="D9" s="125"/>
-      <c r="E9" s="125"/>
-      <c r="F9" s="125"/>
-      <c r="G9" s="92"/>
-      <c r="H9" s="125"/>
-      <c r="I9" s="125"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="124"/>
-      <c r="B10" s="125"/>
-      <c r="C10" s="126"/>
-      <c r="D10" s="125"/>
-      <c r="E10" s="125"/>
-      <c r="F10" s="125"/>
-      <c r="G10" s="92"/>
-      <c r="H10" s="125"/>
-      <c r="I10" s="125"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="124"/>
-      <c r="B11" s="125"/>
-      <c r="C11" s="126"/>
-      <c r="D11" s="125"/>
-      <c r="E11" s="125"/>
-      <c r="F11" s="125"/>
-      <c r="G11" s="92"/>
-      <c r="H11" s="125"/>
-      <c r="I11" s="125"/>
-    </row>
-    <row r="12" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="10"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="23"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-    </row>
-    <row r="13" spans="1:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="94"/>
-      <c r="B13" s="95" t="s">
-        <v>29</v>
-      </c>
-      <c r="C13" s="96" t="s">
-        <v>30</v>
-      </c>
-      <c r="D13" s="95"/>
-      <c r="E13" s="97" t="s">
+      <c r="D16" s="128"/>
+      <c r="E16" s="130" t="s">
         <v>28</v>
       </c>
-      <c r="F13" s="97"/>
-      <c r="G13" s="98" t="s">
+      <c r="F16" s="130"/>
+      <c r="G16" s="131" t="s">
         <v>31</v>
       </c>
-      <c r="H13" s="95" t="s">
+      <c r="H16" s="128" t="s">
         <v>39</v>
       </c>
-      <c r="I13" s="95" t="s">
+      <c r="I16" s="128" t="s">
         <v>51</v>
       </c>
-      <c r="J13" s="78"/>
-    </row>
-    <row r="14" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="61" t="s">
-        <v>77</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="I14" s="62">
-        <v>45712</v>
-      </c>
-      <c r="J14" s="78"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="61"/>
-      <c r="I15"/>
-      <c r="J15" s="78"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="61"/>
-      <c r="I16"/>
-      <c r="J16" s="78"/>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="28" t="s">
+      <c r="J16" s="3"/>
+    </row>
+    <row r="17" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="63" t="s">
+      <c r="B17" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="30">
+      <c r="C17" s="24">
         <v>45342</v>
       </c>
-      <c r="D17" s="28" t="s">
+      <c r="D17" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="E17" s="29"/>
-      <c r="F17" s="39" t="s">
+      <c r="E17" s="23"/>
+      <c r="F17" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="G17" s="31"/>
-      <c r="H17" s="29"/>
-      <c r="I17" s="31"/>
-      <c r="J17" s="78"/>
+      <c r="G17" s="25"/>
+      <c r="H17" s="23"/>
+      <c r="I17" s="25"/>
+      <c r="J17" s="3"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="28"/>
-      <c r="B18" s="66" t="s">
+      <c r="A18" s="22"/>
+      <c r="B18" s="54" t="s">
         <v>24</v>
       </c>
-      <c r="C18" s="30">
+      <c r="C18" s="24">
         <v>45537</v>
       </c>
-      <c r="D18" s="28" t="s">
+      <c r="D18" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="E18" s="29"/>
-      <c r="F18" s="40" t="s">
+      <c r="E18" s="23"/>
+      <c r="F18" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="G18" s="31">
+      <c r="G18" s="25">
         <v>45691</v>
       </c>
-      <c r="H18" s="29"/>
-      <c r="I18" s="31"/>
-      <c r="J18" s="78"/>
+      <c r="H18" s="23"/>
+      <c r="I18" s="25"/>
+      <c r="J18" s="3"/>
     </row>
     <row r="19" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="56"/>
-      <c r="B19" s="57"/>
-      <c r="C19" s="58"/>
-      <c r="D19" s="16" t="s">
+      <c r="A19" s="44"/>
+      <c r="B19" s="45"/>
+      <c r="C19" s="46"/>
+      <c r="D19" s="13" t="s">
         <v>22</v>
       </c>
       <c r="F19" s="5"/>
       <c r="H19" s="5"/>
-      <c r="J19" s="78"/>
+      <c r="J19" s="3"/>
     </row>
     <row r="20" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
-      <c r="C20" s="121">
+      <c r="C20" s="98">
         <v>45726</v>
       </c>
-      <c r="D20" s="122" t="s">
+      <c r="D20" s="99" t="s">
         <v>85</v>
       </c>
-      <c r="E20" s="122"/>
-      <c r="F20" s="123"/>
-      <c r="G20" s="123"/>
-      <c r="H20" s="59"/>
-      <c r="I20" s="60"/>
-      <c r="J20" s="78"/>
+      <c r="E20" s="99"/>
+      <c r="F20" s="100"/>
+      <c r="G20" s="100"/>
+      <c r="H20" s="47"/>
+      <c r="I20" s="48"/>
+      <c r="J20" s="3"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
-      <c r="C21" s="89"/>
-      <c r="D21" s="90"/>
-      <c r="E21" s="90"/>
-      <c r="F21" s="91"/>
-      <c r="G21" s="91"/>
-      <c r="H21" s="92"/>
-      <c r="I21" s="92"/>
-      <c r="J21" s="78"/>
+      <c r="C21" s="69"/>
+      <c r="D21" s="70"/>
+      <c r="E21" s="70"/>
+      <c r="F21" s="71"/>
+      <c r="G21" s="71"/>
+      <c r="H21" s="72"/>
+      <c r="I21" s="72"/>
+      <c r="J21" s="3"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="61"/>
+      <c r="A22" s="49"/>
       <c r="I22"/>
-      <c r="J22" s="78"/>
+      <c r="J22" s="3"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="93"/>
-      <c r="B23" s="78"/>
-      <c r="C23" s="86"/>
-      <c r="D23" s="78"/>
-      <c r="E23" s="78"/>
-      <c r="F23" s="78"/>
-      <c r="G23" s="79"/>
-      <c r="H23" s="78"/>
-      <c r="I23" s="78"/>
-      <c r="J23" s="78"/>
+      <c r="A23" s="132"/>
+      <c r="B23" s="3"/>
+      <c r="C23" s="18"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
+      <c r="J23" s="3"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="61"/>
+      <c r="A24" s="49"/>
       <c r="I24"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="61"/>
+      <c r="A25" s="49"/>
       <c r="I25"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="61"/>
-      <c r="I26"/>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" s="99"/>
-      <c r="B27" s="100" t="s">
+    <row r="26" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="73"/>
+      <c r="B26" s="74" t="s">
         <v>29</v>
       </c>
-      <c r="C27" s="101" t="s">
+      <c r="C26" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="D27" s="100"/>
-      <c r="E27" s="102" t="s">
+      <c r="D26" s="74"/>
+      <c r="E26" s="76" t="s">
         <v>28</v>
       </c>
-      <c r="F27" s="102"/>
-      <c r="G27" s="103" t="s">
+      <c r="F26" s="76"/>
+      <c r="G26" s="77" t="s">
         <v>31</v>
       </c>
-      <c r="H27" s="100" t="s">
+      <c r="H26" s="74" t="s">
         <v>39</v>
       </c>
-      <c r="I27" s="100" t="s">
+      <c r="I26" s="74" t="s">
         <v>51</v>
       </c>
-      <c r="J27" s="78"/>
+      <c r="J26" s="62"/>
+    </row>
+    <row r="27" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="49" t="s">
+        <v>77</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="I27" s="50">
+        <v>45712</v>
+      </c>
+      <c r="J27" s="62"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="49"/>
+      <c r="I28"/>
+      <c r="J28" s="62"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="60"/>
+      <c r="B29" s="61"/>
+      <c r="C29" s="67"/>
+      <c r="D29" s="60"/>
+      <c r="E29" s="60"/>
+      <c r="F29" s="60"/>
+      <c r="G29" s="68"/>
+      <c r="H29" s="60"/>
+      <c r="I29" s="65" t="s">
+        <v>93</v>
+      </c>
+      <c r="J29" s="62"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" s="2"/>
+      <c r="B30" s="62"/>
+      <c r="C30" s="66"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="63"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="63"/>
+      <c r="J30" s="62"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" s="49"/>
+      <c r="I31"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="49"/>
+      <c r="I32"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" s="133"/>
+      <c r="B33" s="134" t="s">
+        <v>29</v>
+      </c>
+      <c r="C33" s="135" t="s">
+        <v>30</v>
+      </c>
+      <c r="D33" s="134"/>
+      <c r="E33" s="136" t="s">
+        <v>28</v>
+      </c>
+      <c r="F33" s="136"/>
+      <c r="G33" s="137" t="s">
+        <v>31</v>
+      </c>
+      <c r="H33" s="134" t="s">
+        <v>39</v>
+      </c>
+      <c r="I33" s="134" t="s">
+        <v>51</v>
+      </c>
+      <c r="J33" s="3"/>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B28" s="63" t="s">
+      <c r="B34" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="C28" s="24">
+      <c r="C34" s="18">
         <v>45475</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D34" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E28" s="47">
+      <c r="E34" s="37">
         <v>97</v>
       </c>
-      <c r="F28" s="4" t="s">
+      <c r="F34" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="H28" s="4" t="s">
+      <c r="H34" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="I28" s="6">
+      <c r="I34" s="6">
         <v>45705</v>
       </c>
-      <c r="J28" s="78"/>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="4"/>
-      <c r="B29" s="64" t="s">
+      <c r="J34" s="3"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" s="4"/>
+      <c r="B35" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="C29" s="24">
+      <c r="C35" s="18">
         <v>45604</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="D35" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E29" s="47">
+      <c r="E35" s="37">
         <v>178</v>
       </c>
-      <c r="F29" s="4" t="s">
+      <c r="F35" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="H29" s="13" t="s">
+      <c r="H35" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="I29" s="27">
+      <c r="I35" s="21">
         <v>45705</v>
       </c>
-      <c r="J29" s="78"/>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="1"/>
-      <c r="B30" s="65" t="s">
-        <v>36</v>
-      </c>
-      <c r="C30" s="25">
-        <v>45704</v>
-      </c>
-      <c r="D30" s="55" t="s">
-        <v>82</v>
-      </c>
-      <c r="J30" s="78"/>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" s="1"/>
-      <c r="B31" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C31" s="25">
-        <v>45705</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="H31" s="1"/>
-      <c r="J31" s="78"/>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" s="1"/>
-      <c r="C32" s="48"/>
-      <c r="D32" s="1"/>
-      <c r="H32" s="1"/>
-      <c r="J32" s="78"/>
-    </row>
-    <row r="33" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="1"/>
-      <c r="C33" s="48" t="s">
-        <v>56</v>
-      </c>
-      <c r="D33" s="55" t="s">
-        <v>61</v>
-      </c>
-      <c r="H33" s="1"/>
-      <c r="J33" s="78"/>
-    </row>
-    <row r="34" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="1"/>
-      <c r="C34" s="116">
-        <v>45717</v>
-      </c>
-      <c r="D34" s="117" t="s">
-        <v>76</v>
-      </c>
-      <c r="E34" s="118" t="s">
-        <v>62</v>
-      </c>
-      <c r="F34" s="117"/>
-      <c r="G34" s="119"/>
-      <c r="H34" s="117" t="s">
-        <v>63</v>
-      </c>
-      <c r="I34" s="120"/>
-      <c r="J34" s="78"/>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" s="1"/>
-      <c r="C35" s="51"/>
-      <c r="D35" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="H35" s="1"/>
-      <c r="J35" s="78"/>
+      <c r="J35" s="3"/>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
-      <c r="C36" s="48"/>
-      <c r="D36" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="H36" s="1"/>
-      <c r="J36" s="78"/>
+      <c r="B36" s="53" t="s">
+        <v>36</v>
+      </c>
+      <c r="C36" s="19">
+        <v>45704</v>
+      </c>
+      <c r="D36" s="43" t="s">
+        <v>82</v>
+      </c>
+      <c r="J36" s="3"/>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
-      <c r="C37" s="48"/>
-      <c r="D37" s="1"/>
+      <c r="B37" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C37" s="19">
+        <v>45705</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>59</v>
+      </c>
       <c r="H37" s="1"/>
-      <c r="J37" s="78"/>
+      <c r="J37" s="3"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
-      <c r="C38" s="48"/>
+      <c r="C38" s="38"/>
       <c r="D38" s="1"/>
-      <c r="I38" s="80" t="s">
-        <v>81</v>
-      </c>
-      <c r="J38" s="78"/>
+      <c r="H38" s="1"/>
+      <c r="J38" s="3"/>
     </row>
     <row r="39" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
-      <c r="B39" s="75" t="s">
-        <v>53</v>
-      </c>
-      <c r="C39" s="76">
-        <v>45805</v>
-      </c>
-      <c r="D39" s="77">
-        <v>0.40972222222222227</v>
-      </c>
-      <c r="E39" s="78" t="s">
-        <v>55</v>
-      </c>
-      <c r="F39" s="78"/>
-      <c r="G39" s="79"/>
-      <c r="H39" s="78"/>
-      <c r="I39" s="78"/>
-      <c r="J39" s="78"/>
-    </row>
-    <row r="40" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="C39" s="38" t="s">
+        <v>56</v>
+      </c>
+      <c r="D39" s="43" t="s">
+        <v>61</v>
+      </c>
+      <c r="H39" s="1"/>
+      <c r="J39" s="3"/>
+    </row>
+    <row r="40" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
-      <c r="C40" s="48">
-        <v>45805</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>57</v>
-      </c>
+      <c r="C40" s="94">
+        <v>45717</v>
+      </c>
+      <c r="D40" s="95" t="s">
+        <v>76</v>
+      </c>
+      <c r="E40" s="96" t="s">
+        <v>62</v>
+      </c>
+      <c r="F40" s="95"/>
+      <c r="G40" s="97"/>
+      <c r="H40" s="95" t="s">
+        <v>63</v>
+      </c>
+      <c r="I40" s="64" t="s">
+        <v>81</v>
+      </c>
+      <c r="J40" s="3"/>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="1"/>
-      <c r="C41" s="48"/>
-      <c r="D41" s="1"/>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A42" s="99"/>
-      <c r="B42" s="100" t="s">
+      <c r="C41" s="41"/>
+      <c r="D41" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="J41" s="3"/>
+    </row>
+    <row r="42" spans="1:10" s="144" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B42" s="149" t="s">
+        <v>53</v>
+      </c>
+      <c r="C42" s="150">
+        <v>45805</v>
+      </c>
+      <c r="D42" s="151">
+        <v>0.40972222222222227</v>
+      </c>
+      <c r="E42" s="145" t="s">
+        <v>55</v>
+      </c>
+      <c r="F42" s="145"/>
+      <c r="G42" s="146"/>
+      <c r="I42" s="147"/>
+      <c r="J42" s="148"/>
+    </row>
+    <row r="43" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="4"/>
+      <c r="B43" s="3"/>
+      <c r="C43" s="152">
+        <v>45805</v>
+      </c>
+      <c r="D43" s="37" t="s">
+        <v>57</v>
+      </c>
+      <c r="E43" s="37"/>
+      <c r="F43" s="37"/>
+      <c r="G43" s="153"/>
+      <c r="H43" s="3"/>
+      <c r="I43" s="6"/>
+      <c r="J43" s="3"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" s="1"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" s="1"/>
+      <c r="C45" s="38"/>
+      <c r="D45" s="1"/>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" s="133"/>
+      <c r="B46" s="134" t="s">
         <v>29</v>
       </c>
-      <c r="C42" s="101" t="s">
+      <c r="C46" s="135" t="s">
         <v>30</v>
       </c>
-      <c r="D42" s="100"/>
-      <c r="E42" s="102" t="s">
+      <c r="D46" s="134"/>
+      <c r="E46" s="136" t="s">
         <v>28</v>
       </c>
-      <c r="F42" s="102"/>
-      <c r="G42" s="103" t="s">
+      <c r="F46" s="136"/>
+      <c r="G46" s="137" t="s">
         <v>31</v>
       </c>
-      <c r="H42" s="100" t="s">
+      <c r="H46" s="134" t="s">
         <v>39</v>
       </c>
-      <c r="I42" s="100" t="s">
+      <c r="I46" s="134" t="s">
         <v>51</v>
       </c>
-      <c r="J42" s="78"/>
-    </row>
-    <row r="43" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="4" t="s">
+      <c r="J46" s="3"/>
+    </row>
+    <row r="47" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B43" s="63" t="s">
+      <c r="B47" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="C43" s="69">
+      <c r="C47" s="56">
         <v>45588</v>
       </c>
-      <c r="D43" s="47" t="s">
+      <c r="D47" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="E43" s="3"/>
-      <c r="F43" s="4" t="s">
+      <c r="E47" s="3"/>
+      <c r="F47" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="H43" s="4" t="s">
+      <c r="H47" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="I43" s="6">
+      <c r="I47" s="6">
         <v>45630</v>
       </c>
-      <c r="J43" s="78"/>
-    </row>
-    <row r="44" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="4"/>
-      <c r="B44" s="63" t="s">
+      <c r="J47" s="3"/>
+    </row>
+    <row r="48" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="4"/>
+      <c r="B48" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="C44" s="24"/>
-      <c r="D44" s="4"/>
-      <c r="E44" s="3"/>
-      <c r="F44" s="4"/>
-      <c r="H44" s="13" t="s">
+      <c r="C48" s="18"/>
+      <c r="D48" s="4"/>
+      <c r="E48" s="3"/>
+      <c r="F48" s="4"/>
+      <c r="H48" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="I44" s="6">
+      <c r="I48" s="6">
         <v>45630</v>
       </c>
-      <c r="J44" s="78"/>
-    </row>
-    <row r="45" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="4"/>
-      <c r="B45" s="65" t="s">
+      <c r="J48" s="3"/>
+    </row>
+    <row r="49" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="4"/>
+      <c r="B49" s="53" t="s">
         <v>35</v>
       </c>
-      <c r="C45" s="45">
+      <c r="C49" s="35">
         <v>45704</v>
       </c>
-      <c r="D45" s="55" t="s">
+      <c r="D49" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="E45" s="1"/>
-      <c r="F45" s="1"/>
-      <c r="H45" s="1"/>
-      <c r="I45"/>
-      <c r="J45" s="78"/>
-    </row>
-    <row r="46" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="1"/>
-      <c r="B46" s="1" t="s">
+      <c r="E49" s="1"/>
+      <c r="F49" s="1"/>
+      <c r="H49" s="1"/>
+      <c r="I49"/>
+      <c r="J49" s="3"/>
+    </row>
+    <row r="50" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="1"/>
+      <c r="B50" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C46" s="25">
+      <c r="C50" s="19">
         <v>45709</v>
       </c>
-      <c r="D46" s="1" t="s">
+      <c r="D50" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="H46" s="1"/>
-      <c r="J46" s="78"/>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A47" s="1"/>
-      <c r="C47" s="48" t="s">
-        <v>56</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H47" s="1"/>
-      <c r="J47" s="78"/>
-    </row>
-    <row r="48" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="1"/>
-      <c r="C48" s="48">
-        <v>45712</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="H48" s="1"/>
-      <c r="J48" s="78"/>
-    </row>
-    <row r="49" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="1"/>
-      <c r="C49" s="110">
-        <v>45717</v>
-      </c>
-      <c r="D49" s="111" t="s">
-        <v>76</v>
-      </c>
-      <c r="E49" s="112" t="s">
-        <v>62</v>
-      </c>
-      <c r="F49" s="111"/>
-      <c r="G49" s="113"/>
-      <c r="H49" s="111" t="s">
-        <v>63</v>
-      </c>
-      <c r="I49" s="114"/>
-      <c r="J49" s="78"/>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A50" s="1"/>
-      <c r="C50" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="F50" s="5"/>
-      <c r="G50" s="71"/>
-      <c r="H50" s="70"/>
-      <c r="I50" s="71"/>
-      <c r="J50" s="78"/>
+      <c r="H50" s="1"/>
+      <c r="J50" s="3"/>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="1"/>
-      <c r="C51" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="F51" s="5"/>
-      <c r="G51" s="71"/>
-      <c r="H51" s="70"/>
-      <c r="I51" s="71"/>
-      <c r="J51" s="78"/>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C51" s="38" t="s">
+        <v>56</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="H51" s="1"/>
+      <c r="J51" s="3"/>
+    </row>
+    <row r="52" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1"/>
+      <c r="C52" s="38">
+        <v>45712</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>58</v>
+      </c>
       <c r="H52" s="1"/>
-      <c r="I52" s="68" t="s">
-        <v>81</v>
-      </c>
-      <c r="J52" s="78"/>
+      <c r="J52" s="3"/>
     </row>
     <row r="53" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1"/>
-      <c r="B53" s="42" t="s">
+      <c r="C53" s="88">
+        <v>45717</v>
+      </c>
+      <c r="D53" s="89" t="s">
+        <v>76</v>
+      </c>
+      <c r="E53" s="90" t="s">
+        <v>62</v>
+      </c>
+      <c r="F53" s="89"/>
+      <c r="G53" s="91"/>
+      <c r="H53" s="89" t="s">
+        <v>63</v>
+      </c>
+      <c r="I53" s="92"/>
+      <c r="J53" s="3"/>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A54" s="1"/>
+      <c r="C54" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F54" s="5"/>
+      <c r="G54" s="58"/>
+      <c r="H54" s="57"/>
+      <c r="I54" s="58"/>
+      <c r="J54" s="3"/>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A55" s="1"/>
+      <c r="C55" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F55" s="5"/>
+      <c r="G55" s="58"/>
+      <c r="H55" s="57"/>
+      <c r="I55" s="55" t="s">
+        <v>81</v>
+      </c>
+      <c r="J55" s="3"/>
+    </row>
+    <row r="56" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="1"/>
+      <c r="B56" s="32" t="s">
         <v>53</v>
       </c>
-      <c r="C53" s="43">
+      <c r="C56" s="33">
         <v>45805</v>
       </c>
-      <c r="D53" s="49">
+      <c r="D56" s="39">
         <v>0</v>
       </c>
-      <c r="J53" s="78"/>
-    </row>
-    <row r="54" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="1"/>
-      <c r="B54" s="78"/>
-      <c r="C54" s="82">
+      <c r="J56" s="3"/>
+    </row>
+    <row r="57" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="4"/>
+      <c r="B57" s="3"/>
+      <c r="C57" s="138">
         <v>45805</v>
       </c>
-      <c r="D54" s="2" t="s">
+      <c r="D57" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="E54" s="78"/>
-      <c r="F54" s="78"/>
-      <c r="G54" s="79"/>
-      <c r="H54" s="78"/>
-      <c r="I54" s="79"/>
-      <c r="J54" s="78"/>
-    </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A55" s="73"/>
-      <c r="B55" s="74"/>
-      <c r="C55" s="108"/>
-      <c r="D55" s="73"/>
-      <c r="E55" s="74"/>
-      <c r="F55" s="74"/>
-      <c r="G55" s="88"/>
-      <c r="H55" s="74"/>
-      <c r="I55" s="88"/>
-      <c r="J55" s="74"/>
-    </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A56" s="73"/>
-      <c r="B56" s="74"/>
-      <c r="C56" s="108"/>
-      <c r="D56" s="73"/>
-      <c r="E56" s="74"/>
-      <c r="F56" s="74"/>
-      <c r="G56" s="88"/>
-      <c r="H56" s="74"/>
-      <c r="I56" s="88"/>
-      <c r="J56" s="74"/>
-    </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A57" s="1"/>
-      <c r="D57" s="1"/>
-      <c r="E57" s="1"/>
-      <c r="F57" s="1"/>
-      <c r="H57" s="1"/>
-      <c r="I57"/>
+      <c r="E57" s="3"/>
+      <c r="F57" s="3"/>
+      <c r="G57" s="6"/>
+      <c r="H57" s="3"/>
+      <c r="I57" s="6"/>
+      <c r="J57" s="3"/>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A58" s="99"/>
-      <c r="B58" s="100" t="s">
+      <c r="A58" s="60"/>
+      <c r="B58" s="61"/>
+      <c r="C58" s="87"/>
+      <c r="D58" s="60"/>
+      <c r="E58" s="61"/>
+      <c r="F58" s="61"/>
+      <c r="G58" s="68"/>
+      <c r="H58" s="61"/>
+      <c r="I58" s="68"/>
+      <c r="J58" s="61"/>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A59" s="60"/>
+      <c r="B59" s="61"/>
+      <c r="C59" s="87"/>
+      <c r="D59" s="60"/>
+      <c r="E59" s="61"/>
+      <c r="F59" s="61"/>
+      <c r="G59" s="68"/>
+      <c r="H59" s="61"/>
+      <c r="I59" s="68"/>
+      <c r="J59" s="61"/>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A60" s="1"/>
+      <c r="D60" s="1"/>
+      <c r="E60" s="1"/>
+      <c r="F60" s="1"/>
+      <c r="H60" s="1"/>
+      <c r="I60"/>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A61" s="118"/>
+      <c r="B61" s="119" t="s">
         <v>29</v>
       </c>
-      <c r="C58" s="101" t="s">
+      <c r="C61" s="120" t="s">
         <v>30</v>
       </c>
-      <c r="D58" s="100"/>
-      <c r="E58" s="102" t="s">
+      <c r="D61" s="119"/>
+      <c r="E61" s="121" t="s">
         <v>28</v>
       </c>
-      <c r="F58" s="102"/>
-      <c r="G58" s="103" t="s">
+      <c r="F61" s="121"/>
+      <c r="G61" s="122" t="s">
         <v>31</v>
       </c>
-      <c r="H58" s="100" t="s">
+      <c r="H61" s="119" t="s">
         <v>39</v>
       </c>
-      <c r="I58" s="100" t="s">
+      <c r="I61" s="119" t="s">
         <v>51</v>
       </c>
-      <c r="J58" s="78"/>
-    </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A59" s="2" t="s">
+      <c r="J61" s="113"/>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B59" s="63" t="s">
+      <c r="B62" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="C59" s="24">
+      <c r="C62" s="18">
         <v>45475</v>
       </c>
-      <c r="D59" s="4" t="s">
+      <c r="D62" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E59" s="47">
+      <c r="E62" s="37">
         <v>214</v>
       </c>
-      <c r="F59" s="4" t="s">
+      <c r="F62" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="H59" s="4" t="s">
+      <c r="H62" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I59" s="6">
+      <c r="I62" s="6">
         <v>45702</v>
       </c>
-      <c r="J59" s="78"/>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A60" s="2"/>
-      <c r="B60" s="3"/>
-      <c r="C60" s="24"/>
-      <c r="D60" s="72">
+      <c r="J62" s="113"/>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A63" s="2"/>
+      <c r="B63" s="3"/>
+      <c r="C63" s="18"/>
+      <c r="D63" s="59">
         <v>158437</v>
       </c>
-      <c r="E60" s="3"/>
-      <c r="F60" s="4"/>
-      <c r="H60" s="13" t="s">
+      <c r="E63" s="3"/>
+      <c r="F63" s="4"/>
+      <c r="H63" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="I60" s="6">
+      <c r="I63" s="6">
         <v>45702</v>
       </c>
-      <c r="J60" s="78"/>
-    </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A61" s="1"/>
-      <c r="B61" s="65" t="s">
+      <c r="J63" s="113"/>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A64" s="1"/>
+      <c r="B64" s="53" t="s">
         <v>33</v>
       </c>
-      <c r="C61" s="25">
+      <c r="C64" s="19">
         <v>45704</v>
       </c>
-      <c r="D61" s="1" t="s">
+      <c r="D64" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="H61" s="1"/>
-      <c r="I61"/>
-      <c r="J61" s="78"/>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A62" s="1"/>
-      <c r="B62" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C62" s="25">
-        <v>45705</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="H62" s="1"/>
-      <c r="J62" s="78"/>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A63" s="1"/>
-      <c r="D63" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="H63" s="1"/>
-      <c r="J63" s="78"/>
-    </row>
-    <row r="64" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="1"/>
-      <c r="C64" s="48" t="s">
-        <v>56</v>
-      </c>
-      <c r="D64" s="55" t="s">
-        <v>68</v>
-      </c>
       <c r="H64" s="1"/>
-      <c r="J64" s="78"/>
+      <c r="I64"/>
+      <c r="J64" s="113"/>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" s="1"/>
-      <c r="C65" s="104">
-        <v>45711</v>
-      </c>
-      <c r="D65" s="105" t="s">
-        <v>69</v>
-      </c>
-      <c r="E65" s="105"/>
-      <c r="F65" s="105"/>
-      <c r="G65" s="106"/>
-      <c r="H65" s="105"/>
-      <c r="I65" s="107"/>
-      <c r="J65" s="78"/>
-    </row>
-    <row r="66" spans="1:10" s="74" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C66" s="51" t="s">
-        <v>70</v>
-      </c>
-      <c r="D66" s="70"/>
-      <c r="E66" s="70"/>
-      <c r="F66" s="70"/>
-      <c r="G66" s="71"/>
-      <c r="H66" s="70"/>
-      <c r="I66" s="71"/>
-      <c r="J66" s="78"/>
-    </row>
-    <row r="67" spans="1:10" s="74" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="73">
-        <v>1</v>
-      </c>
-      <c r="C67" s="51" t="s">
-        <v>88</v>
-      </c>
-      <c r="D67" s="55" t="s">
-        <v>90</v>
-      </c>
-      <c r="E67" s="70"/>
-      <c r="F67" s="70"/>
-      <c r="G67" s="71"/>
-      <c r="H67" s="70"/>
-      <c r="I67" s="71"/>
-      <c r="J67" s="78"/>
+      <c r="B65" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C65" s="19">
+        <v>45705</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H65" s="1"/>
+      <c r="J65" s="113"/>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A66" s="1"/>
+      <c r="D66" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H66" s="1"/>
+      <c r="J66" s="113"/>
+    </row>
+    <row r="67" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="1"/>
+      <c r="C67" s="38" t="s">
+        <v>56</v>
+      </c>
+      <c r="D67" s="43" t="s">
+        <v>68</v>
+      </c>
+      <c r="H67" s="1"/>
+      <c r="J67" s="113"/>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" s="1"/>
-      <c r="D68" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="H68" s="1"/>
-      <c r="J68" s="78"/>
-    </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A69" s="1"/>
-      <c r="C69" s="51"/>
-      <c r="D69" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H69" s="1"/>
-      <c r="J69" s="78"/>
-    </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A70" s="1"/>
-      <c r="C70" s="51"/>
-      <c r="D70" s="1"/>
-      <c r="H70" s="1"/>
-      <c r="J70" s="78"/>
+      <c r="C68" s="83">
+        <v>45711</v>
+      </c>
+      <c r="D68" s="84" t="s">
+        <v>69</v>
+      </c>
+      <c r="E68" s="84"/>
+      <c r="F68" s="84"/>
+      <c r="G68" s="85"/>
+      <c r="H68" s="84"/>
+      <c r="I68" s="86"/>
+      <c r="J68" s="113"/>
+    </row>
+    <row r="69" spans="1:10" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C69" s="41" t="s">
+        <v>70</v>
+      </c>
+      <c r="D69" s="57"/>
+      <c r="E69" s="57"/>
+      <c r="F69" s="57"/>
+      <c r="G69" s="58"/>
+      <c r="H69" s="57"/>
+      <c r="I69" s="58"/>
+      <c r="J69" s="113"/>
+    </row>
+    <row r="70" spans="1:10" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="60">
+        <v>1</v>
+      </c>
+      <c r="C70" s="41" t="s">
+        <v>88</v>
+      </c>
+      <c r="D70" s="43" t="s">
+        <v>90</v>
+      </c>
+      <c r="E70" s="57"/>
+      <c r="F70" s="57"/>
+      <c r="G70" s="58"/>
+      <c r="H70" s="57"/>
+      <c r="I70" s="58"/>
+      <c r="J70" s="113"/>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" s="1"/>
-      <c r="C71" s="51"/>
-      <c r="D71" s="1"/>
+      <c r="D71" s="1" t="s">
+        <v>71</v>
+      </c>
       <c r="H71" s="1"/>
-      <c r="I71" s="81" t="s">
+      <c r="I71" s="65" t="s">
         <v>92</v>
       </c>
-      <c r="J71" s="78"/>
+      <c r="J71" s="113"/>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" s="1"/>
-      <c r="C72" s="51"/>
-      <c r="D72" s="1"/>
+      <c r="C72" s="41"/>
+      <c r="D72" s="1" t="s">
+        <v>72</v>
+      </c>
       <c r="H72" s="1"/>
-      <c r="I72" s="81" t="s">
+      <c r="I72" s="65" t="s">
         <v>91</v>
       </c>
-      <c r="J72" s="78"/>
+      <c r="J72" s="113"/>
     </row>
     <row r="73" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="1"/>
-      <c r="B73" s="75" t="s">
+      <c r="B73" s="149" t="s">
         <v>53</v>
       </c>
-      <c r="C73" s="109">
+      <c r="C73" s="159">
         <v>45792</v>
       </c>
-      <c r="D73" s="77">
+      <c r="D73" s="151">
         <v>0.39930555555555558</v>
       </c>
-      <c r="E73" s="78"/>
-      <c r="F73" s="78"/>
-      <c r="G73" s="79"/>
-      <c r="H73" s="78"/>
-      <c r="I73" s="78"/>
-      <c r="J73" s="78"/>
+      <c r="E73" s="61"/>
+      <c r="F73" s="61"/>
+      <c r="J73" s="113"/>
     </row>
     <row r="74" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="1"/>
-      <c r="C74" s="48">
-        <v>45792</v>
-      </c>
-      <c r="D74" s="1" t="s">
+      <c r="A74" s="123"/>
+      <c r="B74" s="154" t="s">
+        <v>110</v>
+      </c>
+      <c r="C74" s="155">
+        <v>45939</v>
+      </c>
+      <c r="D74" s="156">
+        <v>0.40277777777777773</v>
+      </c>
+      <c r="E74" s="157"/>
+      <c r="F74" s="157"/>
+      <c r="G74" s="158" t="s">
         <v>67</v>
       </c>
-      <c r="H74" s="1"/>
-      <c r="I74"/>
+      <c r="H74" s="158" t="s">
+        <v>108</v>
+      </c>
+      <c r="I74" s="158" t="s">
+        <v>109</v>
+      </c>
+      <c r="J74" s="113"/>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" s="1"/>
-      <c r="C75" s="48"/>
+      <c r="C75" s="38"/>
       <c r="D75" s="1"/>
       <c r="H75" s="1"/>
       <c r="I75"/>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A76" s="4" t="s">
+      <c r="A76" s="1"/>
+      <c r="C76" s="38"/>
+      <c r="D76" s="1"/>
+      <c r="H76" s="1"/>
+      <c r="I76"/>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A77" s="78"/>
+      <c r="B77" s="79" t="s">
+        <v>29</v>
+      </c>
+      <c r="C77" s="80" t="s">
+        <v>30</v>
+      </c>
+      <c r="D77" s="79"/>
+      <c r="E77" s="81" t="s">
+        <v>28</v>
+      </c>
+      <c r="F77" s="81"/>
+      <c r="G77" s="82" t="s">
+        <v>31</v>
+      </c>
+      <c r="H77" s="79" t="s">
+        <v>39</v>
+      </c>
+      <c r="I77" s="79" t="s">
+        <v>51</v>
+      </c>
+      <c r="J77" s="62"/>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A78" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B76" s="63" t="s">
+      <c r="B78" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="C76" s="24">
+      <c r="C78" s="18">
         <v>45676</v>
       </c>
-      <c r="D76" s="47" t="s">
+      <c r="D78" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="E76" s="4"/>
-      <c r="F76" s="4" t="s">
+      <c r="E78" s="4"/>
+      <c r="F78" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="H76" s="1" t="s">
+      <c r="H78" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="J76" s="78"/>
-    </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A77" s="4" t="s">
+      <c r="J78" s="62"/>
+    </row>
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A79" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B77" s="63" t="s">
+      <c r="B79" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="C77" s="24"/>
-      <c r="D77" s="4"/>
-      <c r="E77" s="4"/>
-      <c r="F77" s="4"/>
-      <c r="H77" s="13" t="s">
+      <c r="C79" s="18"/>
+      <c r="D79" s="4"/>
+      <c r="E79" s="4"/>
+      <c r="F79" s="4"/>
+      <c r="H79" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="I77" s="14">
+      <c r="I79" s="12">
         <v>45714</v>
       </c>
-      <c r="J77" s="78"/>
-    </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A78" s="73"/>
-      <c r="B78" s="74"/>
-      <c r="C78" s="87"/>
-      <c r="D78" s="73"/>
-      <c r="E78" s="73"/>
-      <c r="F78" s="73"/>
-      <c r="G78" s="88"/>
-      <c r="H78" s="73"/>
-      <c r="J78" s="78"/>
-    </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A79" s="73"/>
-      <c r="B79" s="74"/>
-      <c r="C79" s="87"/>
-      <c r="D79" s="73"/>
-      <c r="E79" s="73"/>
-      <c r="F79" s="73"/>
-      <c r="G79" s="88"/>
-      <c r="H79" s="73"/>
-      <c r="I79" s="81" t="s">
+      <c r="J79" s="62"/>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A80" s="60"/>
+      <c r="B80" s="61"/>
+      <c r="C80" s="67"/>
+      <c r="D80" s="60"/>
+      <c r="E80" s="60"/>
+      <c r="F80" s="60"/>
+      <c r="G80" s="68"/>
+      <c r="H80" s="60"/>
+      <c r="J80" s="62"/>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A81" s="60"/>
+      <c r="B81" s="61"/>
+      <c r="C81" s="67"/>
+      <c r="D81" s="60"/>
+      <c r="E81" s="60"/>
+      <c r="F81" s="60"/>
+      <c r="G81" s="68"/>
+      <c r="H81" s="60"/>
+      <c r="I81" s="65" t="s">
         <v>93</v>
       </c>
-      <c r="J79" s="78"/>
-    </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A80" s="2"/>
-      <c r="B80" s="78"/>
-      <c r="C80" s="86"/>
-      <c r="D80" s="2"/>
-      <c r="E80" s="2"/>
-      <c r="F80" s="2"/>
-      <c r="G80" s="79"/>
-      <c r="H80" s="2"/>
-      <c r="I80" s="79"/>
-      <c r="J80" s="78"/>
-    </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A81" s="1"/>
-      <c r="C81" s="48"/>
-      <c r="D81" s="1"/>
-      <c r="H81" s="1"/>
-      <c r="I81"/>
+      <c r="J81" s="62"/>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A82" s="1"/>
-      <c r="C82" s="48"/>
-      <c r="D82" s="1"/>
-      <c r="H82" s="1"/>
-      <c r="I82"/>
+      <c r="A82" s="2"/>
+      <c r="B82" s="62"/>
+      <c r="C82" s="66"/>
+      <c r="D82" s="2"/>
+      <c r="E82" s="2"/>
+      <c r="F82" s="2"/>
+      <c r="G82" s="63"/>
+      <c r="H82" s="2"/>
+      <c r="I82" s="63"/>
+      <c r="J82" s="62"/>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" s="1"/>
-      <c r="C83" s="48"/>
+      <c r="C83" s="38"/>
       <c r="D83" s="1"/>
       <c r="H83" s="1"/>
       <c r="I83"/>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" s="1"/>
-      <c r="C84" s="48"/>
+      <c r="C84" s="38"/>
       <c r="D84" s="1"/>
       <c r="H84" s="1"/>
       <c r="I84"/>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A85" s="99"/>
-      <c r="B85" s="100" t="s">
+      <c r="A85" s="118"/>
+      <c r="B85" s="119" t="s">
         <v>29</v>
       </c>
-      <c r="C85" s="101" t="s">
+      <c r="C85" s="120" t="s">
         <v>30</v>
       </c>
-      <c r="D85" s="100"/>
-      <c r="E85" s="102" t="s">
+      <c r="D85" s="119"/>
+      <c r="E85" s="121" t="s">
         <v>28</v>
       </c>
-      <c r="F85" s="102"/>
-      <c r="G85" s="103" t="s">
+      <c r="F85" s="121"/>
+      <c r="G85" s="122" t="s">
         <v>31</v>
       </c>
-      <c r="H85" s="100" t="s">
+      <c r="H85" s="119" t="s">
         <v>39</v>
       </c>
-      <c r="I85" s="100" t="s">
+      <c r="I85" s="119" t="s">
         <v>51</v>
       </c>
-      <c r="J85" s="78"/>
+      <c r="J85" s="113"/>
     </row>
     <row r="86" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B86" s="63" t="s">
+      <c r="B86" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="C86" s="46">
+      <c r="C86" s="36">
         <v>45603</v>
       </c>
       <c r="D86" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E86" s="47">
-        <v>156</v>
+      <c r="E86" s="37">
+        <v>156000</v>
       </c>
       <c r="F86" s="4" t="s">
         <v>26</v>
@@ -2449,30 +2681,30 @@
       <c r="I86" s="5">
         <v>45705</v>
       </c>
-      <c r="J86" s="78"/>
+      <c r="J86" s="113"/>
     </row>
     <row r="87" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A87" s="4"/>
       <c r="B87" s="3"/>
-      <c r="C87" s="24"/>
+      <c r="C87" s="18"/>
       <c r="D87" s="4"/>
       <c r="E87" s="3"/>
       <c r="F87" s="4"/>
       <c r="G87" s="6"/>
-      <c r="H87" s="13" t="s">
+      <c r="H87" s="11" t="s">
         <v>43</v>
       </c>
       <c r="I87" s="5">
         <v>45705</v>
       </c>
-      <c r="J87" s="78"/>
+      <c r="J87" s="113"/>
     </row>
     <row r="88" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="1"/>
-      <c r="B88" s="65" t="s">
+      <c r="B88" s="53" t="s">
         <v>37</v>
       </c>
-      <c r="C88" s="45">
+      <c r="C88" s="35">
         <v>45704</v>
       </c>
       <c r="D88" s="1" t="s">
@@ -2480,75 +2712,75 @@
       </c>
       <c r="F88" s="1"/>
       <c r="H88" s="1"/>
-      <c r="J88" s="78"/>
+      <c r="J88" s="113"/>
     </row>
     <row r="89" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A89" s="1"/>
       <c r="B89" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C89" s="25">
+      <c r="C89" s="19">
         <v>45705</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>52</v>
       </c>
       <c r="H89" s="1"/>
-      <c r="J89" s="78"/>
+      <c r="J89" s="113"/>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" s="1"/>
-      <c r="J90" s="78"/>
+      <c r="J90" s="113"/>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
-      <c r="C91" s="48" t="s">
+      <c r="C91" s="38" t="s">
         <v>56</v>
       </c>
-      <c r="D91" s="55" t="s">
+      <c r="D91" s="43" t="s">
         <v>68</v>
       </c>
-      <c r="G91" s="54"/>
+      <c r="G91" s="42"/>
       <c r="H91" s="1"/>
-      <c r="J91" s="78"/>
+      <c r="J91" s="113"/>
     </row>
     <row r="92" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="1"/>
-      <c r="C92" s="48">
+      <c r="C92" s="38">
         <v>45706</v>
       </c>
       <c r="D92" s="1" t="s">
         <v>58</v>
       </c>
       <c r="H92" s="1"/>
-      <c r="J92" s="78"/>
+      <c r="J92" s="113"/>
     </row>
     <row r="93" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="1"/>
-      <c r="C93" s="115">
+      <c r="C93" s="93">
         <v>45711</v>
       </c>
-      <c r="D93" s="111" t="s">
+      <c r="D93" s="89" t="s">
         <v>69</v>
       </c>
-      <c r="E93" s="111"/>
-      <c r="F93" s="111"/>
-      <c r="G93" s="113"/>
-      <c r="H93" s="111"/>
-      <c r="I93" s="114"/>
-      <c r="J93" s="78"/>
+      <c r="E93" s="89"/>
+      <c r="F93" s="89"/>
+      <c r="G93" s="91"/>
+      <c r="H93" s="89"/>
+      <c r="I93" s="92"/>
+      <c r="J93" s="113"/>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" s="1"/>
       <c r="B94" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="C94" s="50"/>
+      <c r="C94" s="40"/>
       <c r="D94" s="1" t="s">
         <v>74</v>
       </c>
       <c r="H94" s="1"/>
-      <c r="J94" s="78"/>
+      <c r="J94" s="113"/>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" s="1"/>
@@ -2556,302 +2788,334 @@
         <v>73</v>
       </c>
       <c r="H95" s="1"/>
-      <c r="J95" s="78"/>
+      <c r="J95" s="113"/>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" s="1"/>
       <c r="D96" s="1"/>
       <c r="H96" s="1"/>
-      <c r="I96" s="81" t="s">
+      <c r="I96" s="65" t="s">
         <v>95</v>
       </c>
-      <c r="J96" s="78"/>
+      <c r="J96" s="113"/>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" s="1"/>
       <c r="D97" s="1"/>
       <c r="H97" s="1"/>
-      <c r="I97" s="81" t="s">
+      <c r="I97" s="65" t="s">
         <v>92</v>
       </c>
-      <c r="J97" s="78"/>
+      <c r="J97" s="113"/>
     </row>
     <row r="98" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B98" s="83" t="s">
+      <c r="B98" s="106" t="s">
         <v>53</v>
       </c>
-      <c r="C98" s="84">
+      <c r="C98" s="107">
         <v>45792</v>
       </c>
-      <c r="D98" s="85">
+      <c r="D98" s="108">
         <v>0.39583333333333331</v>
       </c>
-      <c r="E98" s="78"/>
-      <c r="F98" s="78"/>
-      <c r="G98" s="79"/>
-      <c r="H98" s="78"/>
-      <c r="I98" s="78"/>
-      <c r="J98" s="78"/>
+      <c r="E98" s="61"/>
+      <c r="F98" s="61" t="s">
+        <v>107</v>
+      </c>
+      <c r="G98" s="68"/>
+      <c r="H98" s="61"/>
+      <c r="I98" s="61"/>
+      <c r="J98" s="113"/>
     </row>
     <row r="99" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="B99" s="52"/>
-      <c r="C99" s="53">
-        <v>45792</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="I99"/>
-    </row>
-    <row r="100" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="8"/>
-      <c r="B100" s="8"/>
-      <c r="C100" s="23"/>
-      <c r="D100" s="8"/>
-      <c r="E100" s="8"/>
-      <c r="F100" s="8"/>
-      <c r="G100" s="9"/>
-      <c r="H100" s="8"/>
-      <c r="I100" s="9"/>
-    </row>
-    <row r="101" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="28" t="s">
+      <c r="A99" s="113"/>
+      <c r="B99" s="114" t="s">
+        <v>110</v>
+      </c>
+      <c r="C99" s="115">
+        <v>45939</v>
+      </c>
+      <c r="D99" s="116">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="E99" s="113"/>
+      <c r="F99" s="113"/>
+      <c r="G99" s="117"/>
+      <c r="H99" s="113"/>
+      <c r="I99" s="113"/>
+      <c r="J99" s="113"/>
+    </row>
+    <row r="100" spans="1:10" s="105" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B100" s="109"/>
+      <c r="C100" s="110"/>
+      <c r="D100" s="112"/>
+      <c r="G100" s="111"/>
+    </row>
+    <row r="101" spans="1:10" s="105" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B101" s="109"/>
+      <c r="C101" s="110"/>
+      <c r="D101" s="112"/>
+      <c r="G101" s="111"/>
+    </row>
+    <row r="102" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A102" s="8"/>
+      <c r="B102" s="8"/>
+      <c r="C102" s="17"/>
+      <c r="D102" s="8"/>
+      <c r="E102" s="8"/>
+      <c r="F102" s="8"/>
+      <c r="G102" s="9"/>
+      <c r="H102" s="8"/>
+      <c r="I102" s="9"/>
+    </row>
+    <row r="103" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="B101" s="63" t="s">
+      <c r="B103" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="C101" s="30">
+      <c r="C103" s="24">
         <v>45588</v>
       </c>
-      <c r="D101" s="28" t="s">
+      <c r="D103" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="E101" s="29"/>
-      <c r="F101" s="29"/>
-      <c r="G101" s="7">
-        <v>45672</v>
-      </c>
-      <c r="H101" s="28" t="s">
-        <v>45</v>
-      </c>
-      <c r="I101" s="31">
-        <v>45625</v>
-      </c>
-    </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A102" s="28"/>
-      <c r="B102" s="63" t="s">
-        <v>87</v>
-      </c>
-      <c r="C102" s="30"/>
-      <c r="D102" s="28"/>
-      <c r="E102" s="29"/>
-      <c r="F102" s="29"/>
-      <c r="G102" s="7"/>
-      <c r="H102" s="28"/>
-      <c r="I102" s="31"/>
-    </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A103" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="B103" s="63" t="s">
-        <v>5</v>
-      </c>
-      <c r="C103" s="30">
-        <v>45588</v>
-      </c>
-      <c r="D103" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="E103" s="29"/>
-      <c r="F103" s="29"/>
+      <c r="E103" s="23"/>
+      <c r="F103" s="23"/>
       <c r="G103" s="7">
         <v>45672</v>
       </c>
-      <c r="H103" s="41" t="s">
+      <c r="H103" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="I103" s="25">
+        <v>45625</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A104" s="22"/>
+      <c r="B104" s="51" t="s">
+        <v>87</v>
+      </c>
+      <c r="C104" s="24"/>
+      <c r="D104" s="22"/>
+      <c r="E104" s="23"/>
+      <c r="F104" s="23"/>
+      <c r="G104" s="7"/>
+      <c r="H104" s="22"/>
+      <c r="I104" s="25"/>
+    </row>
+    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A105" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="B105" s="51" t="s">
+        <v>5</v>
+      </c>
+      <c r="C105" s="24">
+        <v>45588</v>
+      </c>
+      <c r="D105" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="E105" s="23"/>
+      <c r="F105" s="23"/>
+      <c r="G105" s="7">
+        <v>45672</v>
+      </c>
+      <c r="H105" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="I103" s="31">
+      <c r="I105" s="25">
         <v>45625</v>
       </c>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A104" s="13" t="s">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A106" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B104" s="63" t="s">
+      <c r="B106" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="C104" s="37">
+      <c r="C106" s="27">
         <v>45475</v>
       </c>
-      <c r="D104" s="13" t="s">
+      <c r="D106" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E104" s="36">
+      <c r="E106" s="26">
         <v>113</v>
       </c>
-      <c r="F104" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="G104" s="7">
-        <v>45672</v>
-      </c>
-      <c r="H104" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="I104" s="38">
-        <v>45705</v>
-      </c>
-    </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A105" s="13"/>
-      <c r="B105" s="63" t="s">
-        <v>86</v>
-      </c>
-      <c r="C105" s="37"/>
-      <c r="D105" s="13"/>
-      <c r="E105" s="36"/>
-      <c r="F105" s="13"/>
-      <c r="G105" s="7"/>
-      <c r="H105" s="13"/>
-      <c r="I105" s="38"/>
-    </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A106" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="B106" s="63" t="s">
-        <v>8</v>
-      </c>
-      <c r="C106" s="37"/>
-      <c r="D106" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E106" s="36">
-        <v>113</v>
-      </c>
-      <c r="F106" s="13" t="s">
+      <c r="F106" s="11" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="7">
         <v>45672</v>
       </c>
-      <c r="H106" s="44" t="s">
+      <c r="H106" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="I106" s="28">
+        <v>45705</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A107" s="11"/>
+      <c r="B107" s="51" t="s">
+        <v>86</v>
+      </c>
+      <c r="C107" s="27"/>
+      <c r="D107" s="11"/>
+      <c r="E107" s="26"/>
+      <c r="F107" s="11"/>
+      <c r="G107" s="7"/>
+      <c r="H107" s="11"/>
+      <c r="I107" s="28"/>
+    </row>
+    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A108" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B108" s="51" t="s">
+        <v>8</v>
+      </c>
+      <c r="C108" s="27"/>
+      <c r="D108" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E108" s="26">
+        <v>113</v>
+      </c>
+      <c r="F108" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="G108" s="7">
+        <v>45672</v>
+      </c>
+      <c r="H108" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="I106" s="38">
+      <c r="I108" s="28">
         <v>45705</v>
       </c>
     </row>
-    <row r="110" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="11"/>
-      <c r="B110" s="8"/>
-      <c r="C110" s="23"/>
-      <c r="D110" s="11"/>
-      <c r="E110" s="8"/>
-      <c r="F110" s="9"/>
-      <c r="G110" s="9"/>
-      <c r="H110" s="9"/>
-      <c r="I110" s="9"/>
-    </row>
-    <row r="111" spans="1:10" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="28" t="s">
+    <row r="112" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A112" s="10"/>
+      <c r="B112" s="8"/>
+      <c r="C112" s="17"/>
+      <c r="D112" s="10"/>
+      <c r="E112" s="8"/>
+      <c r="F112" s="9"/>
+      <c r="G112" s="9"/>
+      <c r="H112" s="9"/>
+      <c r="I112" s="9"/>
+    </row>
+    <row r="113" spans="1:9" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="B111" s="63" t="s">
+      <c r="B113" s="123" t="s">
         <v>9</v>
       </c>
-      <c r="C111" s="30">
+      <c r="C113" s="164">
         <v>45438</v>
       </c>
-      <c r="D111" s="28" t="s">
+      <c r="D113" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="E111" s="29">
+      <c r="E113" s="22">
         <v>0</v>
       </c>
-      <c r="F111" s="12" t="s">
+      <c r="F113" s="160" t="s">
         <v>27</v>
       </c>
-      <c r="G111" s="31"/>
-      <c r="H111" s="29"/>
-      <c r="I111" s="31"/>
-    </row>
-    <row r="112" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A112" s="28"/>
-      <c r="B112" s="67" t="s">
+      <c r="G113" s="29"/>
+      <c r="H113" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="I113" s="29"/>
+    </row>
+    <row r="114" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A114" s="22"/>
+      <c r="B114" s="163" t="s">
         <v>17</v>
       </c>
-      <c r="C112" s="32">
+      <c r="C114" s="161">
         <v>45486</v>
       </c>
-      <c r="D112" s="28" t="s">
+      <c r="D114" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="E112" s="29"/>
-      <c r="F112" s="33" t="s">
+      <c r="E114" s="22"/>
+      <c r="F114" s="162" t="s">
         <v>27</v>
       </c>
-      <c r="G112" s="34">
+      <c r="G114" s="166">
         <v>45588</v>
       </c>
-      <c r="H112" s="29"/>
-      <c r="I112" s="31"/>
-    </row>
-    <row r="113" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A113" s="28"/>
-      <c r="B113" s="67" t="s">
+      <c r="H114" s="22" t="s">
+        <v>118</v>
+      </c>
+      <c r="I114" s="29"/>
+    </row>
+    <row r="115" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A115" s="22"/>
+      <c r="B115" s="163" t="s">
         <v>18</v>
       </c>
-      <c r="C113" s="32">
+      <c r="C115" s="161">
         <v>45590</v>
       </c>
-      <c r="D113" s="28" t="s">
+      <c r="D115" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="E113" s="28"/>
-      <c r="F113" s="33" t="s">
+      <c r="E115" s="22"/>
+      <c r="F115" s="162" t="s">
         <v>27</v>
       </c>
-      <c r="G113" s="34">
+      <c r="G115" s="166">
         <v>45688</v>
       </c>
-      <c r="H113" s="29"/>
-      <c r="I113" s="31"/>
-    </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A114" s="16"/>
-      <c r="B114" s="17"/>
-      <c r="C114" s="35"/>
-      <c r="D114" s="16" t="s">
+      <c r="H115" s="22" t="s">
+        <v>116</v>
+      </c>
+      <c r="I115" s="29"/>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A116" s="22"/>
+      <c r="B116" s="124"/>
+      <c r="C116" s="125"/>
+      <c r="D116" s="124" t="s">
         <v>32</v>
       </c>
-      <c r="E114" s="17"/>
-      <c r="F114" s="18"/>
-      <c r="G114" s="19"/>
-      <c r="H114" s="15"/>
-      <c r="I114" s="14"/>
-    </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A115" s="1"/>
-      <c r="B115" s="20"/>
-      <c r="C115" s="26"/>
-      <c r="D115" s="1"/>
-      <c r="E115" s="20"/>
-      <c r="F115" s="22"/>
-      <c r="G115" s="21"/>
-    </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A116" s="1"/>
-      <c r="B116" s="20"/>
-      <c r="C116" s="26"/>
-      <c r="D116" s="1"/>
-      <c r="E116" s="20"/>
-      <c r="F116" s="22"/>
-      <c r="G116" s="21"/>
+      <c r="E116" s="124"/>
+      <c r="F116" s="126"/>
+      <c r="G116" s="165">
+        <v>45782</v>
+      </c>
+      <c r="H116" s="22" t="s">
+        <v>117</v>
+      </c>
+      <c r="I116" s="29"/>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A117" s="1"/>
+      <c r="B117" s="14"/>
+      <c r="C117" s="20"/>
+      <c r="D117" s="1"/>
+      <c r="E117" s="14"/>
+      <c r="F117" s="16"/>
+      <c r="G117" s="15"/>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A118" s="1"/>
+      <c r="B118" s="14"/>
+      <c r="C118" s="20"/>
+      <c r="D118" s="1"/>
+      <c r="E118" s="14"/>
+      <c r="F118" s="16"/>
+      <c r="G118" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/mahkeme/2025-02-Dosya Listesi.xlsx
+++ b/mahkeme/2025-02-Dosya Listesi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\aaGitMe\yzhn\mahkeme\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{376551AE-B91C-4240-8626-444BAAE66197}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75547575-94AD-4E5E-9A80-DEA0F1073CB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -827,7 +827,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="167">
+  <cellXfs count="166">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -997,9 +997,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1414,7 +1411,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J118"/>
+  <dimension ref="A1:J119"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -1442,7 +1439,7 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="101"/>
-      <c r="B2" s="139" t="s">
+      <c r="B2" s="138" t="s">
         <v>114</v>
       </c>
       <c r="C2" s="103" t="s">
@@ -1468,26 +1465,26 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="101"/>
-      <c r="B4" s="143" t="s">
+      <c r="B4" s="142" t="s">
         <v>115</v>
       </c>
       <c r="C4" s="103"/>
-      <c r="D4" s="139" t="s">
+      <c r="D4" s="138" t="s">
         <v>16</v>
       </c>
       <c r="E4" s="102"/>
       <c r="F4" s="102"/>
-      <c r="G4" s="139" t="s">
+      <c r="G4" s="138" t="s">
         <v>112</v>
       </c>
-      <c r="H4" s="139" t="s">
+      <c r="H4" s="138" t="s">
         <v>111</v>
       </c>
       <c r="I4" s="102"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="101"/>
-      <c r="B5" s="143" t="s">
+      <c r="B5" s="142" t="s">
         <v>115</v>
       </c>
       <c r="C5" s="61" t="s">
@@ -1498,10 +1495,10 @@
       </c>
       <c r="E5" s="102"/>
       <c r="F5" s="102"/>
-      <c r="G5" s="140" t="s">
+      <c r="G5" s="139" t="s">
         <v>113</v>
       </c>
-      <c r="H5" s="139" t="s">
+      <c r="H5" s="138" t="s">
         <v>111</v>
       </c>
       <c r="I5" s="102"/>
@@ -1520,70 +1517,88 @@
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="101"/>
       <c r="B7" s="141" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C7" s="19">
-        <v>45939</v>
-      </c>
-      <c r="D7" s="105" t="s">
-        <v>105</v>
-      </c>
-      <c r="E7" s="105">
+        <v>45827</v>
+      </c>
+      <c r="D7" s="103" t="s">
+        <v>97</v>
+      </c>
+      <c r="E7">
         <v>9</v>
       </c>
-      <c r="F7" s="105">
-        <v>30</v>
+      <c r="F7">
+        <v>40</v>
       </c>
       <c r="H7" s="102" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="I7" s="102"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="101"/>
-      <c r="B8" s="141" t="s">
-        <v>102</v>
-      </c>
-      <c r="C8" s="103">
-        <v>45939</v>
-      </c>
-      <c r="D8" s="102" t="s">
-        <v>104</v>
-      </c>
-      <c r="E8" s="102">
-        <v>9</v>
-      </c>
-      <c r="F8" s="102">
-        <v>40</v>
-      </c>
+      <c r="B8" s="102"/>
+      <c r="C8" s="103"/>
+      <c r="D8" s="102"/>
+      <c r="E8" s="102"/>
+      <c r="F8" s="102"/>
       <c r="G8" s="72"/>
-      <c r="H8" s="102" t="s">
-        <v>103</v>
-      </c>
+      <c r="H8" s="102"/>
       <c r="I8" s="102"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="101"/>
-      <c r="B9" s="102"/>
-      <c r="C9" s="103"/>
-      <c r="D9" s="102"/>
-      <c r="E9" s="102"/>
-      <c r="F9" s="102"/>
-      <c r="G9" s="72"/>
-      <c r="H9" s="102"/>
+      <c r="B9" s="140" t="s">
+        <v>106</v>
+      </c>
+      <c r="C9" s="19">
+        <v>45939</v>
+      </c>
+      <c r="D9" s="104" t="s">
+        <v>105</v>
+      </c>
+      <c r="E9" s="104">
+        <v>9</v>
+      </c>
+      <c r="F9" s="104">
+        <v>30</v>
+      </c>
+      <c r="H9" s="102" t="s">
+        <v>103</v>
+      </c>
       <c r="I9" s="102"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="104"/>
-      <c r="I10" s="72"/>
+      <c r="A10" s="101"/>
+      <c r="B10" s="140" t="s">
+        <v>102</v>
+      </c>
+      <c r="C10" s="103">
+        <v>45939</v>
+      </c>
+      <c r="D10" s="102" t="s">
+        <v>104</v>
+      </c>
+      <c r="E10" s="102">
+        <v>9</v>
+      </c>
+      <c r="F10" s="102">
+        <v>40</v>
+      </c>
+      <c r="G10" s="72"/>
+      <c r="H10" s="102" t="s">
+        <v>103</v>
+      </c>
+      <c r="I10" s="102"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="101"/>
-      <c r="B11" s="142" t="s">
+      <c r="B11" s="140" t="s">
         <v>36</v>
       </c>
       <c r="C11" s="103">
-        <v>45805</v>
+        <v>45952</v>
       </c>
       <c r="D11" s="102" t="s">
         <v>101</v>
@@ -1592,7 +1607,7 @@
         <v>9</v>
       </c>
       <c r="F11">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="G11" s="102"/>
       <c r="H11" s="102" t="s">
@@ -1602,17 +1617,21 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="101"/>
-      <c r="B12" s="142" t="s">
+      <c r="B12" s="140" t="s">
         <v>35</v>
       </c>
       <c r="C12" s="103">
-        <v>45805</v>
+        <v>45952</v>
       </c>
       <c r="D12" s="102" t="s">
         <v>101</v>
       </c>
-      <c r="E12" s="102"/>
-      <c r="F12" s="102"/>
+      <c r="E12" s="102">
+        <v>9</v>
+      </c>
+      <c r="F12" s="102">
+        <v>35</v>
+      </c>
       <c r="G12" s="72"/>
       <c r="H12" s="102" t="s">
         <v>100</v>
@@ -1621,640 +1640,621 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="101"/>
-      <c r="B13" s="142" t="s">
-        <v>96</v>
-      </c>
-      <c r="C13" s="19">
-        <v>45827</v>
-      </c>
-      <c r="D13" s="103" t="s">
-        <v>97</v>
-      </c>
-      <c r="E13">
-        <v>9</v>
-      </c>
-      <c r="F13">
-        <v>40</v>
-      </c>
-      <c r="H13" s="102" t="s">
-        <v>98</v>
-      </c>
-      <c r="I13" s="102"/>
+      <c r="B13" s="104"/>
+      <c r="C13" s="103"/>
+      <c r="D13" s="102"/>
+      <c r="E13" s="102"/>
+      <c r="F13" s="102"/>
+      <c r="G13" s="72"/>
+      <c r="H13" s="102"/>
+      <c r="I13" s="72"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="101"/>
       <c r="I14" s="102"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="49"/>
-      <c r="I15"/>
-      <c r="J15" s="61"/>
-    </row>
-    <row r="16" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="127"/>
-      <c r="B16" s="128" t="s">
+      <c r="A15" s="101"/>
+      <c r="I15" s="102"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="49"/>
+      <c r="I16"/>
+      <c r="J16" s="61"/>
+    </row>
+    <row r="17" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="126"/>
+      <c r="B17" s="127" t="s">
         <v>29</v>
       </c>
-      <c r="C16" s="129" t="s">
+      <c r="C17" s="128" t="s">
         <v>30</v>
       </c>
-      <c r="D16" s="128"/>
-      <c r="E16" s="130" t="s">
+      <c r="D17" s="127"/>
+      <c r="E17" s="129" t="s">
         <v>28</v>
       </c>
-      <c r="F16" s="130"/>
-      <c r="G16" s="131" t="s">
+      <c r="F17" s="129"/>
+      <c r="G17" s="130" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="128" t="s">
+      <c r="H17" s="127" t="s">
         <v>39</v>
       </c>
-      <c r="I16" s="128" t="s">
+      <c r="I17" s="127" t="s">
         <v>51</v>
       </c>
-      <c r="J16" s="3"/>
-    </row>
-    <row r="17" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="22" t="s">
+      <c r="J17" s="3"/>
+    </row>
+    <row r="18" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="51" t="s">
+      <c r="B18" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="24">
+      <c r="C18" s="24">
         <v>45342</v>
       </c>
-      <c r="D17" s="22" t="s">
+      <c r="D18" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="E17" s="23"/>
-      <c r="F17" s="29" t="s">
+      <c r="E18" s="23"/>
+      <c r="F18" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="G17" s="25"/>
-      <c r="H17" s="23"/>
-      <c r="I17" s="25"/>
-      <c r="J17" s="3"/>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="22"/>
-      <c r="B18" s="54" t="s">
-        <v>24</v>
-      </c>
-      <c r="C18" s="24">
-        <v>45537</v>
-      </c>
-      <c r="D18" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="E18" s="23"/>
-      <c r="F18" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="G18" s="25">
-        <v>45691</v>
-      </c>
+      <c r="G18" s="25"/>
       <c r="H18" s="23"/>
       <c r="I18" s="25"/>
       <c r="J18" s="3"/>
     </row>
-    <row r="19" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="44"/>
-      <c r="B19" s="45"/>
-      <c r="C19" s="46"/>
-      <c r="D19" s="13" t="s">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="22"/>
+      <c r="B19" s="54" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" s="24">
+        <v>45537</v>
+      </c>
+      <c r="D19" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" s="23"/>
+      <c r="F19" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="G19" s="25">
+        <v>45691</v>
+      </c>
+      <c r="H19" s="23"/>
+      <c r="I19" s="25"/>
+      <c r="J19" s="3"/>
+    </row>
+    <row r="20" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="44"/>
+      <c r="B20" s="45"/>
+      <c r="C20" s="46"/>
+      <c r="D20" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="F19" s="5"/>
-      <c r="H19" s="5"/>
-      <c r="J19" s="3"/>
-    </row>
-    <row r="20" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="1"/>
-      <c r="C20" s="98">
+      <c r="F20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="J20" s="3"/>
+    </row>
+    <row r="21" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="1"/>
+      <c r="C21" s="98">
         <v>45726</v>
       </c>
-      <c r="D20" s="99" t="s">
+      <c r="D21" s="99" t="s">
         <v>85</v>
       </c>
-      <c r="E20" s="99"/>
-      <c r="F20" s="100"/>
-      <c r="G20" s="100"/>
-      <c r="H20" s="47"/>
-      <c r="I20" s="48"/>
-      <c r="J20" s="3"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="1"/>
-      <c r="C21" s="69"/>
-      <c r="D21" s="70"/>
-      <c r="E21" s="70"/>
-      <c r="F21" s="71"/>
-      <c r="G21" s="71"/>
-      <c r="H21" s="72"/>
-      <c r="I21" s="72"/>
+      <c r="E21" s="99"/>
+      <c r="F21" s="100"/>
+      <c r="G21" s="100"/>
+      <c r="H21" s="47"/>
+      <c r="I21" s="48"/>
       <c r="J21" s="3"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="49"/>
-      <c r="I22"/>
+      <c r="A22" s="1"/>
+      <c r="C22" s="69"/>
+      <c r="D22" s="70"/>
+      <c r="E22" s="70"/>
+      <c r="F22" s="71"/>
+      <c r="G22" s="71"/>
+      <c r="H22" s="72"/>
+      <c r="I22" s="72"/>
       <c r="J22" s="3"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="132"/>
-      <c r="B23" s="3"/>
-      <c r="C23" s="18"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
+      <c r="A23" s="49"/>
+      <c r="I23"/>
       <c r="J23" s="3"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="49"/>
-      <c r="I24"/>
+      <c r="A24" s="131"/>
+      <c r="B24" s="3"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
+      <c r="J24" s="3"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="49"/>
       <c r="I25"/>
     </row>
-    <row r="26" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="73"/>
-      <c r="B26" s="74" t="s">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="49"/>
+      <c r="I26"/>
+    </row>
+    <row r="27" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="73"/>
+      <c r="B27" s="74" t="s">
         <v>29</v>
       </c>
-      <c r="C26" s="75" t="s">
+      <c r="C27" s="75" t="s">
         <v>30</v>
       </c>
-      <c r="D26" s="74"/>
-      <c r="E26" s="76" t="s">
+      <c r="D27" s="74"/>
+      <c r="E27" s="76" t="s">
         <v>28</v>
       </c>
-      <c r="F26" s="76"/>
-      <c r="G26" s="77" t="s">
+      <c r="F27" s="76"/>
+      <c r="G27" s="77" t="s">
         <v>31</v>
       </c>
-      <c r="H26" s="74" t="s">
+      <c r="H27" s="74" t="s">
         <v>39</v>
       </c>
-      <c r="I26" s="74" t="s">
+      <c r="I27" s="74" t="s">
         <v>51</v>
       </c>
-      <c r="J26" s="62"/>
-    </row>
-    <row r="27" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="49" t="s">
+      <c r="J27" s="62"/>
+    </row>
+    <row r="28" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="49" t="s">
         <v>77</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="D28" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="H27" s="4" t="s">
+      <c r="H28" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="I27" s="50">
+      <c r="I28" s="50">
         <v>45712</v>
       </c>
-      <c r="J27" s="62"/>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="49"/>
-      <c r="I28"/>
       <c r="J28" s="62"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="60"/>
-      <c r="B29" s="61"/>
-      <c r="C29" s="67"/>
-      <c r="D29" s="60"/>
-      <c r="E29" s="60"/>
-      <c r="F29" s="60"/>
-      <c r="G29" s="68"/>
-      <c r="H29" s="60"/>
-      <c r="I29" s="65" t="s">
+      <c r="A29" s="49"/>
+      <c r="I29"/>
+      <c r="J29" s="62"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" s="60"/>
+      <c r="B30" s="61"/>
+      <c r="C30" s="67"/>
+      <c r="D30" s="60"/>
+      <c r="E30" s="60"/>
+      <c r="F30" s="60"/>
+      <c r="G30" s="68"/>
+      <c r="H30" s="60"/>
+      <c r="I30" s="65" t="s">
         <v>93</v>
       </c>
-      <c r="J29" s="62"/>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="2"/>
-      <c r="B30" s="62"/>
-      <c r="C30" s="66"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="63"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="63"/>
       <c r="J30" s="62"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" s="49"/>
-      <c r="I31"/>
+      <c r="A31" s="2"/>
+      <c r="B31" s="62"/>
+      <c r="C31" s="66"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="63"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="63"/>
+      <c r="J31" s="62"/>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="49"/>
       <c r="I32"/>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="133"/>
-      <c r="B33" s="134" t="s">
+      <c r="A33" s="49"/>
+      <c r="I33"/>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" s="132"/>
+      <c r="B34" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="C33" s="135" t="s">
+      <c r="C34" s="134" t="s">
         <v>30</v>
       </c>
-      <c r="D33" s="134"/>
-      <c r="E33" s="136" t="s">
+      <c r="D34" s="133"/>
+      <c r="E34" s="135" t="s">
         <v>28</v>
       </c>
-      <c r="F33" s="136"/>
-      <c r="G33" s="137" t="s">
+      <c r="F34" s="135"/>
+      <c r="G34" s="136" t="s">
         <v>31</v>
       </c>
-      <c r="H33" s="134" t="s">
+      <c r="H34" s="133" t="s">
         <v>39</v>
       </c>
-      <c r="I33" s="134" t="s">
+      <c r="I34" s="133" t="s">
         <v>51</v>
       </c>
-      <c r="J33" s="3"/>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="2" t="s">
+      <c r="J34" s="3"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B34" s="51" t="s">
+      <c r="B35" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="C34" s="18">
+      <c r="C35" s="18">
         <v>45475</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E34" s="37">
-        <v>97</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H34" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="I34" s="6">
-        <v>45705</v>
-      </c>
-      <c r="J34" s="3"/>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" s="4"/>
-      <c r="B35" s="52" t="s">
-        <v>2</v>
-      </c>
-      <c r="C35" s="18">
-        <v>45604</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>20</v>
       </c>
       <c r="E35" s="37">
-        <v>178</v>
+        <v>97</v>
       </c>
       <c r="F35" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="H35" s="11" t="s">
+      <c r="H35" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="I35" s="6">
+        <v>45705</v>
+      </c>
+      <c r="J35" s="3"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" s="4"/>
+      <c r="B36" s="52" t="s">
+        <v>2</v>
+      </c>
+      <c r="C36" s="18">
+        <v>45604</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E36" s="37">
+        <v>178</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H36" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="I35" s="21">
+      <c r="I36" s="21">
         <v>45705</v>
-      </c>
-      <c r="J35" s="3"/>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="1"/>
-      <c r="B36" s="53" t="s">
-        <v>36</v>
-      </c>
-      <c r="C36" s="19">
-        <v>45704</v>
-      </c>
-      <c r="D36" s="43" t="s">
-        <v>82</v>
       </c>
       <c r="J36" s="3"/>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
-      <c r="B37" s="1" t="s">
-        <v>65</v>
+      <c r="B37" s="53" t="s">
+        <v>36</v>
       </c>
       <c r="C37" s="19">
-        <v>45705</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="H37" s="1"/>
+        <v>45704</v>
+      </c>
+      <c r="D37" s="43" t="s">
+        <v>82</v>
+      </c>
       <c r="J37" s="3"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
-      <c r="C38" s="38"/>
-      <c r="D38" s="1"/>
+      <c r="B38" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C38" s="19">
+        <v>45705</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>59</v>
+      </c>
       <c r="H38" s="1"/>
       <c r="J38" s="3"/>
     </row>
-    <row r="39" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
-      <c r="C39" s="38" t="s">
-        <v>56</v>
-      </c>
-      <c r="D39" s="43" t="s">
-        <v>61</v>
-      </c>
+      <c r="C39" s="38"/>
+      <c r="D39" s="1"/>
       <c r="H39" s="1"/>
       <c r="J39" s="3"/>
     </row>
     <row r="40" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
-      <c r="C40" s="94">
+      <c r="C40" s="38" t="s">
+        <v>56</v>
+      </c>
+      <c r="D40" s="43" t="s">
+        <v>61</v>
+      </c>
+      <c r="H40" s="1"/>
+      <c r="J40" s="3"/>
+    </row>
+    <row r="41" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="1"/>
+      <c r="C41" s="94">
         <v>45717</v>
       </c>
-      <c r="D40" s="95" t="s">
+      <c r="D41" s="95" t="s">
         <v>76</v>
       </c>
-      <c r="E40" s="96" t="s">
+      <c r="E41" s="96" t="s">
         <v>62</v>
       </c>
-      <c r="F40" s="95"/>
-      <c r="G40" s="97"/>
-      <c r="H40" s="95" t="s">
+      <c r="F41" s="95"/>
+      <c r="G41" s="97"/>
+      <c r="H41" s="95" t="s">
         <v>63</v>
       </c>
-      <c r="I40" s="64" t="s">
+      <c r="I41" s="64" t="s">
         <v>81</v>
       </c>
-      <c r="J40" s="3"/>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A41" s="1"/>
-      <c r="C41" s="41"/>
-      <c r="D41" s="1" t="s">
+      <c r="J41" s="3"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="1"/>
+      <c r="C42" s="41"/>
+      <c r="D42" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="H41" s="1" t="s">
+      <c r="H42" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="J41" s="3"/>
-    </row>
-    <row r="42" spans="1:10" s="144" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="149" t="s">
+      <c r="J42" s="3"/>
+    </row>
+    <row r="43" spans="1:10" s="143" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B43" s="148" t="s">
         <v>53</v>
       </c>
-      <c r="C42" s="150">
+      <c r="C43" s="149">
         <v>45805</v>
       </c>
-      <c r="D42" s="151">
+      <c r="D43" s="150">
         <v>0.40972222222222227</v>
       </c>
-      <c r="E42" s="145" t="s">
+      <c r="E43" s="144" t="s">
         <v>55</v>
       </c>
-      <c r="F42" s="145"/>
-      <c r="G42" s="146"/>
-      <c r="I42" s="147"/>
-      <c r="J42" s="148"/>
-    </row>
-    <row r="43" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="4"/>
-      <c r="B43" s="3"/>
-      <c r="C43" s="152">
+      <c r="F43" s="144"/>
+      <c r="G43" s="145"/>
+      <c r="I43" s="146"/>
+      <c r="J43" s="147"/>
+    </row>
+    <row r="44" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="4"/>
+      <c r="B44" s="3"/>
+      <c r="C44" s="151">
         <v>45805</v>
       </c>
-      <c r="D43" s="37" t="s">
+      <c r="D44" s="37" t="s">
         <v>57</v>
       </c>
-      <c r="E43" s="37"/>
-      <c r="F43" s="37"/>
-      <c r="G43" s="153"/>
-      <c r="H43" s="3"/>
-      <c r="I43" s="6"/>
-      <c r="J43" s="3"/>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A44" s="1"/>
+      <c r="E44" s="37"/>
+      <c r="F44" s="37"/>
+      <c r="G44" s="152"/>
+      <c r="H44" s="3"/>
+      <c r="I44" s="6"/>
+      <c r="J44" s="3"/>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="1"/>
-      <c r="C45" s="38"/>
-      <c r="D45" s="1"/>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A46" s="133"/>
-      <c r="B46" s="134" t="s">
+      <c r="A46" s="1"/>
+      <c r="C46" s="38"/>
+      <c r="D46" s="1"/>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A47" s="132"/>
+      <c r="B47" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="C46" s="135" t="s">
+      <c r="C47" s="134" t="s">
         <v>30</v>
       </c>
-      <c r="D46" s="134"/>
-      <c r="E46" s="136" t="s">
+      <c r="D47" s="133"/>
+      <c r="E47" s="135" t="s">
         <v>28</v>
       </c>
-      <c r="F46" s="136"/>
-      <c r="G46" s="137" t="s">
+      <c r="F47" s="135"/>
+      <c r="G47" s="136" t="s">
         <v>31</v>
       </c>
-      <c r="H46" s="134" t="s">
+      <c r="H47" s="133" t="s">
         <v>39</v>
       </c>
-      <c r="I46" s="134" t="s">
+      <c r="I47" s="133" t="s">
         <v>51</v>
       </c>
-      <c r="J46" s="3"/>
-    </row>
-    <row r="47" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="4" t="s">
+      <c r="J47" s="3"/>
+    </row>
+    <row r="48" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B47" s="51" t="s">
-        <v>4</v>
-      </c>
-      <c r="C47" s="56">
-        <v>45588</v>
-      </c>
-      <c r="D47" s="37" t="s">
-        <v>21</v>
-      </c>
-      <c r="E47" s="3"/>
-      <c r="F47" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H47" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="I47" s="6">
-        <v>45630</v>
-      </c>
-      <c r="J47" s="3"/>
-    </row>
-    <row r="48" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="4"/>
       <c r="B48" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="C48" s="18"/>
-      <c r="D48" s="4"/>
+      <c r="C48" s="56">
+        <v>45588</v>
+      </c>
+      <c r="D48" s="37" t="s">
+        <v>21</v>
+      </c>
       <c r="E48" s="3"/>
-      <c r="F48" s="4"/>
-      <c r="H48" s="11" t="s">
-        <v>47</v>
+      <c r="F48" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H48" s="4" t="s">
+        <v>46</v>
       </c>
       <c r="I48" s="6">
         <v>45630</v>
       </c>
       <c r="J48" s="3"/>
     </row>
-    <row r="49" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A49" s="4"/>
-      <c r="B49" s="53" t="s">
+      <c r="B49" s="51" t="s">
+        <v>4</v>
+      </c>
+      <c r="C49" s="18"/>
+      <c r="D49" s="4"/>
+      <c r="E49" s="3"/>
+      <c r="F49" s="4"/>
+      <c r="H49" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="I49" s="6">
+        <v>45630</v>
+      </c>
+      <c r="J49" s="3"/>
+    </row>
+    <row r="50" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="4"/>
+      <c r="B50" s="53" t="s">
         <v>35</v>
       </c>
-      <c r="C49" s="35">
+      <c r="C50" s="35">
         <v>45704</v>
       </c>
-      <c r="D49" s="43" t="s">
+      <c r="D50" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="E49" s="1"/>
-      <c r="F49" s="1"/>
-      <c r="H49" s="1"/>
-      <c r="I49"/>
-      <c r="J49" s="3"/>
-    </row>
-    <row r="50" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="1"/>
-      <c r="B50" s="1" t="s">
+      <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
+      <c r="H50" s="1"/>
+      <c r="I50"/>
+      <c r="J50" s="3"/>
+    </row>
+    <row r="51" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="1"/>
+      <c r="B51" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C50" s="19">
+      <c r="C51" s="19">
         <v>45709</v>
       </c>
-      <c r="D50" s="1" t="s">
+      <c r="D51" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="H50" s="1"/>
-      <c r="J50" s="3"/>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A51" s="1"/>
-      <c r="C51" s="38" t="s">
-        <v>56</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>64</v>
       </c>
       <c r="H51" s="1"/>
       <c r="J51" s="3"/>
     </row>
-    <row r="52" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="1"/>
-      <c r="C52" s="38">
-        <v>45712</v>
+      <c r="C52" s="38" t="s">
+        <v>56</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="H52" s="1"/>
       <c r="J52" s="3"/>
     </row>
     <row r="53" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1"/>
-      <c r="C53" s="88">
+      <c r="C53" s="38">
+        <v>45712</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H53" s="1"/>
+      <c r="J53" s="3"/>
+    </row>
+    <row r="54" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="1"/>
+      <c r="C54" s="88">
         <v>45717</v>
       </c>
-      <c r="D53" s="89" t="s">
+      <c r="D54" s="89" t="s">
         <v>76</v>
       </c>
-      <c r="E53" s="90" t="s">
+      <c r="E54" s="90" t="s">
         <v>62</v>
       </c>
-      <c r="F53" s="89"/>
-      <c r="G53" s="91"/>
-      <c r="H53" s="89" t="s">
+      <c r="F54" s="89"/>
+      <c r="G54" s="91"/>
+      <c r="H54" s="89" t="s">
         <v>63</v>
       </c>
-      <c r="I53" s="92"/>
-      <c r="J53" s="3"/>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A54" s="1"/>
-      <c r="C54" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="F54" s="5"/>
-      <c r="G54" s="58"/>
-      <c r="H54" s="57"/>
-      <c r="I54" s="58"/>
+      <c r="I54" s="92"/>
       <c r="J54" s="3"/>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="1"/>
       <c r="C55" s="1" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="F55" s="5"/>
       <c r="G55" s="58"/>
       <c r="H55" s="57"/>
-      <c r="I55" s="55" t="s">
+      <c r="I55" s="58"/>
+      <c r="J55" s="3"/>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A56" s="1"/>
+      <c r="C56" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F56" s="5"/>
+      <c r="G56" s="58"/>
+      <c r="H56" s="57"/>
+      <c r="I56" s="55" t="s">
         <v>81</v>
       </c>
-      <c r="J55" s="3"/>
-    </row>
-    <row r="56" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="1"/>
-      <c r="B56" s="32" t="s">
+      <c r="J56" s="3"/>
+    </row>
+    <row r="57" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="1"/>
+      <c r="B57" s="32" t="s">
         <v>53</v>
       </c>
-      <c r="C56" s="33">
+      <c r="C57" s="33">
         <v>45805</v>
       </c>
-      <c r="D56" s="39">
+      <c r="D57" s="39">
         <v>0</v>
       </c>
-      <c r="J56" s="3"/>
-    </row>
-    <row r="57" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="4"/>
-      <c r="B57" s="3"/>
-      <c r="C57" s="138">
+      <c r="J57" s="3"/>
+    </row>
+    <row r="58" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="4"/>
+      <c r="B58" s="3"/>
+      <c r="C58" s="137">
         <v>45805</v>
       </c>
-      <c r="D57" s="4" t="s">
+      <c r="D58" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="E57" s="3"/>
-      <c r="F57" s="3"/>
-      <c r="G57" s="6"/>
-      <c r="H57" s="3"/>
-      <c r="I57" s="6"/>
-      <c r="J57" s="3"/>
-    </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A58" s="60"/>
-      <c r="B58" s="61"/>
-      <c r="C58" s="87"/>
-      <c r="D58" s="60"/>
-      <c r="E58" s="61"/>
-      <c r="F58" s="61"/>
-      <c r="G58" s="68"/>
-      <c r="H58" s="61"/>
-      <c r="I58" s="68"/>
-      <c r="J58" s="61"/>
+      <c r="E58" s="3"/>
+      <c r="F58" s="3"/>
+      <c r="G58" s="6"/>
+      <c r="H58" s="3"/>
+      <c r="I58" s="6"/>
+      <c r="J58" s="3"/>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="60"/>
@@ -2269,244 +2269,249 @@
       <c r="J59" s="61"/>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A60" s="1"/>
-      <c r="D60" s="1"/>
-      <c r="E60" s="1"/>
-      <c r="F60" s="1"/>
-      <c r="H60" s="1"/>
-      <c r="I60"/>
+      <c r="A60" s="60"/>
+      <c r="B60" s="61"/>
+      <c r="C60" s="87"/>
+      <c r="D60" s="60"/>
+      <c r="E60" s="61"/>
+      <c r="F60" s="61"/>
+      <c r="G60" s="68"/>
+      <c r="H60" s="61"/>
+      <c r="I60" s="68"/>
+      <c r="J60" s="61"/>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A61" s="118"/>
-      <c r="B61" s="119" t="s">
+      <c r="A61" s="1"/>
+      <c r="D61" s="1"/>
+      <c r="E61" s="1"/>
+      <c r="F61" s="1"/>
+      <c r="H61" s="1"/>
+      <c r="I61"/>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A62" s="117"/>
+      <c r="B62" s="118" t="s">
         <v>29</v>
       </c>
-      <c r="C61" s="120" t="s">
+      <c r="C62" s="119" t="s">
         <v>30</v>
       </c>
-      <c r="D61" s="119"/>
-      <c r="E61" s="121" t="s">
+      <c r="D62" s="118"/>
+      <c r="E62" s="120" t="s">
         <v>28</v>
       </c>
-      <c r="F61" s="121"/>
-      <c r="G61" s="122" t="s">
+      <c r="F62" s="120"/>
+      <c r="G62" s="121" t="s">
         <v>31</v>
       </c>
-      <c r="H61" s="119" t="s">
+      <c r="H62" s="118" t="s">
         <v>39</v>
       </c>
-      <c r="I61" s="119" t="s">
+      <c r="I62" s="118" t="s">
         <v>51</v>
       </c>
-      <c r="J61" s="113"/>
-    </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A62" s="2" t="s">
+      <c r="J62" s="112"/>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B62" s="51" t="s">
+      <c r="B63" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="C62" s="18">
+      <c r="C63" s="18">
         <v>45475</v>
       </c>
-      <c r="D62" s="4" t="s">
+      <c r="D63" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E62" s="37">
+      <c r="E63" s="37">
         <v>214</v>
       </c>
-      <c r="F62" s="4" t="s">
+      <c r="F63" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="H62" s="4" t="s">
+      <c r="H63" s="4" t="s">
         <v>40</v>
-      </c>
-      <c r="I62" s="6">
-        <v>45702</v>
-      </c>
-      <c r="J62" s="113"/>
-    </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A63" s="2"/>
-      <c r="B63" s="3"/>
-      <c r="C63" s="18"/>
-      <c r="D63" s="59">
-        <v>158437</v>
-      </c>
-      <c r="E63" s="3"/>
-      <c r="F63" s="4"/>
-      <c r="H63" s="11" t="s">
-        <v>49</v>
       </c>
       <c r="I63" s="6">
         <v>45702</v>
       </c>
-      <c r="J63" s="113"/>
+      <c r="J63" s="112"/>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A64" s="1"/>
-      <c r="B64" s="53" t="s">
-        <v>33</v>
-      </c>
-      <c r="C64" s="19">
-        <v>45704</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="H64" s="1"/>
-      <c r="I64"/>
-      <c r="J64" s="113"/>
+      <c r="A64" s="2"/>
+      <c r="B64" s="3"/>
+      <c r="C64" s="18"/>
+      <c r="D64" s="59">
+        <v>158437</v>
+      </c>
+      <c r="E64" s="3"/>
+      <c r="F64" s="4"/>
+      <c r="H64" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="I64" s="6">
+        <v>45702</v>
+      </c>
+      <c r="J64" s="112"/>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" s="1"/>
-      <c r="B65" s="1" t="s">
-        <v>65</v>
+      <c r="B65" s="53" t="s">
+        <v>33</v>
       </c>
       <c r="C65" s="19">
-        <v>45705</v>
+        <v>45704</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H65" s="1"/>
-      <c r="J65" s="113"/>
+      <c r="I65"/>
+      <c r="J65" s="112"/>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" s="1"/>
+      <c r="B66" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C66" s="19">
+        <v>45705</v>
+      </c>
       <c r="D66" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H66" s="1"/>
+      <c r="J66" s="112"/>
+    </row>
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A67" s="1"/>
+      <c r="D67" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="H66" s="1"/>
-      <c r="J66" s="113"/>
-    </row>
-    <row r="67" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="1"/>
-      <c r="C67" s="38" t="s">
+      <c r="H67" s="1"/>
+      <c r="J67" s="112"/>
+    </row>
+    <row r="68" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="1"/>
+      <c r="C68" s="38" t="s">
         <v>56</v>
       </c>
-      <c r="D67" s="43" t="s">
+      <c r="D68" s="43" t="s">
         <v>68</v>
       </c>
-      <c r="H67" s="1"/>
-      <c r="J67" s="113"/>
-    </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A68" s="1"/>
-      <c r="C68" s="83">
+      <c r="H68" s="1"/>
+      <c r="J68" s="112"/>
+    </row>
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A69" s="1"/>
+      <c r="C69" s="83">
         <v>45711</v>
       </c>
-      <c r="D68" s="84" t="s">
+      <c r="D69" s="84" t="s">
         <v>69</v>
       </c>
-      <c r="E68" s="84"/>
-      <c r="F68" s="84"/>
-      <c r="G68" s="85"/>
-      <c r="H68" s="84"/>
-      <c r="I68" s="86"/>
-      <c r="J68" s="113"/>
-    </row>
-    <row r="69" spans="1:10" s="61" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="1" t="s">
+      <c r="E69" s="84"/>
+      <c r="F69" s="84"/>
+      <c r="G69" s="85"/>
+      <c r="H69" s="84"/>
+      <c r="I69" s="86"/>
+      <c r="J69" s="112"/>
+    </row>
+    <row r="70" spans="1:10" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="C69" s="41" t="s">
+      <c r="C70" s="41" t="s">
         <v>70</v>
       </c>
-      <c r="D69" s="57"/>
-      <c r="E69" s="57"/>
-      <c r="F69" s="57"/>
-      <c r="G69" s="58"/>
-      <c r="H69" s="57"/>
-      <c r="I69" s="58"/>
-      <c r="J69" s="113"/>
-    </row>
-    <row r="70" spans="1:10" s="61" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="60">
-        <v>1</v>
-      </c>
-      <c r="C70" s="41" t="s">
-        <v>88</v>
-      </c>
-      <c r="D70" s="43" t="s">
-        <v>90</v>
-      </c>
+      <c r="D70" s="57"/>
       <c r="E70" s="57"/>
       <c r="F70" s="57"/>
       <c r="G70" s="58"/>
       <c r="H70" s="57"/>
       <c r="I70" s="58"/>
-      <c r="J70" s="113"/>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A71" s="1"/>
-      <c r="D71" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="H71" s="1"/>
-      <c r="I71" s="65" t="s">
-        <v>92</v>
-      </c>
-      <c r="J71" s="113"/>
+      <c r="J70" s="112"/>
+    </row>
+    <row r="71" spans="1:10" s="61" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="60">
+        <v>1</v>
+      </c>
+      <c r="C71" s="41" t="s">
+        <v>88</v>
+      </c>
+      <c r="D71" s="43" t="s">
+        <v>90</v>
+      </c>
+      <c r="E71" s="57"/>
+      <c r="F71" s="57"/>
+      <c r="G71" s="58"/>
+      <c r="H71" s="57"/>
+      <c r="I71" s="58"/>
+      <c r="J71" s="112"/>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" s="1"/>
-      <c r="C72" s="41"/>
       <c r="D72" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H72" s="1"/>
       <c r="I72" s="65" t="s">
+        <v>92</v>
+      </c>
+      <c r="J72" s="112"/>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A73" s="1"/>
+      <c r="C73" s="41"/>
+      <c r="D73" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H73" s="1"/>
+      <c r="I73" s="65" t="s">
         <v>91</v>
       </c>
-      <c r="J72" s="113"/>
-    </row>
-    <row r="73" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="1"/>
-      <c r="B73" s="149" t="s">
+      <c r="J73" s="112"/>
+    </row>
+    <row r="74" spans="1:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="1"/>
+      <c r="B74" s="148" t="s">
         <v>53</v>
       </c>
-      <c r="C73" s="159">
+      <c r="C74" s="158">
         <v>45792</v>
       </c>
-      <c r="D73" s="151">
+      <c r="D74" s="150">
         <v>0.39930555555555558</v>
       </c>
-      <c r="E73" s="61"/>
-      <c r="F73" s="61"/>
-      <c r="J73" s="113"/>
-    </row>
-    <row r="74" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="123"/>
-      <c r="B74" s="154" t="s">
+      <c r="E74" s="61"/>
+      <c r="F74" s="61"/>
+      <c r="J74" s="112"/>
+    </row>
+    <row r="75" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="122"/>
+      <c r="B75" s="153" t="s">
         <v>110</v>
       </c>
-      <c r="C74" s="155">
+      <c r="C75" s="154">
         <v>45939</v>
       </c>
-      <c r="D74" s="156">
+      <c r="D75" s="155">
         <v>0.40277777777777773</v>
       </c>
-      <c r="E74" s="157"/>
-      <c r="F74" s="157"/>
-      <c r="G74" s="158" t="s">
+      <c r="E75" s="156"/>
+      <c r="F75" s="156"/>
+      <c r="G75" s="157" t="s">
         <v>67</v>
       </c>
-      <c r="H74" s="158" t="s">
+      <c r="H75" s="157" t="s">
         <v>108</v>
       </c>
-      <c r="I74" s="158" t="s">
+      <c r="I75" s="157" t="s">
         <v>109</v>
       </c>
-      <c r="J74" s="113"/>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A75" s="1"/>
-      <c r="C75" s="38"/>
-      <c r="D75" s="1"/>
-      <c r="H75" s="1"/>
-      <c r="I75"/>
+      <c r="J75" s="112"/>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" s="1"/>
@@ -2516,48 +2521,33 @@
       <c r="I76"/>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A77" s="78"/>
-      <c r="B77" s="79" t="s">
+      <c r="A77" s="1"/>
+      <c r="C77" s="38"/>
+      <c r="D77" s="1"/>
+      <c r="H77" s="1"/>
+      <c r="I77"/>
+    </row>
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A78" s="78"/>
+      <c r="B78" s="79" t="s">
         <v>29</v>
       </c>
-      <c r="C77" s="80" t="s">
+      <c r="C78" s="80" t="s">
         <v>30</v>
       </c>
-      <c r="D77" s="79"/>
-      <c r="E77" s="81" t="s">
+      <c r="D78" s="79"/>
+      <c r="E78" s="81" t="s">
         <v>28</v>
       </c>
-      <c r="F77" s="81"/>
-      <c r="G77" s="82" t="s">
+      <c r="F78" s="81"/>
+      <c r="G78" s="82" t="s">
         <v>31</v>
       </c>
-      <c r="H77" s="79" t="s">
+      <c r="H78" s="79" t="s">
         <v>39</v>
       </c>
-      <c r="I77" s="79" t="s">
+      <c r="I78" s="79" t="s">
         <v>51</v>
-      </c>
-      <c r="J77" s="62"/>
-    </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A78" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B78" s="51" t="s">
-        <v>1</v>
-      </c>
-      <c r="C78" s="18">
-        <v>45676</v>
-      </c>
-      <c r="D78" s="37" t="s">
-        <v>21</v>
-      </c>
-      <c r="E78" s="4"/>
-      <c r="F78" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H78" s="1" t="s">
-        <v>50</v>
       </c>
       <c r="J78" s="62"/>
     </row>
@@ -2568,27 +2558,38 @@
       <c r="B79" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="C79" s="18"/>
-      <c r="D79" s="4"/>
+      <c r="C79" s="18">
+        <v>45676</v>
+      </c>
+      <c r="D79" s="37" t="s">
+        <v>21</v>
+      </c>
       <c r="E79" s="4"/>
-      <c r="F79" s="4"/>
-      <c r="H79" s="11" t="s">
+      <c r="F79" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H79" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="J79" s="62"/>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A80" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B80" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="C80" s="18"/>
+      <c r="D80" s="4"/>
+      <c r="E80" s="4"/>
+      <c r="F80" s="4"/>
+      <c r="H80" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="I79" s="12">
+      <c r="I80" s="12">
         <v>45714</v>
       </c>
-      <c r="J79" s="62"/>
-    </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A80" s="60"/>
-      <c r="B80" s="61"/>
-      <c r="C80" s="67"/>
-      <c r="D80" s="60"/>
-      <c r="E80" s="60"/>
-      <c r="F80" s="60"/>
-      <c r="G80" s="68"/>
-      <c r="H80" s="60"/>
       <c r="J80" s="62"/>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
@@ -2600,29 +2601,33 @@
       <c r="F81" s="60"/>
       <c r="G81" s="68"/>
       <c r="H81" s="60"/>
-      <c r="I81" s="65" t="s">
+      <c r="J81" s="62"/>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A82" s="60"/>
+      <c r="B82" s="61"/>
+      <c r="C82" s="67"/>
+      <c r="D82" s="60"/>
+      <c r="E82" s="60"/>
+      <c r="F82" s="60"/>
+      <c r="G82" s="68"/>
+      <c r="H82" s="60"/>
+      <c r="I82" s="65" t="s">
         <v>93</v>
       </c>
-      <c r="J81" s="62"/>
-    </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A82" s="2"/>
-      <c r="B82" s="62"/>
-      <c r="C82" s="66"/>
-      <c r="D82" s="2"/>
-      <c r="E82" s="2"/>
-      <c r="F82" s="2"/>
-      <c r="G82" s="63"/>
-      <c r="H82" s="2"/>
-      <c r="I82" s="63"/>
       <c r="J82" s="62"/>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A83" s="1"/>
-      <c r="C83" s="38"/>
-      <c r="D83" s="1"/>
-      <c r="H83" s="1"/>
-      <c r="I83"/>
+      <c r="A83" s="2"/>
+      <c r="B83" s="62"/>
+      <c r="C83" s="66"/>
+      <c r="D83" s="2"/>
+      <c r="E83" s="2"/>
+      <c r="F83" s="2"/>
+      <c r="G83" s="63"/>
+      <c r="H83" s="2"/>
+      <c r="I83" s="63"/>
+      <c r="J83" s="62"/>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" s="1"/>
@@ -2632,481 +2637,479 @@
       <c r="I84"/>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A85" s="118"/>
-      <c r="B85" s="119" t="s">
+      <c r="A85" s="1"/>
+      <c r="C85" s="38"/>
+      <c r="D85" s="1"/>
+      <c r="H85" s="1"/>
+      <c r="I85"/>
+    </row>
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A86" s="117"/>
+      <c r="B86" s="118" t="s">
         <v>29</v>
       </c>
-      <c r="C85" s="120" t="s">
+      <c r="C86" s="119" t="s">
         <v>30</v>
       </c>
-      <c r="D85" s="119"/>
-      <c r="E85" s="121" t="s">
+      <c r="D86" s="118"/>
+      <c r="E86" s="120" t="s">
         <v>28</v>
       </c>
-      <c r="F85" s="121"/>
-      <c r="G85" s="122" t="s">
+      <c r="F86" s="120"/>
+      <c r="G86" s="121" t="s">
         <v>31</v>
       </c>
-      <c r="H85" s="119" t="s">
+      <c r="H86" s="118" t="s">
         <v>39</v>
       </c>
-      <c r="I85" s="119" t="s">
+      <c r="I86" s="118" t="s">
         <v>51</v>
       </c>
-      <c r="J85" s="113"/>
-    </row>
-    <row r="86" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="4" t="s">
+      <c r="J86" s="112"/>
+    </row>
+    <row r="87" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B86" s="51" t="s">
+      <c r="B87" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="C86" s="36">
+      <c r="C87" s="36">
         <v>45603</v>
       </c>
-      <c r="D86" s="4" t="s">
+      <c r="D87" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E86" s="37">
+      <c r="E87" s="37">
         <v>156000</v>
       </c>
-      <c r="F86" s="4" t="s">
+      <c r="F87" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="G86" s="6"/>
-      <c r="H86" s="1" t="s">
+      <c r="G87" s="6"/>
+      <c r="H87" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="I86" s="5">
-        <v>45705</v>
-      </c>
-      <c r="J86" s="113"/>
-    </row>
-    <row r="87" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="4"/>
-      <c r="B87" s="3"/>
-      <c r="C87" s="18"/>
-      <c r="D87" s="4"/>
-      <c r="E87" s="3"/>
-      <c r="F87" s="4"/>
-      <c r="G87" s="6"/>
-      <c r="H87" s="11" t="s">
-        <v>43</v>
       </c>
       <c r="I87" s="5">
         <v>45705</v>
       </c>
-      <c r="J87" s="113"/>
-    </row>
-    <row r="88" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="1"/>
-      <c r="B88" s="53" t="s">
+      <c r="J87" s="112"/>
+    </row>
+    <row r="88" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="4"/>
+      <c r="B88" s="3"/>
+      <c r="C88" s="18"/>
+      <c r="D88" s="4"/>
+      <c r="E88" s="3"/>
+      <c r="F88" s="4"/>
+      <c r="G88" s="6"/>
+      <c r="H88" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="I88" s="5">
+        <v>45705</v>
+      </c>
+      <c r="J88" s="112"/>
+    </row>
+    <row r="89" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="1"/>
+      <c r="B89" s="53" t="s">
         <v>37</v>
       </c>
-      <c r="C88" s="35">
+      <c r="C89" s="35">
         <v>45704</v>
       </c>
-      <c r="D88" s="1" t="s">
+      <c r="D89" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F88" s="1"/>
-      <c r="H88" s="1"/>
-      <c r="J88" s="113"/>
-    </row>
-    <row r="89" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="1"/>
-      <c r="B89" s="1" t="s">
+      <c r="F89" s="1"/>
+      <c r="H89" s="1"/>
+      <c r="J89" s="112"/>
+    </row>
+    <row r="90" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="1"/>
+      <c r="B90" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C89" s="19">
+      <c r="C90" s="19">
         <v>45705</v>
       </c>
-      <c r="D89" s="1" t="s">
+      <c r="D90" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="H89" s="1"/>
-      <c r="J89" s="113"/>
-    </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A90" s="1"/>
-      <c r="J90" s="113"/>
+      <c r="H90" s="1"/>
+      <c r="J90" s="112"/>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
-      <c r="C91" s="38" t="s">
+      <c r="J91" s="112"/>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A92" s="1"/>
+      <c r="C92" s="38" t="s">
         <v>56</v>
       </c>
-      <c r="D91" s="43" t="s">
+      <c r="D92" s="43" t="s">
         <v>68</v>
       </c>
-      <c r="G91" s="42"/>
-      <c r="H91" s="1"/>
-      <c r="J91" s="113"/>
-    </row>
-    <row r="92" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="1"/>
-      <c r="C92" s="38">
-        <v>45706</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>58</v>
-      </c>
+      <c r="G92" s="42"/>
       <c r="H92" s="1"/>
-      <c r="J92" s="113"/>
+      <c r="J92" s="112"/>
     </row>
     <row r="93" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="1"/>
-      <c r="C93" s="93">
+      <c r="C93" s="38">
+        <v>45706</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H93" s="1"/>
+      <c r="J93" s="112"/>
+    </row>
+    <row r="94" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="1"/>
+      <c r="C94" s="93">
         <v>45711</v>
       </c>
-      <c r="D93" s="89" t="s">
+      <c r="D94" s="89" t="s">
         <v>69</v>
       </c>
-      <c r="E93" s="89"/>
-      <c r="F93" s="89"/>
-      <c r="G93" s="91"/>
-      <c r="H93" s="89"/>
-      <c r="I93" s="92"/>
-      <c r="J93" s="113"/>
-    </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A94" s="1"/>
-      <c r="B94" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C94" s="40"/>
-      <c r="D94" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="H94" s="1"/>
-      <c r="J94" s="113"/>
+      <c r="E94" s="89"/>
+      <c r="F94" s="89"/>
+      <c r="G94" s="91"/>
+      <c r="H94" s="89"/>
+      <c r="I94" s="92"/>
+      <c r="J94" s="112"/>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" s="1"/>
+      <c r="B95" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C95" s="40"/>
       <c r="D95" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H95" s="1"/>
-      <c r="J95" s="113"/>
+      <c r="J95" s="112"/>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" s="1"/>
-      <c r="D96" s="1"/>
+      <c r="D96" s="1" t="s">
+        <v>73</v>
+      </c>
       <c r="H96" s="1"/>
-      <c r="I96" s="65" t="s">
-        <v>95</v>
-      </c>
-      <c r="J96" s="113"/>
+      <c r="J96" s="112"/>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" s="1"/>
       <c r="D97" s="1"/>
       <c r="H97" s="1"/>
       <c r="I97" s="65" t="s">
+        <v>95</v>
+      </c>
+      <c r="J97" s="112"/>
+    </row>
+    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A98" s="1"/>
+      <c r="D98" s="1"/>
+      <c r="H98" s="1"/>
+      <c r="I98" s="65" t="s">
         <v>92</v>
       </c>
-      <c r="J97" s="113"/>
-    </row>
-    <row r="98" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B98" s="106" t="s">
+      <c r="J98" s="112"/>
+    </row>
+    <row r="99" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B99" s="105" t="s">
         <v>53</v>
       </c>
-      <c r="C98" s="107">
+      <c r="C99" s="106">
         <v>45792</v>
       </c>
-      <c r="D98" s="108">
+      <c r="D99" s="107">
         <v>0.39583333333333331</v>
       </c>
-      <c r="E98" s="61"/>
-      <c r="F98" s="61" t="s">
+      <c r="E99" s="61"/>
+      <c r="F99" s="61" t="s">
         <v>107</v>
       </c>
-      <c r="G98" s="68"/>
-      <c r="H98" s="61"/>
-      <c r="I98" s="61"/>
-      <c r="J98" s="113"/>
-    </row>
-    <row r="99" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="113"/>
-      <c r="B99" s="114" t="s">
+      <c r="G99" s="68"/>
+      <c r="H99" s="61"/>
+      <c r="I99" s="61"/>
+      <c r="J99" s="112"/>
+    </row>
+    <row r="100" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="112"/>
+      <c r="B100" s="113" t="s">
         <v>110</v>
       </c>
-      <c r="C99" s="115">
+      <c r="C100" s="114">
         <v>45939</v>
       </c>
-      <c r="D99" s="116">
+      <c r="D100" s="115">
         <v>0.39583333333333331</v>
       </c>
-      <c r="E99" s="113"/>
-      <c r="F99" s="113"/>
-      <c r="G99" s="117"/>
-      <c r="H99" s="113"/>
-      <c r="I99" s="113"/>
-      <c r="J99" s="113"/>
-    </row>
-    <row r="100" spans="1:10" s="105" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B100" s="109"/>
-      <c r="C100" s="110"/>
-      <c r="D100" s="112"/>
-      <c r="G100" s="111"/>
-    </row>
-    <row r="101" spans="1:10" s="105" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B101" s="109"/>
-      <c r="C101" s="110"/>
-      <c r="D101" s="112"/>
-      <c r="G101" s="111"/>
-    </row>
-    <row r="102" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="8"/>
-      <c r="B102" s="8"/>
-      <c r="C102" s="17"/>
-      <c r="D102" s="8"/>
-      <c r="E102" s="8"/>
-      <c r="F102" s="8"/>
-      <c r="G102" s="9"/>
-      <c r="H102" s="8"/>
-      <c r="I102" s="9"/>
-    </row>
-    <row r="103" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="22" t="s">
+      <c r="E100" s="112"/>
+      <c r="F100" s="112"/>
+      <c r="G100" s="116"/>
+      <c r="H100" s="112"/>
+      <c r="I100" s="112"/>
+      <c r="J100" s="112"/>
+    </row>
+    <row r="101" spans="1:10" s="104" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B101" s="108"/>
+      <c r="C101" s="109"/>
+      <c r="D101" s="111"/>
+      <c r="G101" s="110"/>
+    </row>
+    <row r="102" spans="1:10" s="104" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B102" s="108"/>
+      <c r="C102" s="109"/>
+      <c r="D102" s="111"/>
+      <c r="G102" s="110"/>
+    </row>
+    <row r="103" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="8"/>
+      <c r="B103" s="8"/>
+      <c r="C103" s="17"/>
+      <c r="D103" s="8"/>
+      <c r="E103" s="8"/>
+      <c r="F103" s="8"/>
+      <c r="G103" s="9"/>
+      <c r="H103" s="8"/>
+      <c r="I103" s="9"/>
+    </row>
+    <row r="104" spans="1:10" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="B103" s="51" t="s">
+      <c r="B104" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="C103" s="24">
+      <c r="C104" s="24">
         <v>45588</v>
       </c>
-      <c r="D103" s="22" t="s">
+      <c r="D104" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="E103" s="23"/>
-      <c r="F103" s="23"/>
-      <c r="G103" s="7">
-        <v>45672</v>
-      </c>
-      <c r="H103" s="22" t="s">
-        <v>45</v>
-      </c>
-      <c r="I103" s="25">
-        <v>45625</v>
-      </c>
-    </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A104" s="22"/>
-      <c r="B104" s="51" t="s">
-        <v>87</v>
-      </c>
-      <c r="C104" s="24"/>
-      <c r="D104" s="22"/>
       <c r="E104" s="23"/>
       <c r="F104" s="23"/>
-      <c r="G104" s="7"/>
-      <c r="H104" s="22"/>
-      <c r="I104" s="25"/>
+      <c r="G104" s="7">
+        <v>45672</v>
+      </c>
+      <c r="H104" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="I104" s="25">
+        <v>45625</v>
+      </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A105" s="22" t="s">
-        <v>13</v>
-      </c>
+      <c r="A105" s="22"/>
       <c r="B105" s="51" t="s">
-        <v>5</v>
-      </c>
-      <c r="C105" s="24">
-        <v>45588</v>
-      </c>
-      <c r="D105" s="22" t="s">
-        <v>21</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="C105" s="24"/>
+      <c r="D105" s="22"/>
       <c r="E105" s="23"/>
       <c r="F105" s="23"/>
-      <c r="G105" s="7">
-        <v>45672</v>
-      </c>
-      <c r="H105" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="I105" s="25">
-        <v>45625</v>
-      </c>
+      <c r="G105" s="7"/>
+      <c r="H105" s="22"/>
+      <c r="I105" s="25"/>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A106" s="11" t="s">
+      <c r="A106" s="22" t="s">
         <v>13</v>
       </c>
       <c r="B106" s="51" t="s">
-        <v>8</v>
-      </c>
-      <c r="C106" s="27">
-        <v>45475</v>
-      </c>
-      <c r="D106" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="E106" s="26">
-        <v>113</v>
-      </c>
-      <c r="F106" s="11" t="s">
-        <v>26</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="C106" s="24">
+        <v>45588</v>
+      </c>
+      <c r="D106" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="E106" s="23"/>
+      <c r="F106" s="23"/>
       <c r="G106" s="7">
         <v>45672</v>
       </c>
-      <c r="H106" s="11" t="s">
+      <c r="H106" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="I106" s="25">
+        <v>45625</v>
+      </c>
+    </row>
+    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A107" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B107" s="51" t="s">
+        <v>8</v>
+      </c>
+      <c r="C107" s="27">
+        <v>45475</v>
+      </c>
+      <c r="D107" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E107" s="26">
+        <v>113</v>
+      </c>
+      <c r="F107" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="G107" s="7">
+        <v>45672</v>
+      </c>
+      <c r="H107" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="I106" s="28">
+      <c r="I107" s="28">
         <v>45705</v>
       </c>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A107" s="11"/>
-      <c r="B107" s="51" t="s">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A108" s="11"/>
+      <c r="B108" s="51" t="s">
         <v>86</v>
       </c>
-      <c r="C107" s="27"/>
-      <c r="D107" s="11"/>
-      <c r="E107" s="26"/>
-      <c r="F107" s="11"/>
-      <c r="G107" s="7"/>
-      <c r="H107" s="11"/>
-      <c r="I107" s="28"/>
-    </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A108" s="11" t="s">
+      <c r="C108" s="27"/>
+      <c r="D108" s="11"/>
+      <c r="E108" s="26"/>
+      <c r="F108" s="11"/>
+      <c r="G108" s="7"/>
+      <c r="H108" s="11"/>
+      <c r="I108" s="28"/>
+    </row>
+    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A109" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B108" s="51" t="s">
+      <c r="B109" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="C108" s="27"/>
-      <c r="D108" s="11" t="s">
+      <c r="C109" s="27"/>
+      <c r="D109" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E108" s="26">
+      <c r="E109" s="26">
         <v>113</v>
       </c>
-      <c r="F108" s="11" t="s">
+      <c r="F109" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="G108" s="7">
+      <c r="G109" s="7">
         <v>45672</v>
       </c>
-      <c r="H108" s="34" t="s">
+      <c r="H109" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="I108" s="28">
+      <c r="I109" s="28">
         <v>45705</v>
       </c>
     </row>
-    <row r="112" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="10"/>
-      <c r="B112" s="8"/>
-      <c r="C112" s="17"/>
-      <c r="D112" s="10"/>
-      <c r="E112" s="8"/>
-      <c r="F112" s="9"/>
-      <c r="G112" s="9"/>
-      <c r="H112" s="9"/>
-      <c r="I112" s="9"/>
-    </row>
-    <row r="113" spans="1:9" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="22" t="s">
+    <row r="113" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A113" s="10"/>
+      <c r="B113" s="8"/>
+      <c r="C113" s="17"/>
+      <c r="D113" s="10"/>
+      <c r="E113" s="8"/>
+      <c r="F113" s="9"/>
+      <c r="G113" s="9"/>
+      <c r="H113" s="9"/>
+      <c r="I113" s="9"/>
+    </row>
+    <row r="114" spans="1:9" ht="16.5" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="B113" s="123" t="s">
+      <c r="B114" s="122" t="s">
         <v>9</v>
       </c>
-      <c r="C113" s="164">
+      <c r="C114" s="163">
         <v>45438</v>
       </c>
-      <c r="D113" s="22" t="s">
+      <c r="D114" s="22" t="s">
         <v>20</v>
       </c>
-      <c r="E113" s="22">
+      <c r="E114" s="22">
         <v>0</v>
       </c>
-      <c r="F113" s="160" t="s">
+      <c r="F114" s="159" t="s">
         <v>27</v>
       </c>
-      <c r="G113" s="29"/>
-      <c r="H113" s="22" t="s">
+      <c r="G114" s="29"/>
+      <c r="H114" s="22" t="s">
         <v>119</v>
-      </c>
-      <c r="I113" s="29"/>
-    </row>
-    <row r="114" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A114" s="22"/>
-      <c r="B114" s="163" t="s">
-        <v>17</v>
-      </c>
-      <c r="C114" s="161">
-        <v>45486</v>
-      </c>
-      <c r="D114" s="22" t="s">
-        <v>25</v>
-      </c>
-      <c r="E114" s="22"/>
-      <c r="F114" s="162" t="s">
-        <v>27</v>
-      </c>
-      <c r="G114" s="166">
-        <v>45588</v>
-      </c>
-      <c r="H114" s="22" t="s">
-        <v>118</v>
       </c>
       <c r="I114" s="29"/>
     </row>
     <row r="115" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A115" s="22"/>
-      <c r="B115" s="163" t="s">
+      <c r="B115" s="162" t="s">
+        <v>17</v>
+      </c>
+      <c r="C115" s="160">
+        <v>45486</v>
+      </c>
+      <c r="D115" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="E115" s="22"/>
+      <c r="F115" s="161" t="s">
+        <v>27</v>
+      </c>
+      <c r="G115" s="165">
+        <v>45588</v>
+      </c>
+      <c r="H115" s="22" t="s">
+        <v>118</v>
+      </c>
+      <c r="I115" s="29"/>
+    </row>
+    <row r="116" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A116" s="22"/>
+      <c r="B116" s="162" t="s">
         <v>18</v>
       </c>
-      <c r="C115" s="161">
+      <c r="C116" s="160">
         <v>45590</v>
       </c>
-      <c r="D115" s="22" t="s">
+      <c r="D116" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="E115" s="22"/>
-      <c r="F115" s="162" t="s">
+      <c r="E116" s="22"/>
+      <c r="F116" s="161" t="s">
         <v>27</v>
       </c>
-      <c r="G115" s="166">
+      <c r="G116" s="165">
         <v>45688</v>
       </c>
-      <c r="H115" s="22" t="s">
+      <c r="H116" s="22" t="s">
         <v>116</v>
       </c>
-      <c r="I115" s="29"/>
-    </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A116" s="22"/>
-      <c r="B116" s="124"/>
-      <c r="C116" s="125"/>
-      <c r="D116" s="124" t="s">
+      <c r="I116" s="29"/>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A117" s="22"/>
+      <c r="B117" s="123"/>
+      <c r="C117" s="124"/>
+      <c r="D117" s="123" t="s">
         <v>32</v>
       </c>
-      <c r="E116" s="124"/>
-      <c r="F116" s="126"/>
-      <c r="G116" s="165">
+      <c r="E117" s="123"/>
+      <c r="F117" s="125"/>
+      <c r="G117" s="164">
         <v>45782</v>
       </c>
-      <c r="H116" s="22" t="s">
+      <c r="H117" s="22" t="s">
         <v>117</v>
       </c>
-      <c r="I116" s="29"/>
-    </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A117" s="1"/>
-      <c r="B117" s="14"/>
-      <c r="C117" s="20"/>
-      <c r="D117" s="1"/>
-      <c r="E117" s="14"/>
-      <c r="F117" s="16"/>
-      <c r="G117" s="15"/>
+      <c r="I117" s="29"/>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" s="1"/>
@@ -3117,6 +3120,15 @@
       <c r="F118" s="16"/>
       <c r="G118" s="15"/>
     </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A119" s="1"/>
+      <c r="B119" s="14"/>
+      <c r="C119" s="20"/>
+      <c r="D119" s="1"/>
+      <c r="E119" s="14"/>
+      <c r="F119" s="16"/>
+      <c r="G119" s="15"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/mahkeme/2025-02-Dosya Listesi.xlsx
+++ b/mahkeme/2025-02-Dosya Listesi.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\aaGitMe\yzhn\mahkeme\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75547575-94AD-4E5E-9A80-DEA0F1073CB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12CF33D1-EF10-40A8-9BDE-3981F95F7B80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sayfa1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="134">
   <si>
     <t>Dosya Listesi</t>
   </si>
@@ -412,6 +413,48 @@
   </si>
   <si>
     <t>dava</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/12081 </t>
+  </si>
+  <si>
+    <t>soruşturma</t>
+  </si>
+  <si>
+    <t>2025/10342</t>
+  </si>
+  <si>
+    <t>tehdit</t>
+  </si>
+  <si>
+    <t>cmhrbşk</t>
+  </si>
+  <si>
+    <t>2025/1676</t>
+  </si>
+  <si>
+    <t>iddianae</t>
+  </si>
+  <si>
+    <t>2025/2221</t>
+  </si>
+  <si>
+    <t>TCK 125-3A</t>
+  </si>
+  <si>
+    <t>TCK 53-1</t>
+  </si>
+  <si>
+    <t>2025/478</t>
+  </si>
+  <si>
+    <t>salih-ali-duran-samed-umut</t>
+  </si>
+  <si>
+    <t>2025/668</t>
+  </si>
+  <si>
+    <t>toyota</t>
   </si>
 </sst>
 </file>
@@ -827,7 +870,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="166">
+  <cellXfs count="167">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1096,6 +1139,7 @@
     </xf>
     <xf numFmtId="164" fontId="16" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="15" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3133,4 +3177,101 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BE28945-35B1-45CD-8C11-D11D54E7ECA8}">
+  <dimension ref="A4:G15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" style="5"/>
+    <col min="6" max="6" width="12.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="5">
+        <v>45967</v>
+      </c>
+      <c r="B4" t="s">
+        <v>120</v>
+      </c>
+      <c r="D4" t="s">
+        <v>121</v>
+      </c>
+      <c r="E4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="5">
+        <v>45927</v>
+      </c>
+      <c r="B5" t="s">
+        <v>122</v>
+      </c>
+      <c r="D5" t="s">
+        <v>121</v>
+      </c>
+      <c r="E5" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="5">
+        <v>45708</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G7" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="D8" s="5">
+        <v>46064</v>
+      </c>
+      <c r="E8" s="166">
+        <v>0.41666666666666669</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D9" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D15" s="5">
+        <v>46028</v>
+      </c>
+      <c r="E15" s="166">
+        <v>0.42708333333333331</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
 </file>
--- a/mahkeme/2025-02-Dosya Listesi.xlsx
+++ b/mahkeme/2025-02-Dosya Listesi.xlsx
@@ -5,12 +5,12 @@
   <workbookPr showInkAnnotation="0" autoCompressPictures="0" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\aaGitMe\yzhn\mahkeme\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\aaGitMe_2026\26-yzhn\mahkeme\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12CF33D1-EF10-40A8-9BDE-3981F95F7B80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA6970DF-FDB5-4272-B23E-66520D80D43C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3375" yWindow="3375" windowWidth="21600" windowHeight="11295" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="135">
   <si>
     <t>Dosya Listesi</t>
   </si>
@@ -455,6 +455,9 @@
   </si>
   <si>
     <t>toyota</t>
+  </si>
+  <si>
+    <t>adli tıp taporunun beklenmesi</t>
   </si>
 </sst>
 </file>
@@ -2895,15 +2898,21 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="E100" s="112"/>
-      <c r="F100" s="112"/>
+      <c r="F100" s="112" t="s">
+        <v>134</v>
+      </c>
       <c r="G100" s="116"/>
       <c r="H100" s="112"/>
       <c r="I100" s="112"/>
       <c r="J100" s="112"/>
     </row>
     <row r="101" spans="1:10" s="104" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B101" s="108"/>
-      <c r="C101" s="109"/>
+      <c r="B101" s="108" t="s">
+        <v>110</v>
+      </c>
+      <c r="C101" s="109">
+        <v>46079</v>
+      </c>
       <c r="D101" s="111"/>
       <c r="G101" s="110"/>
     </row>
@@ -3014,6 +3023,9 @@
       </c>
       <c r="I107" s="28">
         <v>45705</v>
+      </c>
+      <c r="J107">
+        <v>86000</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
